--- a/arquivos extras/Planilha.xlsx
+++ b/arquivos extras/Planilha.xlsx
@@ -91,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1618" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="263">
   <si>
     <t xml:space="preserve">JAN</t>
   </si>
@@ -673,6 +673,12 @@
   </si>
   <si>
     <t xml:space="preserve">JUL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cartao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">\</t>
   </si>
   <si>
     <t xml:space="preserve">AGO</t>
@@ -2350,10 +2356,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.0673788003286771"/>
-          <c:y val="0.102142771156856"/>
-          <c:w val="0.74826324045716"/>
-          <c:h val="0.815697604429999"/>
+          <c:x val="0.0673813169984686"/>
+          <c:y val="0.102148919520857"/>
+          <c:w val="0.748253837821686"/>
+          <c:h val="0.815626316739903"/>
         </c:manualLayout>
       </c:layout>
       <c:pie3DChart>
@@ -3008,7 +3014,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>448.64</c:v>
+                  <c:v>468.64</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>710</c:v>
@@ -3337,9 +3343,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>47160</xdr:colOff>
+      <xdr:colOff>46800</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>21960</xdr:rowOff>
+      <xdr:rowOff>21600</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3348,7 +3354,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
-        <a:ext cx="9638280" cy="5980680"/>
+        <a:ext cx="9637920" cy="5980320"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3626,7 +3632,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46201</v>
+        <v>46209</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -4793,7 +4799,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -4821,7 +4827,7 @@
       </c>
       <c r="F3" s="11" t="n">
         <f aca="false">SUM(D3,D5,D6,D7,D4)</f>
-        <v>69.9999999999998</v>
+        <v>-129.7</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>6</v>
@@ -4849,7 +4855,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46201</v>
+        <v>46209</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -4908,14 +4914,14 @@
       <c r="C7" s="33"/>
       <c r="D7" s="34" t="n">
         <f aca="false">Set!F7</f>
-        <v>69.9999999999998</v>
+        <v>-129.7</v>
       </c>
       <c r="E7" s="35" t="s">
         <v>19</v>
       </c>
       <c r="F7" s="36" t="n">
         <f aca="false">F3-F4-F6</f>
-        <v>69.9999999999998</v>
+        <v>-129.7</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5865,7 +5871,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -5893,7 +5899,7 @@
       </c>
       <c r="F3" s="11" t="n">
         <f aca="false">SUM(D3,D5,D6,D7,D4)</f>
-        <v>69.9999999999998</v>
+        <v>-129.7</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>6</v>
@@ -5921,7 +5927,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46201</v>
+        <v>46209</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -5980,14 +5986,14 @@
       <c r="C7" s="33"/>
       <c r="D7" s="34" t="n">
         <f aca="false">Out!F7</f>
-        <v>69.9999999999998</v>
+        <v>-129.7</v>
       </c>
       <c r="E7" s="35" t="s">
         <v>19</v>
       </c>
       <c r="F7" s="36" t="n">
         <f aca="false">F3-F4-F6</f>
-        <v>69.9999999999998</v>
+        <v>-129.7</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6940,7 +6946,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -6968,7 +6974,7 @@
       </c>
       <c r="F3" s="11" t="n">
         <f aca="false">SUM(D3,D5,D6,D7,D4)</f>
-        <v>69.9999999999998</v>
+        <v>-129.7</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>6</v>
@@ -6996,7 +7002,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46201</v>
+        <v>46209</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -7055,14 +7061,14 @@
       <c r="C7" s="33"/>
       <c r="D7" s="34" t="n">
         <f aca="false">Nov!F7</f>
-        <v>69.9999999999998</v>
+        <v>-129.7</v>
       </c>
       <c r="E7" s="35" t="s">
         <v>19</v>
       </c>
       <c r="F7" s="36" t="n">
         <f aca="false">F3-F4-F6</f>
-        <v>69.9999999999998</v>
+        <v>-129.7</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8017,46 +8023,46 @@
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="100" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C2" s="101" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D2" s="102" t="s">
         <v>106</v>
       </c>
       <c r="E2" s="102" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F2" s="102" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G2" s="102" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="H2" s="102" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I2" s="102" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="J2" s="102" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="K2" s="102" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L2" s="102" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M2" s="102" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N2" s="103" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="O2" s="103" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8093,32 +8099,32 @@
       </c>
       <c r="J3" s="106" t="n">
         <f aca="false">Ago!$F$3</f>
-        <v>69.9999999999998</v>
+        <v>-129.7</v>
       </c>
       <c r="K3" s="106" t="n">
         <f aca="false">Set!$F$3</f>
-        <v>69.9999999999998</v>
+        <v>-129.7</v>
       </c>
       <c r="L3" s="106" t="n">
         <f aca="false">Out!$F$3</f>
-        <v>69.9999999999998</v>
+        <v>-129.7</v>
       </c>
       <c r="M3" s="106" t="n">
         <f aca="false">Nov!$F$3</f>
-        <v>69.9999999999998</v>
+        <v>-129.7</v>
       </c>
       <c r="N3" s="107" t="n">
         <f aca="false">Dez!$F$3</f>
-        <v>69.9999999999998</v>
+        <v>-129.7</v>
       </c>
       <c r="O3" s="107" t="n">
         <f aca="false">SUM(C3:N3)</f>
-        <v>16323.37</v>
+        <v>15324.87</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="108" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C4" s="109" t="n">
         <f aca="false">Jan!$F$4</f>
@@ -8146,7 +8152,7 @@
       </c>
       <c r="I4" s="109" t="n">
         <f aca="false">Jul!$F$4</f>
-        <v>0</v>
+        <v>179.7</v>
       </c>
       <c r="J4" s="109" t="n">
         <f aca="false">Ago!$F$4</f>
@@ -8170,12 +8176,12 @@
       </c>
       <c r="O4" s="110" t="n">
         <f aca="false">SUM(C4:N4)</f>
-        <v>7621.35</v>
+        <v>7801.05</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="108" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C5" s="111" t="n">
         <f aca="false">Jan!$F$6</f>
@@ -8203,7 +8209,7 @@
       </c>
       <c r="I5" s="111" t="n">
         <f aca="false">Jul!$F$6</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J5" s="111" t="n">
         <f aca="false">Ago!$F$6</f>
@@ -8227,7 +8233,7 @@
       </c>
       <c r="O5" s="112" t="n">
         <f aca="false">SUM(C5:N5)</f>
-        <v>3639.22</v>
+        <v>3659.22</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8289,7 +8295,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="108" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C7" s="116" t="n">
         <f aca="false">Jan!$L$4</f>
@@ -8346,7 +8352,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="108" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C8" s="119" t="n">
         <f aca="false">C4+C5</f>
@@ -8374,7 +8380,7 @@
       </c>
       <c r="I8" s="119" t="n">
         <f aca="false">I4+I5</f>
-        <v>0</v>
+        <v>199.7</v>
       </c>
       <c r="J8" s="119" t="n">
         <f aca="false">J4+J5</f>
@@ -8398,7 +8404,7 @@
       </c>
       <c r="O8" s="120" t="n">
         <f aca="false">SUM(C8:N8)</f>
-        <v>11260.57</v>
+        <v>11460.27</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8431,31 +8437,31 @@
       </c>
       <c r="I9" s="121" t="n">
         <f aca="false">I3-I8</f>
-        <v>69.9999999999998</v>
+        <v>-129.7</v>
       </c>
       <c r="J9" s="121" t="n">
         <f aca="false">J3-J8</f>
-        <v>69.9999999999998</v>
+        <v>-129.7</v>
       </c>
       <c r="K9" s="121" t="n">
         <f aca="false">K3-K8</f>
-        <v>69.9999999999998</v>
+        <v>-129.7</v>
       </c>
       <c r="L9" s="121" t="n">
         <f aca="false">L3-L8</f>
-        <v>69.9999999999998</v>
+        <v>-129.7</v>
       </c>
       <c r="M9" s="121" t="n">
         <f aca="false">M3-M8</f>
-        <v>69.9999999999998</v>
+        <v>-129.7</v>
       </c>
       <c r="N9" s="122" t="n">
         <f aca="false">N3-N8</f>
-        <v>69.9999999999998</v>
+        <v>-129.7</v>
       </c>
       <c r="O9" s="122" t="n">
         <f aca="false">N9</f>
-        <v>69.9999999999998</v>
+        <v>-129.7</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8525,46 +8531,46 @@
     <row r="14" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="100" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C15" s="101" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D15" s="102" t="s">
         <v>106</v>
       </c>
       <c r="E15" s="102" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F15" s="102" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G15" s="102" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="H15" s="102" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I15" s="102" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="J15" s="102" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="K15" s="102" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L15" s="102" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M15" s="102" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N15" s="103" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="O15" s="103" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9052,7 +9058,7 @@
         <v>30</v>
       </c>
       <c r="I28" s="143" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="J28" s="143"/>
       <c r="K28" s="143"/>
@@ -9078,19 +9084,19 @@
         <v>380.9</v>
       </c>
       <c r="I29" s="145" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="J29" s="146" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="K29" s="146" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L29" s="146" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M29" s="147" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9109,10 +9115,10 @@
         <v>0</v>
       </c>
       <c r="I30" s="148" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="J30" s="149" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K30" s="149" t="n">
         <v>201.64</v>
@@ -9140,10 +9146,10 @@
         <v>0</v>
       </c>
       <c r="I31" s="151" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="J31" s="149" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="K31" s="149" t="n">
         <v>1289.99</v>
@@ -9164,13 +9170,13 @@
       </c>
       <c r="G32" s="75" t="n">
         <f aca="false">SUBTOTAL(9,Jan!I39,Fev!I39,Mar!I39,Abr!I39,Mai!I39,Jun!I39,Jul!I39,Ago!I39,Set!I39,Out!I39,Nov!I39,Dez!I39)</f>
-        <v>448.64</v>
+        <v>468.64</v>
       </c>
       <c r="I32" s="151" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J32" s="149" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="K32" s="149" t="n">
         <v>700</v>
@@ -9202,13 +9208,13 @@
         <v>710</v>
       </c>
       <c r="H33" s="99" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="I33" s="151" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="J33" s="149" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K33" s="149" t="n">
         <v>128</v>
@@ -9245,10 +9251,10 @@
         <v>5165.22</v>
       </c>
       <c r="I34" s="151" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="J34" s="149" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K34" s="149" t="n">
         <v>320.74</v>
@@ -9277,10 +9283,10 @@
         <v>1889.68</v>
       </c>
       <c r="I35" s="151" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="J35" s="149" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K35" s="149" t="n">
         <v>1715.14</v>
@@ -9309,10 +9315,10 @@
         <v>0</v>
       </c>
       <c r="I36" s="151" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="J36" s="151" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="K36" s="151" t="n">
         <v>809.71</v>
@@ -9341,10 +9347,10 @@
         <v>6100.33</v>
       </c>
       <c r="I37" s="152" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="J37" s="132" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="K37" s="153" t="n">
         <v>2378</v>
@@ -9371,10 +9377,10 @@
         <v>0</v>
       </c>
       <c r="I38" s="151" t="s">
+        <v>241</v>
+      </c>
+      <c r="J38" s="149" t="s">
         <v>239</v>
-      </c>
-      <c r="J38" s="149" t="s">
-        <v>237</v>
       </c>
       <c r="K38" s="149" t="n">
         <v>78.9</v>
@@ -9394,10 +9400,10 @@
         <v>0</v>
       </c>
       <c r="I39" s="151" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="J39" s="149" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="K39" s="149" t="n">
         <v>630</v>
@@ -9418,10 +9424,10 @@
         <v>0</v>
       </c>
       <c r="I40" s="156" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="J40" s="149" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K40" s="149" t="n">
         <v>394</v>
@@ -9439,10 +9445,10 @@
       <c r="C41" s="64"/>
       <c r="D41" s="78"/>
       <c r="I41" s="156" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="J41" s="149" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K41" s="149" t="n">
         <v>208.14</v>
@@ -9454,10 +9460,10 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I42" s="151" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="J42" s="149" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="K42" s="149" t="n">
         <v>59.9</v>
@@ -9482,13 +9488,13 @@
         <v>107.4</v>
       </c>
       <c r="H43" s="99" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="I43" s="151" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="J43" s="149" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K43" s="149" t="n">
         <v>175</v>
@@ -9518,10 +9524,10 @@
         <v>1652.7</v>
       </c>
       <c r="I44" s="157" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J44" s="158" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K44" s="158" t="n">
         <v>106.76</v>
@@ -9552,7 +9558,7 @@
         <v>142</v>
       </c>
       <c r="I46" s="160" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J46" s="160"/>
       <c r="K46" s="160"/>
@@ -9857,10 +9863,10 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B83" s="69" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C83" s="70" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D83" s="71" t="n">
         <f aca="false">SUBTOTAL(9,Fev!D90,Fev!D90,Mar!D90,Abr!D90,Mai!D90,Jun!D90,Jul!D90,Ago!D90,Set!D90,Out!D90,Nov!D90,Dez!D90)</f>
@@ -9967,7 +9973,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C2" s="162" t="s">
         <v>1</v>
@@ -9997,10 +10003,10 @@
       <c r="G3" s="164"/>
       <c r="H3" s="163"/>
       <c r="M3" s="167" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="N3" s="167" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="P3" s="168" t="s">
         <v>64</v>
@@ -10065,7 +10071,7 @@
         <v>154</v>
       </c>
       <c r="P6" s="168" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="R6" s="169" t="s">
         <v>71</v>
@@ -10077,7 +10083,7 @@
       </c>
       <c r="C7" s="33"/>
       <c r="D7" s="34" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F7" s="36" t="n">
         <f aca="false">F3-F4-F6</f>
@@ -10216,7 +10222,7 @@
       <c r="J13" s="60"/>
       <c r="K13" s="172"/>
       <c r="N13" s="170" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="R13" s="169" t="s">
         <v>129</v>
@@ -10407,7 +10413,7 @@
         <v>Transporte</v>
       </c>
       <c r="N29" s="170" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10505,7 +10511,7 @@
         <v>Educação</v>
       </c>
       <c r="N37" s="177" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10545,7 +10551,7 @@
       <c r="J40" s="54"/>
       <c r="K40" s="55"/>
       <c r="N40" s="177" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10661,7 +10667,7 @@
       <c r="J47" s="54"/>
       <c r="K47" s="55"/>
       <c r="N47" s="170" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10684,7 +10690,7 @@
       <c r="J49" s="54"/>
       <c r="K49" s="55"/>
       <c r="N49" s="170" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11166,7 +11172,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46201</v>
+        <v>46209</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -12359,7 +12365,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46201</v>
+        <v>46209</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -13567,7 +13573,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46201</v>
+        <v>46209</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -14850,7 +14856,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46201</v>
+        <v>46209</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>150</v>
@@ -16136,7 +16142,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46201</v>
+        <v>46209</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>170</v>
@@ -17382,11 +17388,11 @@
       </c>
       <c r="F4" s="19" t="n">
         <f aca="false">SUM(F11:F32)</f>
-        <v>0</v>
+        <v>179.7</v>
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46201</v>
+        <v>46209</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -17428,7 +17434,7 @@
       </c>
       <c r="F6" s="28" t="n">
         <f aca="false">SUM(K11:K22)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I6" s="29" t="n">
         <v>45847</v>
@@ -17452,7 +17458,7 @@
       </c>
       <c r="F7" s="36" t="n">
         <f aca="false">F3-F4-F6</f>
-        <v>69.9999999999998</v>
+        <v>-129.7</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17519,12 +17525,20 @@
       <c r="B11" s="47"/>
       <c r="C11" s="92"/>
       <c r="D11" s="92"/>
-      <c r="E11" s="48"/>
-      <c r="F11" s="49"/>
+      <c r="E11" s="48" t="s">
+        <v>194</v>
+      </c>
+      <c r="F11" s="49" t="n">
+        <v>179.7</v>
+      </c>
       <c r="H11" s="50"/>
-      <c r="I11" s="93"/>
+      <c r="I11" s="51" t="s">
+        <v>49</v>
+      </c>
       <c r="J11" s="51"/>
-      <c r="K11" s="46"/>
+      <c r="K11" s="46" t="n">
+        <v>20</v>
+      </c>
       <c r="M11" s="52"/>
       <c r="N11" s="53"/>
       <c r="O11" s="54"/>
@@ -17537,9 +17551,11 @@
       <c r="E12" s="16"/>
       <c r="F12" s="58"/>
       <c r="H12" s="59"/>
-      <c r="I12" s="93"/>
+      <c r="I12" s="51"/>
       <c r="J12" s="60"/>
-      <c r="K12" s="55"/>
+      <c r="K12" s="55" t="s">
+        <v>195</v>
+      </c>
       <c r="M12" s="52"/>
       <c r="N12" s="53"/>
       <c r="O12" s="54"/>
@@ -17552,7 +17568,7 @@
       <c r="E13" s="16"/>
       <c r="F13" s="58"/>
       <c r="H13" s="59"/>
-      <c r="I13" s="93"/>
+      <c r="I13" s="51"/>
       <c r="J13" s="60"/>
       <c r="K13" s="55"/>
       <c r="M13" s="52"/>
@@ -17567,7 +17583,7 @@
       <c r="E14" s="16"/>
       <c r="F14" s="58"/>
       <c r="H14" s="59"/>
-      <c r="I14" s="93"/>
+      <c r="I14" s="51"/>
       <c r="J14" s="60"/>
       <c r="K14" s="55"/>
       <c r="M14" s="52"/>
@@ -17582,7 +17598,7 @@
       <c r="E15" s="16"/>
       <c r="F15" s="58"/>
       <c r="H15" s="59"/>
-      <c r="I15" s="93"/>
+      <c r="I15" s="51"/>
       <c r="J15" s="60"/>
       <c r="K15" s="55"/>
       <c r="M15" s="52"/>
@@ -17597,7 +17613,7 @@
       <c r="E16" s="16"/>
       <c r="F16" s="58"/>
       <c r="H16" s="59"/>
-      <c r="I16" s="93"/>
+      <c r="I16" s="51"/>
       <c r="J16" s="60"/>
       <c r="K16" s="55"/>
       <c r="M16" s="52"/>
@@ -17612,7 +17628,7 @@
       <c r="E17" s="16"/>
       <c r="F17" s="58"/>
       <c r="H17" s="59"/>
-      <c r="I17" s="93"/>
+      <c r="I17" s="51"/>
       <c r="J17" s="60"/>
       <c r="K17" s="55"/>
       <c r="M17" s="52"/>
@@ -17627,7 +17643,7 @@
       <c r="E18" s="16"/>
       <c r="F18" s="58"/>
       <c r="H18" s="59"/>
-      <c r="I18" s="93"/>
+      <c r="I18" s="51"/>
       <c r="J18" s="60"/>
       <c r="K18" s="55"/>
       <c r="M18" s="52"/>
@@ -17642,7 +17658,7 @@
       <c r="E19" s="16"/>
       <c r="F19" s="58"/>
       <c r="H19" s="59"/>
-      <c r="I19" s="93"/>
+      <c r="I19" s="51"/>
       <c r="J19" s="60"/>
       <c r="K19" s="55"/>
       <c r="M19" s="52"/>
@@ -17657,7 +17673,7 @@
       <c r="E20" s="16"/>
       <c r="F20" s="58"/>
       <c r="H20" s="59"/>
-      <c r="I20" s="93"/>
+      <c r="I20" s="51"/>
       <c r="J20" s="60"/>
       <c r="K20" s="55"/>
       <c r="M20" s="52"/>
@@ -17672,7 +17688,7 @@
       <c r="E21" s="16"/>
       <c r="F21" s="58"/>
       <c r="H21" s="59"/>
-      <c r="I21" s="93"/>
+      <c r="I21" s="51"/>
       <c r="J21" s="60"/>
       <c r="K21" s="55"/>
       <c r="M21" s="52"/>
@@ -17703,7 +17719,7 @@
       <c r="F23" s="58"/>
       <c r="K23" s="12" t="n">
         <f aca="false">SUM(K11:K22)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M23" s="52"/>
       <c r="N23" s="53"/>
@@ -17863,7 +17879,7 @@
       </c>
       <c r="I39" s="75" t="n">
         <f aca="false">SUMIF($I$11:$I$22,H39,$K$11:$K$22)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18402,7 +18418,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -18430,7 +18446,7 @@
       </c>
       <c r="F3" s="11" t="n">
         <f aca="false">SUM(D3,D5,D6,D7,D4)</f>
-        <v>69.9999999999998</v>
+        <v>-129.7</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>6</v>
@@ -18445,7 +18461,7 @@
         <v>8</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D4" s="17" t="n">
         <f aca="false">SUM(P10:P25)</f>
@@ -18460,7 +18476,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46201</v>
+        <v>46209</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -18519,14 +18535,14 @@
       <c r="C7" s="33"/>
       <c r="D7" s="34" t="n">
         <f aca="false">Jul!F7</f>
-        <v>69.9999999999998</v>
+        <v>-129.7</v>
       </c>
       <c r="E7" s="35" t="s">
         <v>19</v>
       </c>
       <c r="F7" s="36" t="n">
         <f aca="false">F3-F4-F6</f>
-        <v>69.9999999999998</v>
+        <v>-129.7</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19476,7 +19492,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -19504,7 +19520,7 @@
       </c>
       <c r="F3" s="11" t="n">
         <f aca="false">SUM(D3,D5,D6,D7,D4)</f>
-        <v>69.9999999999998</v>
+        <v>-129.7</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>6</v>
@@ -19532,7 +19548,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46201</v>
+        <v>46209</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -19591,14 +19607,14 @@
       <c r="C7" s="33"/>
       <c r="D7" s="34" t="n">
         <f aca="false">Ago!F7</f>
-        <v>69.9999999999998</v>
+        <v>-129.7</v>
       </c>
       <c r="E7" s="35" t="s">
         <v>19</v>
       </c>
       <c r="F7" s="36" t="n">
         <f aca="false">F3-F4-F6</f>
-        <v>69.9999999999998</v>
+        <v>-129.7</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/arquivos extras/Planilha.xlsx
+++ b/arquivos extras/Planilha.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Jan" sheetId="1" state="visible" r:id="rId3"/>
@@ -70,15 +70,15 @@
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>10</xdr:col>
-                <xdr:colOff>109</xdr:colOff>
+                <xdr:colOff>145</xdr:colOff>
                 <xdr:row>9</xdr:row>
-                <xdr:rowOff>9</xdr:rowOff>
+                <xdr:rowOff>12</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>-18</xdr:colOff>
+                <xdr:colOff>-24</xdr:colOff>
                 <xdr:row>13</xdr:row>
-                <xdr:rowOff>15</xdr:rowOff>
+                <xdr:rowOff>20</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -91,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1653" uniqueCount="266">
   <si>
     <t xml:space="preserve">JAN</t>
   </si>
@@ -675,10 +675,22 @@
     <t xml:space="preserve">JUL</t>
   </si>
   <si>
+    <t xml:space="preserve">Jogos / Games / Aplicativos pagos</t>
+  </si>
+  <si>
     <t xml:space="preserve">cartao</t>
   </si>
   <si>
-    <t xml:space="preserve">\</t>
+    <t xml:space="preserve">bugao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sitio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">moletom e camisa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">espetinho</t>
   </si>
   <si>
     <t xml:space="preserve">AGO</t>
@@ -862,9 +874,6 @@
   </si>
   <si>
     <t xml:space="preserve">saldo do mês anterior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jogos / Games / Aplicativos pagos</t>
   </si>
   <si>
     <t xml:space="preserve">Acessórios </t>
@@ -886,12 +895,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="_-&quot;R$ &quot;* #,##0.00_-;&quot;-R$ &quot;* #,##0.00_-;_-&quot;R$ &quot;* \-??_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="d/m/yyyy"/>
     <numFmt numFmtId="167" formatCode="[$-F800]dddd&quot;, &quot;mmmm\ dd&quot;, &quot;yyyy"/>
     <numFmt numFmtId="168" formatCode="d/mmm"/>
+    <numFmt numFmtId="169" formatCode="[$R$-416]\ #,##0.00;[RED]\-[$R$-416]\ #,##0.00"/>
   </numFmts>
   <fonts count="17">
     <font>
@@ -1518,7 +1528,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="179">
+  <cellXfs count="180">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1887,12 +1897,16 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="27" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="169" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="27" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -2356,10 +2370,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.0673813169984686"/>
-          <c:y val="0.102148919520857"/>
-          <c:w val="0.748253837821686"/>
-          <c:h val="0.815626316739903"/>
+          <c:x val="0.0673863509020956"/>
+          <c:y val="0.102161218469689"/>
+          <c:w val="0.74823503044339"/>
+          <c:h val="0.815483715610138"/>
         </c:manualLayout>
       </c:layout>
       <c:pie3DChart>
@@ -3002,7 +3016,7 @@
                 <c:formatCode>_-"R$ "* #,##0.00_-;"-R$ "* #,##0.00_-;_-"R$ "* \-??_-;_-@_-</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>30</c:v>
+                  <c:v>60</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>380.9</c:v>
@@ -3017,13 +3031,13 @@
                   <c:v>468.64</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>710</c:v>
+                  <c:v>970</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1889.68</c:v>
+                  <c:v>2902.36</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -3343,9 +3357,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>46800</xdr:colOff>
+      <xdr:colOff>46080</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>21600</xdr:rowOff>
+      <xdr:rowOff>20880</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3354,7 +3368,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
-        <a:ext cx="9637920" cy="5980320"/>
+        <a:ext cx="9637200" cy="5979600"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3632,7 +3646,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46209</v>
+        <v>46221</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -4799,7 +4813,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -4827,7 +4841,7 @@
       </c>
       <c r="F3" s="11" t="n">
         <f aca="false">SUM(D3,D5,D6,D7,D4)</f>
-        <v>-129.7</v>
+        <v>996.740000000001</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>6</v>
@@ -4855,7 +4869,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46209</v>
+        <v>46221</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -4914,14 +4928,14 @@
       <c r="C7" s="33"/>
       <c r="D7" s="34" t="n">
         <f aca="false">Set!F7</f>
-        <v>-129.7</v>
+        <v>996.740000000001</v>
       </c>
       <c r="E7" s="35" t="s">
         <v>19</v>
       </c>
       <c r="F7" s="36" t="n">
         <f aca="false">F3-F4-F6</f>
-        <v>-129.7</v>
+        <v>996.740000000001</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4986,8 +5000,8 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="47"/>
-      <c r="C11" s="92"/>
-      <c r="D11" s="92"/>
+      <c r="C11" s="94"/>
+      <c r="D11" s="94"/>
       <c r="E11" s="48"/>
       <c r="F11" s="49"/>
       <c r="H11" s="50"/>
@@ -5871,7 +5885,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -5899,7 +5913,7 @@
       </c>
       <c r="F3" s="11" t="n">
         <f aca="false">SUM(D3,D5,D6,D7,D4)</f>
-        <v>-129.7</v>
+        <v>996.740000000001</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>6</v>
@@ -5927,7 +5941,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46209</v>
+        <v>46221</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -5986,14 +6000,14 @@
       <c r="C7" s="33"/>
       <c r="D7" s="34" t="n">
         <f aca="false">Out!F7</f>
-        <v>-129.7</v>
+        <v>996.740000000001</v>
       </c>
       <c r="E7" s="35" t="s">
         <v>19</v>
       </c>
       <c r="F7" s="36" t="n">
         <f aca="false">F3-F4-F6</f>
-        <v>-129.7</v>
+        <v>996.740000000001</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6058,8 +6072,8 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="47"/>
-      <c r="C11" s="92"/>
-      <c r="D11" s="92"/>
+      <c r="C11" s="94"/>
+      <c r="D11" s="94"/>
       <c r="E11" s="48"/>
       <c r="F11" s="49"/>
       <c r="H11" s="50"/>
@@ -6939,14 +6953,14 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="34.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="8.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="94" width="10.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="95" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="15.85"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -6974,7 +6988,7 @@
       </c>
       <c r="F3" s="11" t="n">
         <f aca="false">SUM(D3,D5,D6,D7,D4)</f>
-        <v>-129.7</v>
+        <v>996.740000000001</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>6</v>
@@ -7002,7 +7016,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46209</v>
+        <v>46221</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -7061,14 +7075,14 @@
       <c r="C7" s="33"/>
       <c r="D7" s="34" t="n">
         <f aca="false">Nov!F7</f>
-        <v>-129.7</v>
+        <v>996.740000000001</v>
       </c>
       <c r="E7" s="35" t="s">
         <v>19</v>
       </c>
       <c r="F7" s="36" t="n">
         <f aca="false">F3-F4-F6</f>
-        <v>-129.7</v>
+        <v>996.740000000001</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7127,14 +7141,14 @@
         <v>2</v>
       </c>
       <c r="M10" s="43"/>
-      <c r="N10" s="95"/>
+      <c r="N10" s="96"/>
       <c r="O10" s="45"/>
       <c r="P10" s="46"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="47"/>
-      <c r="C11" s="92"/>
-      <c r="D11" s="92"/>
+      <c r="C11" s="94"/>
+      <c r="D11" s="94"/>
       <c r="E11" s="48"/>
       <c r="F11" s="49"/>
       <c r="H11" s="50"/>
@@ -7142,7 +7156,7 @@
       <c r="J11" s="51"/>
       <c r="K11" s="46"/>
       <c r="M11" s="52"/>
-      <c r="N11" s="96"/>
+      <c r="N11" s="97"/>
       <c r="O11" s="54"/>
       <c r="P11" s="55"/>
     </row>
@@ -7157,7 +7171,7 @@
       <c r="J12" s="60"/>
       <c r="K12" s="55"/>
       <c r="M12" s="52"/>
-      <c r="N12" s="96"/>
+      <c r="N12" s="97"/>
       <c r="O12" s="54"/>
       <c r="P12" s="55"/>
     </row>
@@ -7172,7 +7186,7 @@
       <c r="J13" s="60"/>
       <c r="K13" s="55"/>
       <c r="M13" s="52"/>
-      <c r="N13" s="96"/>
+      <c r="N13" s="97"/>
       <c r="O13" s="54"/>
       <c r="P13" s="55"/>
     </row>
@@ -7187,7 +7201,7 @@
       <c r="J14" s="60"/>
       <c r="K14" s="55"/>
       <c r="M14" s="52"/>
-      <c r="N14" s="96"/>
+      <c r="N14" s="97"/>
       <c r="O14" s="54"/>
       <c r="P14" s="55"/>
     </row>
@@ -7202,7 +7216,7 @@
       <c r="J15" s="60"/>
       <c r="K15" s="55"/>
       <c r="M15" s="52"/>
-      <c r="N15" s="96"/>
+      <c r="N15" s="97"/>
       <c r="O15" s="54"/>
       <c r="P15" s="55"/>
     </row>
@@ -7217,7 +7231,7 @@
       <c r="J16" s="60"/>
       <c r="K16" s="55"/>
       <c r="M16" s="52"/>
-      <c r="N16" s="96"/>
+      <c r="N16" s="97"/>
       <c r="O16" s="54"/>
       <c r="P16" s="55"/>
     </row>
@@ -7232,7 +7246,7 @@
       <c r="J17" s="60"/>
       <c r="K17" s="55"/>
       <c r="M17" s="52"/>
-      <c r="N17" s="96"/>
+      <c r="N17" s="97"/>
       <c r="O17" s="54"/>
       <c r="P17" s="55"/>
     </row>
@@ -7247,7 +7261,7 @@
       <c r="J18" s="60"/>
       <c r="K18" s="55"/>
       <c r="M18" s="52"/>
-      <c r="N18" s="96"/>
+      <c r="N18" s="97"/>
       <c r="O18" s="54"/>
       <c r="P18" s="55"/>
     </row>
@@ -7262,7 +7276,7 @@
       <c r="J19" s="60"/>
       <c r="K19" s="55"/>
       <c r="M19" s="52"/>
-      <c r="N19" s="96"/>
+      <c r="N19" s="97"/>
       <c r="O19" s="54"/>
       <c r="P19" s="55"/>
     </row>
@@ -7277,7 +7291,7 @@
       <c r="J20" s="60"/>
       <c r="K20" s="55"/>
       <c r="M20" s="52"/>
-      <c r="N20" s="96"/>
+      <c r="N20" s="97"/>
       <c r="O20" s="54"/>
       <c r="P20" s="55"/>
     </row>
@@ -7292,7 +7306,7 @@
       <c r="J21" s="60"/>
       <c r="K21" s="55"/>
       <c r="M21" s="52"/>
-      <c r="N21" s="96"/>
+      <c r="N21" s="97"/>
       <c r="O21" s="54"/>
       <c r="P21" s="55"/>
     </row>
@@ -7307,7 +7321,7 @@
       <c r="J22" s="62"/>
       <c r="K22" s="63"/>
       <c r="M22" s="52"/>
-      <c r="N22" s="96"/>
+      <c r="N22" s="97"/>
       <c r="O22" s="54"/>
       <c r="P22" s="55"/>
     </row>
@@ -7322,7 +7336,7 @@
         <v>0</v>
       </c>
       <c r="M23" s="52"/>
-      <c r="N23" s="96"/>
+      <c r="N23" s="97"/>
       <c r="O23" s="54"/>
       <c r="P23" s="55"/>
     </row>
@@ -7333,7 +7347,7 @@
       <c r="E24" s="16"/>
       <c r="F24" s="58"/>
       <c r="M24" s="52"/>
-      <c r="N24" s="96"/>
+      <c r="N24" s="97"/>
       <c r="O24" s="54"/>
       <c r="P24" s="55"/>
     </row>
@@ -7344,7 +7358,7 @@
       <c r="E25" s="16"/>
       <c r="F25" s="58"/>
       <c r="M25" s="64"/>
-      <c r="N25" s="97"/>
+      <c r="N25" s="98"/>
       <c r="O25" s="66"/>
       <c r="P25" s="63"/>
     </row>
@@ -8003,18 +8017,18 @@
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="98" width="21.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="99" width="15.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="99" width="14.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="99" width="19.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="99" width="14.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="99" width="14.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="99" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="99" width="17.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="99" width="14.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="99" width="20.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="99" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="99" width="14.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="99" width="21.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="100" width="15.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="100" width="14.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="100" width="19.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="100" width="14.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="100" width="14.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="100" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="100" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="100" width="14.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="100" width="20.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="100" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="100" width="14.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="15.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="19.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="13.15"/>
@@ -8022,1006 +8036,1006 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="100" t="s">
-        <v>202</v>
-      </c>
-      <c r="C2" s="101" t="s">
-        <v>203</v>
-      </c>
-      <c r="D2" s="102" t="s">
+      <c r="B2" s="101" t="s">
+        <v>206</v>
+      </c>
+      <c r="C2" s="102" t="s">
+        <v>207</v>
+      </c>
+      <c r="D2" s="103" t="s">
         <v>106</v>
       </c>
-      <c r="E2" s="102" t="s">
-        <v>204</v>
-      </c>
-      <c r="F2" s="102" t="s">
-        <v>205</v>
-      </c>
-      <c r="G2" s="102" t="s">
-        <v>206</v>
-      </c>
-      <c r="H2" s="102" t="s">
-        <v>207</v>
-      </c>
-      <c r="I2" s="102" t="s">
+      <c r="E2" s="103" t="s">
         <v>208</v>
       </c>
-      <c r="J2" s="102" t="s">
+      <c r="F2" s="103" t="s">
         <v>209</v>
       </c>
-      <c r="K2" s="102" t="s">
+      <c r="G2" s="103" t="s">
         <v>210</v>
       </c>
-      <c r="L2" s="102" t="s">
+      <c r="H2" s="103" t="s">
         <v>211</v>
       </c>
-      <c r="M2" s="102" t="s">
+      <c r="I2" s="103" t="s">
         <v>212</v>
       </c>
-      <c r="N2" s="103" t="s">
+      <c r="J2" s="103" t="s">
         <v>213</v>
       </c>
-      <c r="O2" s="103" t="s">
+      <c r="K2" s="103" t="s">
         <v>214</v>
       </c>
+      <c r="L2" s="103" t="s">
+        <v>215</v>
+      </c>
+      <c r="M2" s="103" t="s">
+        <v>216</v>
+      </c>
+      <c r="N2" s="104" t="s">
+        <v>217</v>
+      </c>
+      <c r="O2" s="104" t="s">
+        <v>218</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="104" t="s">
+      <c r="B3" s="105" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="105" t="n">
+      <c r="C3" s="106" t="n">
         <f aca="false">Jan!$F$3</f>
         <v>2246.57</v>
       </c>
-      <c r="D3" s="106" t="n">
+      <c r="D3" s="107" t="n">
         <f aca="false">Fev!$F$3</f>
         <v>2281.55</v>
       </c>
-      <c r="E3" s="106" t="n">
+      <c r="E3" s="107" t="n">
         <f aca="false">Mar!$F$3</f>
         <v>2080.77</v>
       </c>
-      <c r="F3" s="106" t="n">
+      <c r="F3" s="107" t="n">
         <f aca="false">Abr!$F$3</f>
         <v>2679.04</v>
       </c>
-      <c r="G3" s="106" t="n">
+      <c r="G3" s="107" t="n">
         <f aca="false">Mai!$F$3</f>
         <v>4523.74</v>
       </c>
-      <c r="H3" s="106" t="n">
+      <c r="H3" s="107" t="n">
         <f aca="false">Jun!$F$3</f>
-        <v>2091.7</v>
-      </c>
-      <c r="I3" s="106" t="n">
+        <v>2309.7</v>
+      </c>
+      <c r="I3" s="107" t="n">
         <f aca="false">Jul!$F$3</f>
-        <v>69.9999999999998</v>
-      </c>
-      <c r="J3" s="106" t="n">
+        <v>3135</v>
+      </c>
+      <c r="J3" s="107" t="n">
         <f aca="false">Ago!$F$3</f>
-        <v>-129.7</v>
-      </c>
-      <c r="K3" s="106" t="n">
+        <v>996.740000000001</v>
+      </c>
+      <c r="K3" s="107" t="n">
         <f aca="false">Set!$F$3</f>
-        <v>-129.7</v>
-      </c>
-      <c r="L3" s="106" t="n">
+        <v>996.740000000001</v>
+      </c>
+      <c r="L3" s="107" t="n">
         <f aca="false">Out!$F$3</f>
-        <v>-129.7</v>
-      </c>
-      <c r="M3" s="106" t="n">
+        <v>996.740000000001</v>
+      </c>
+      <c r="M3" s="107" t="n">
         <f aca="false">Nov!$F$3</f>
-        <v>-129.7</v>
-      </c>
-      <c r="N3" s="107" t="n">
+        <v>996.740000000001</v>
+      </c>
+      <c r="N3" s="108" t="n">
         <f aca="false">Dez!$F$3</f>
-        <v>-129.7</v>
-      </c>
-      <c r="O3" s="107" t="n">
+        <v>996.740000000001</v>
+      </c>
+      <c r="O3" s="108" t="n">
         <f aca="false">SUM(C3:N3)</f>
-        <v>15324.87</v>
+        <v>24240.07</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="108" t="s">
-        <v>215</v>
-      </c>
-      <c r="C4" s="109" t="n">
+      <c r="B4" s="109" t="s">
+        <v>219</v>
+      </c>
+      <c r="C4" s="110" t="n">
         <f aca="false">Jan!$F$4</f>
         <v>568.02</v>
       </c>
-      <c r="D4" s="109" t="n">
+      <c r="D4" s="110" t="n">
         <f aca="false">Fev!$F$4</f>
         <v>561.58</v>
       </c>
-      <c r="E4" s="109" t="n">
+      <c r="E4" s="110" t="n">
         <f aca="false">Mar!$F$4</f>
         <v>1203.63</v>
       </c>
-      <c r="F4" s="109" t="n">
+      <c r="F4" s="110" t="n">
         <f aca="false">Abr!$F$4</f>
         <v>723.11</v>
       </c>
-      <c r="G4" s="109" t="n">
+      <c r="G4" s="110" t="n">
         <f aca="false">Mai!$F$4</f>
         <v>3935.01</v>
       </c>
-      <c r="H4" s="109" t="n">
+      <c r="H4" s="110" t="n">
         <f aca="false">Jun!$F$4</f>
         <v>630</v>
       </c>
-      <c r="I4" s="109" t="n">
+      <c r="I4" s="110" t="n">
         <f aca="false">Jul!$F$4</f>
-        <v>179.7</v>
-      </c>
-      <c r="J4" s="109" t="n">
+        <v>780.58</v>
+      </c>
+      <c r="J4" s="110" t="n">
         <f aca="false">Ago!$F$4</f>
         <v>0</v>
       </c>
-      <c r="K4" s="109" t="n">
+      <c r="K4" s="110" t="n">
         <f aca="false">Set!$F$4</f>
         <v>0</v>
       </c>
-      <c r="L4" s="109" t="n">
+      <c r="L4" s="110" t="n">
         <f aca="false">Out!$F$4</f>
         <v>0</v>
       </c>
-      <c r="M4" s="109" t="n">
+      <c r="M4" s="110" t="n">
         <f aca="false">Nov!$F$4</f>
         <v>0</v>
       </c>
-      <c r="N4" s="110" t="n">
+      <c r="N4" s="111" t="n">
         <f aca="false">Dez!$F$4</f>
         <v>0</v>
       </c>
-      <c r="O4" s="110" t="n">
+      <c r="O4" s="111" t="n">
         <f aca="false">SUM(C4:N4)</f>
-        <v>7801.05</v>
+        <v>8401.93</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="108" t="s">
-        <v>216</v>
-      </c>
-      <c r="C5" s="111" t="n">
+      <c r="B5" s="109" t="s">
+        <v>220</v>
+      </c>
+      <c r="C5" s="112" t="n">
         <f aca="false">Jan!$F$6</f>
         <v>337</v>
       </c>
-      <c r="D5" s="111" t="n">
+      <c r="D5" s="112" t="n">
         <f aca="false">Fev!$F$6</f>
         <v>362.2</v>
       </c>
-      <c r="E5" s="111" t="n">
+      <c r="E5" s="112" t="n">
         <f aca="false">Mar!$F$6</f>
         <v>434.6</v>
       </c>
-      <c r="F5" s="111" t="n">
+      <c r="F5" s="112" t="n">
         <f aca="false">Abr!$F$6</f>
         <v>516.69</v>
       </c>
-      <c r="G5" s="111" t="n">
+      <c r="G5" s="112" t="n">
         <f aca="false">Mai!$F$6</f>
         <v>597.03</v>
       </c>
-      <c r="H5" s="111" t="n">
+      <c r="H5" s="112" t="n">
         <f aca="false">Jun!$F$6</f>
         <v>1391.7</v>
       </c>
-      <c r="I5" s="111" t="n">
+      <c r="I5" s="112" t="n">
         <f aca="false">Jul!$F$6</f>
-        <v>20</v>
-      </c>
-      <c r="J5" s="111" t="n">
+        <v>1357.68</v>
+      </c>
+      <c r="J5" s="112" t="n">
         <f aca="false">Ago!$F$6</f>
         <v>0</v>
       </c>
-      <c r="K5" s="111" t="n">
+      <c r="K5" s="112" t="n">
         <f aca="false">Set!$F$6</f>
         <v>0</v>
       </c>
-      <c r="L5" s="111" t="n">
+      <c r="L5" s="112" t="n">
         <f aca="false">Out!$F$6</f>
         <v>0</v>
       </c>
-      <c r="M5" s="111" t="n">
+      <c r="M5" s="112" t="n">
         <f aca="false">Nov!$F$6</f>
         <v>0</v>
       </c>
-      <c r="N5" s="112" t="n">
+      <c r="N5" s="113" t="n">
         <f aca="false">Dez!$F$6</f>
         <v>0</v>
       </c>
-      <c r="O5" s="112" t="n">
+      <c r="O5" s="113" t="n">
         <f aca="false">SUM(C5:N5)</f>
-        <v>3659.22</v>
+        <v>4996.9</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="108" t="s">
+      <c r="B6" s="109" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="113" t="n">
+      <c r="C6" s="114" t="n">
         <f aca="false">Jan!$L$3</f>
         <v>0</v>
       </c>
-      <c r="D6" s="113" t="n">
+      <c r="D6" s="114" t="n">
         <f aca="false">Fev!$L$3</f>
         <v>0</v>
       </c>
-      <c r="E6" s="113" t="n">
+      <c r="E6" s="114" t="n">
         <f aca="false">Mar!$L$3</f>
         <v>0</v>
       </c>
-      <c r="F6" s="113" t="n">
+      <c r="F6" s="114" t="n">
         <f aca="false">Abr!$L$3</f>
         <v>1343</v>
       </c>
-      <c r="G6" s="113" t="n">
+      <c r="G6" s="114" t="n">
         <f aca="false">Mai!$L$3</f>
         <v>2503</v>
       </c>
-      <c r="H6" s="113" t="n">
+      <c r="H6" s="114" t="n">
         <f aca="false">Jun!$L$3</f>
         <v>200</v>
       </c>
-      <c r="I6" s="113" t="n">
+      <c r="I6" s="114" t="n">
         <f aca="false">Jul!$L$3</f>
-        <v>0</v>
-      </c>
-      <c r="J6" s="113" t="n">
+        <v>809.19</v>
+      </c>
+      <c r="J6" s="114" t="n">
         <f aca="false">Ago!$L$3</f>
         <v>0</v>
       </c>
-      <c r="K6" s="113" t="n">
+      <c r="K6" s="114" t="n">
         <f aca="false">Set!$L$3</f>
         <v>0</v>
       </c>
-      <c r="L6" s="113" t="n">
+      <c r="L6" s="114" t="n">
         <f aca="false">Out!$L$3</f>
         <v>0</v>
       </c>
-      <c r="M6" s="113" t="n">
+      <c r="M6" s="114" t="n">
         <f aca="false">Nov!$L$3</f>
         <v>0</v>
       </c>
-      <c r="N6" s="114" t="n">
+      <c r="N6" s="115" t="n">
         <f aca="false">Dez!$L$3</f>
         <v>0</v>
       </c>
-      <c r="O6" s="115" t="n">
+      <c r="O6" s="116" t="n">
         <f aca="false">SUM(C6:N6)</f>
-        <v>4046</v>
+        <v>4855.19</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="108" t="s">
-        <v>217</v>
-      </c>
-      <c r="C7" s="116" t="n">
+      <c r="B7" s="109" t="s">
+        <v>221</v>
+      </c>
+      <c r="C7" s="117" t="n">
         <f aca="false">Jan!$L$4</f>
         <v>0</v>
       </c>
-      <c r="D7" s="116" t="n">
+      <c r="D7" s="117" t="n">
         <f aca="false">Fev!$L$4</f>
         <v>0</v>
       </c>
-      <c r="E7" s="116" t="n">
+      <c r="E7" s="117" t="n">
         <f aca="false">Mar!$L$4</f>
         <v>0</v>
       </c>
-      <c r="F7" s="116" t="n">
+      <c r="F7" s="117" t="n">
         <f aca="false">Abr!$L$4</f>
         <v>983.93</v>
       </c>
-      <c r="G7" s="116" t="n">
+      <c r="G7" s="117" t="n">
         <f aca="false">Mai!$L$4</f>
         <v>0</v>
       </c>
-      <c r="H7" s="116" t="n">
+      <c r="H7" s="117" t="n">
         <f aca="false">Jun!$L$4</f>
         <v>0</v>
       </c>
-      <c r="I7" s="116" t="n">
+      <c r="I7" s="117" t="n">
         <f aca="false">Jul!$L$4</f>
         <v>0</v>
       </c>
-      <c r="J7" s="116" t="n">
+      <c r="J7" s="117" t="n">
         <f aca="false">Ago!$L$4</f>
         <v>0</v>
       </c>
-      <c r="K7" s="116" t="n">
+      <c r="K7" s="117" t="n">
         <f aca="false">Set!$L$4</f>
         <v>0</v>
       </c>
-      <c r="L7" s="116" t="n">
+      <c r="L7" s="117" t="n">
         <f aca="false">Out!$L$4</f>
         <v>0</v>
       </c>
-      <c r="M7" s="116" t="n">
+      <c r="M7" s="117" t="n">
         <f aca="false">Nov!$L$4</f>
         <v>0</v>
       </c>
-      <c r="N7" s="117" t="n">
+      <c r="N7" s="118" t="n">
         <f aca="false">Dez!$L$4</f>
         <v>0</v>
       </c>
-      <c r="O7" s="118" t="n">
+      <c r="O7" s="119" t="n">
         <f aca="false">SUM(C7:N7)</f>
         <v>983.93</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="108" t="s">
-        <v>218</v>
-      </c>
-      <c r="C8" s="119" t="n">
+      <c r="B8" s="109" t="s">
+        <v>222</v>
+      </c>
+      <c r="C8" s="120" t="n">
         <f aca="false">C4+C5</f>
         <v>905.02</v>
       </c>
-      <c r="D8" s="119" t="n">
+      <c r="D8" s="120" t="n">
         <f aca="false">D4+D5</f>
         <v>923.78</v>
       </c>
-      <c r="E8" s="119" t="n">
+      <c r="E8" s="120" t="n">
         <f aca="false">E4+E5</f>
         <v>1638.23</v>
       </c>
-      <c r="F8" s="119" t="n">
+      <c r="F8" s="120" t="n">
         <f aca="false">F4+F5</f>
         <v>1239.8</v>
       </c>
-      <c r="G8" s="119" t="n">
+      <c r="G8" s="120" t="n">
         <f aca="false">G4+G5</f>
         <v>4532.04</v>
       </c>
-      <c r="H8" s="119" t="n">
+      <c r="H8" s="120" t="n">
         <f aca="false">H4+H5</f>
         <v>2021.7</v>
       </c>
-      <c r="I8" s="119" t="n">
+      <c r="I8" s="120" t="n">
         <f aca="false">I4+I5</f>
-        <v>199.7</v>
-      </c>
-      <c r="J8" s="119" t="n">
+        <v>2138.26</v>
+      </c>
+      <c r="J8" s="120" t="n">
         <f aca="false">J4+J5</f>
         <v>0</v>
       </c>
-      <c r="K8" s="119" t="n">
+      <c r="K8" s="120" t="n">
         <f aca="false">K4+K5</f>
         <v>0</v>
       </c>
-      <c r="L8" s="119" t="n">
+      <c r="L8" s="120" t="n">
         <f aca="false">L4+L5</f>
         <v>0</v>
       </c>
-      <c r="M8" s="119" t="n">
+      <c r="M8" s="120" t="n">
         <f aca="false">M4+M5</f>
         <v>0</v>
       </c>
-      <c r="N8" s="120" t="n">
+      <c r="N8" s="121" t="n">
         <f aca="false">N4+N5</f>
         <v>0</v>
       </c>
-      <c r="O8" s="120" t="n">
+      <c r="O8" s="121" t="n">
         <f aca="false">SUM(C8:N8)</f>
-        <v>11460.27</v>
+        <v>13398.83</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="108" t="s">
+      <c r="B9" s="109" t="s">
         <v>107</v>
       </c>
-      <c r="C9" s="121" t="n">
+      <c r="C9" s="122" t="n">
         <f aca="false">C3-C8</f>
         <v>1341.55</v>
       </c>
-      <c r="D9" s="121" t="n">
+      <c r="D9" s="122" t="n">
         <f aca="false">D3-D8</f>
         <v>1357.77</v>
       </c>
-      <c r="E9" s="121" t="n">
+      <c r="E9" s="122" t="n">
         <f aca="false">E3-E8</f>
         <v>442.54</v>
       </c>
-      <c r="F9" s="121" t="n">
+      <c r="F9" s="122" t="n">
         <f aca="false">F3-F8</f>
         <v>1439.24</v>
       </c>
-      <c r="G9" s="121" t="n">
+      <c r="G9" s="122" t="n">
         <f aca="false">G3-G8</f>
         <v>-8.29999999999927</v>
       </c>
-      <c r="H9" s="121" t="n">
+      <c r="H9" s="122" t="n">
         <f aca="false">H3-H8</f>
-        <v>69.9999999999998</v>
-      </c>
-      <c r="I9" s="121" t="n">
+        <v>288.000000000001</v>
+      </c>
+      <c r="I9" s="122" t="n">
         <f aca="false">I3-I8</f>
-        <v>-129.7</v>
-      </c>
-      <c r="J9" s="121" t="n">
+        <v>996.740000000001</v>
+      </c>
+      <c r="J9" s="122" t="n">
         <f aca="false">J3-J8</f>
-        <v>-129.7</v>
-      </c>
-      <c r="K9" s="121" t="n">
+        <v>996.740000000001</v>
+      </c>
+      <c r="K9" s="122" t="n">
         <f aca="false">K3-K8</f>
-        <v>-129.7</v>
-      </c>
-      <c r="L9" s="121" t="n">
+        <v>996.740000000001</v>
+      </c>
+      <c r="L9" s="122" t="n">
         <f aca="false">L3-L8</f>
-        <v>-129.7</v>
-      </c>
-      <c r="M9" s="121" t="n">
+        <v>996.740000000001</v>
+      </c>
+      <c r="M9" s="122" t="n">
         <f aca="false">M3-M8</f>
-        <v>-129.7</v>
-      </c>
-      <c r="N9" s="122" t="n">
+        <v>996.740000000001</v>
+      </c>
+      <c r="N9" s="123" t="n">
         <f aca="false">N3-N8</f>
-        <v>-129.7</v>
-      </c>
-      <c r="O9" s="122" t="n">
+        <v>996.740000000001</v>
+      </c>
+      <c r="O9" s="123" t="n">
         <f aca="false">N9</f>
-        <v>-129.7</v>
+        <v>996.740000000001</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="123" t="s">
+      <c r="B10" s="124" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="124" t="n">
+      <c r="C10" s="125" t="n">
         <f aca="false">Jan!D4</f>
         <v>103.33</v>
       </c>
-      <c r="D10" s="124" t="n">
+      <c r="D10" s="125" t="n">
         <f aca="false">Fev!D4</f>
         <v>200</v>
       </c>
-      <c r="E10" s="124" t="n">
+      <c r="E10" s="125" t="n">
         <f aca="false">Mar!D4</f>
         <v>0</v>
       </c>
-      <c r="F10" s="124" t="n">
+      <c r="F10" s="125" t="n">
         <f aca="false">Abr!D4</f>
         <v>136.5</v>
       </c>
-      <c r="G10" s="124" t="n">
+      <c r="G10" s="125" t="n">
         <f aca="false">Mai!D4</f>
         <v>20</v>
       </c>
-      <c r="H10" s="124" t="n">
+      <c r="H10" s="125" t="n">
         <f aca="false">Jun!D4</f>
         <v>0</v>
       </c>
-      <c r="I10" s="124" t="n">
+      <c r="I10" s="125" t="n">
         <f aca="false">Jul!D4</f>
-        <v>0</v>
-      </c>
-      <c r="J10" s="124" t="n">
+        <v>210</v>
+      </c>
+      <c r="J10" s="125" t="n">
         <f aca="false">Ago!D4</f>
         <v>0</v>
       </c>
-      <c r="K10" s="124" t="n">
+      <c r="K10" s="125" t="n">
         <f aca="false">Set!D4</f>
         <v>0</v>
       </c>
-      <c r="L10" s="124" t="n">
+      <c r="L10" s="125" t="n">
         <f aca="false">Out!D4</f>
         <v>0</v>
       </c>
-      <c r="M10" s="124" t="n">
+      <c r="M10" s="125" t="n">
         <f aca="false">Nov!D4</f>
         <v>0</v>
       </c>
-      <c r="N10" s="125" t="n">
+      <c r="N10" s="126" t="n">
         <f aca="false">Dez!D4</f>
         <v>0</v>
       </c>
-      <c r="O10" s="125" t="n">
+      <c r="O10" s="126" t="n">
         <f aca="false">SUM(C10:N10)</f>
-        <v>459.83</v>
+        <v>669.83</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="13" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="L13" s="99" t="n">
+      <c r="L13" s="100" t="n">
         <f aca="false">12*25.82</f>
         <v>309.84</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="100" t="s">
-        <v>202</v>
-      </c>
-      <c r="C15" s="101" t="s">
-        <v>203</v>
-      </c>
-      <c r="D15" s="102" t="s">
+      <c r="B15" s="101" t="s">
+        <v>206</v>
+      </c>
+      <c r="C15" s="102" t="s">
+        <v>207</v>
+      </c>
+      <c r="D15" s="103" t="s">
         <v>106</v>
       </c>
-      <c r="E15" s="102" t="s">
-        <v>204</v>
-      </c>
-      <c r="F15" s="102" t="s">
-        <v>205</v>
-      </c>
-      <c r="G15" s="102" t="s">
-        <v>206</v>
-      </c>
-      <c r="H15" s="102" t="s">
-        <v>207</v>
-      </c>
-      <c r="I15" s="102" t="s">
+      <c r="E15" s="103" t="s">
         <v>208</v>
       </c>
-      <c r="J15" s="102" t="s">
+      <c r="F15" s="103" t="s">
         <v>209</v>
       </c>
-      <c r="K15" s="102" t="s">
+      <c r="G15" s="103" t="s">
         <v>210</v>
       </c>
-      <c r="L15" s="102" t="s">
+      <c r="H15" s="103" t="s">
         <v>211</v>
       </c>
-      <c r="M15" s="102" t="s">
+      <c r="I15" s="103" t="s">
         <v>212</v>
       </c>
-      <c r="N15" s="103" t="s">
+      <c r="J15" s="103" t="s">
         <v>213</v>
       </c>
-      <c r="O15" s="103" t="s">
-        <v>219</v>
+      <c r="K15" s="103" t="s">
+        <v>214</v>
+      </c>
+      <c r="L15" s="103" t="s">
+        <v>215</v>
+      </c>
+      <c r="M15" s="103" t="s">
+        <v>216</v>
+      </c>
+      <c r="N15" s="104" t="s">
+        <v>217</v>
+      </c>
+      <c r="O15" s="104" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="126" t="s">
+      <c r="B16" s="127" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="127" t="n">
+      <c r="C16" s="128" t="n">
         <f aca="false">Jan!$B$36</f>
         <v>0</v>
       </c>
-      <c r="D16" s="128" t="n">
+      <c r="D16" s="129" t="n">
         <f aca="false">Fev!$B$36</f>
         <v>0</v>
       </c>
-      <c r="E16" s="127" t="n">
+      <c r="E16" s="128" t="n">
         <f aca="false">Mar!$B$36</f>
         <v>12</v>
       </c>
-      <c r="F16" s="128" t="n">
+      <c r="F16" s="129" t="n">
         <f aca="false">Abr!$B$36</f>
         <v>79.46</v>
       </c>
-      <c r="G16" s="127" t="n">
+      <c r="G16" s="128" t="n">
         <f aca="false">Mai!$B$36</f>
         <v>0</v>
       </c>
-      <c r="H16" s="128" t="n">
+      <c r="H16" s="129" t="n">
         <f aca="false">Jun!$B$36</f>
         <v>0</v>
       </c>
-      <c r="I16" s="127" t="n">
+      <c r="I16" s="128" t="n">
         <f aca="false">Jul!$B$36</f>
-        <v>0</v>
-      </c>
-      <c r="J16" s="128" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="J16" s="129" t="n">
         <f aca="false">Ago!$B$36</f>
         <v>0</v>
       </c>
-      <c r="K16" s="127" t="n">
+      <c r="K16" s="128" t="n">
         <f aca="false">Set!$B$36</f>
         <v>0</v>
       </c>
-      <c r="L16" s="128" t="n">
+      <c r="L16" s="129" t="n">
         <f aca="false">Out!$B$36</f>
         <v>0</v>
       </c>
-      <c r="M16" s="127" t="n">
+      <c r="M16" s="128" t="n">
         <f aca="false">Nov!$B$36</f>
         <v>0</v>
       </c>
-      <c r="N16" s="129" t="n">
+      <c r="N16" s="130" t="n">
         <f aca="false">Dez!$B$36</f>
         <v>0</v>
       </c>
-      <c r="O16" s="130" t="n">
+      <c r="O16" s="131" t="n">
         <f aca="false">SUM(C16:N16)</f>
-        <v>91.46</v>
+        <v>154.66</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="131" t="s">
+      <c r="B17" s="132" t="s">
         <v>50</v>
       </c>
-      <c r="C17" s="132" t="n">
+      <c r="C17" s="133" t="n">
         <f aca="false">Jan!$B$42</f>
         <v>23.69</v>
       </c>
-      <c r="D17" s="133" t="n">
+      <c r="D17" s="134" t="n">
         <f aca="false">Fev!$B$42</f>
         <v>39</v>
       </c>
-      <c r="E17" s="132" t="n">
+      <c r="E17" s="133" t="n">
         <f aca="false">Mar!$B$42</f>
         <v>47.88</v>
       </c>
-      <c r="F17" s="133" t="n">
+      <c r="F17" s="134" t="n">
         <f aca="false">Abr!$B$42</f>
         <v>190.31</v>
       </c>
-      <c r="G17" s="132" t="n">
+      <c r="G17" s="133" t="n">
         <f aca="false">Mai!$B$42</f>
         <v>69.7</v>
       </c>
-      <c r="H17" s="133" t="n">
+      <c r="H17" s="134" t="n">
         <f aca="false">Jun!$B$42</f>
         <v>42</v>
       </c>
-      <c r="I17" s="132" t="n">
+      <c r="I17" s="133" t="n">
         <f aca="false">Jul!$B$42</f>
-        <v>0</v>
-      </c>
-      <c r="J17" s="133" t="n">
+        <v>119</v>
+      </c>
+      <c r="J17" s="134" t="n">
         <f aca="false">Ago!$B$42</f>
         <v>0</v>
       </c>
-      <c r="K17" s="132" t="n">
+      <c r="K17" s="133" t="n">
         <f aca="false">Set!$B$42</f>
         <v>0</v>
       </c>
-      <c r="L17" s="133" t="n">
+      <c r="L17" s="134" t="n">
         <f aca="false">Out!$B$42</f>
         <v>0</v>
       </c>
-      <c r="M17" s="132" t="n">
+      <c r="M17" s="133" t="n">
         <f aca="false">Nov!$B$42</f>
         <v>0</v>
       </c>
-      <c r="N17" s="134" t="n">
+      <c r="N17" s="135" t="n">
         <f aca="false">Dez!$B$42</f>
         <v>0</v>
       </c>
-      <c r="O17" s="135" t="n">
+      <c r="O17" s="136" t="n">
         <f aca="false">SUM(C17:N17)</f>
-        <v>412.58</v>
+        <v>531.58</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="131" t="s">
+      <c r="B18" s="132" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="132" t="n">
+      <c r="C18" s="133" t="n">
         <f aca="false">Jan!$B$51</f>
         <v>93.95</v>
       </c>
-      <c r="D18" s="133" t="n">
+      <c r="D18" s="134" t="n">
         <f aca="false">Fev!B51</f>
         <v>226.24</v>
       </c>
-      <c r="E18" s="132" t="n">
+      <c r="E18" s="133" t="n">
         <f aca="false">Mar!$B$51</f>
         <v>19.3</v>
       </c>
-      <c r="F18" s="133" t="n">
+      <c r="F18" s="134" t="n">
         <f aca="false">Abr!$B$51</f>
         <v>153.2</v>
       </c>
-      <c r="G18" s="132" t="n">
+      <c r="G18" s="133" t="n">
         <f aca="false">Mai!$B$51</f>
         <v>76.9</v>
       </c>
-      <c r="H18" s="133" t="n">
+      <c r="H18" s="134" t="n">
         <f aca="false">Jun!$B$51</f>
         <v>0</v>
       </c>
-      <c r="I18" s="132" t="n">
+      <c r="I18" s="133" t="n">
         <f aca="false">Jul!$B$51</f>
-        <v>0</v>
-      </c>
-      <c r="J18" s="133" t="n">
+        <v>345.68</v>
+      </c>
+      <c r="J18" s="134" t="n">
         <f aca="false">Ago!$B$51</f>
         <v>0</v>
       </c>
-      <c r="K18" s="132" t="n">
+      <c r="K18" s="133" t="n">
         <f aca="false">Set!$B$51</f>
         <v>0</v>
       </c>
-      <c r="L18" s="133" t="n">
+      <c r="L18" s="134" t="n">
         <f aca="false">Out!$B$51</f>
         <v>0</v>
       </c>
-      <c r="M18" s="132" t="n">
+      <c r="M18" s="133" t="n">
         <f aca="false">Nov!$B$51</f>
         <v>0</v>
       </c>
-      <c r="N18" s="134" t="n">
+      <c r="N18" s="135" t="n">
         <f aca="false">Dez!$B$51</f>
         <v>0</v>
       </c>
-      <c r="O18" s="135" t="n">
+      <c r="O18" s="136" t="n">
         <f aca="false">SUM(C18:N18)</f>
-        <v>569.59</v>
+        <v>915.27</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="131" t="s">
+      <c r="B19" s="132" t="s">
         <v>39</v>
       </c>
-      <c r="C19" s="132" t="n">
+      <c r="C19" s="133" t="n">
         <f aca="false">Jan!$B$59</f>
         <v>72</v>
       </c>
-      <c r="D19" s="133" t="n">
+      <c r="D19" s="134" t="n">
         <f aca="false">Fev!$B$59</f>
         <v>296.34</v>
       </c>
-      <c r="E19" s="132" t="n">
+      <c r="E19" s="133" t="n">
         <f aca="false">Mar!$B$59</f>
         <v>210</v>
       </c>
-      <c r="F19" s="133" t="n">
+      <c r="F19" s="134" t="n">
         <f aca="false">Abr!$B$59</f>
         <v>48.5</v>
       </c>
-      <c r="G19" s="132" t="n">
+      <c r="G19" s="133" t="n">
         <f aca="false">Mai!$B$59</f>
         <v>48</v>
       </c>
-      <c r="H19" s="133" t="n">
+      <c r="H19" s="134" t="n">
         <f aca="false">Jun!$B$59</f>
         <v>0</v>
       </c>
-      <c r="I19" s="132" t="n">
+      <c r="I19" s="133" t="n">
         <f aca="false">Jul!$B$59</f>
-        <v>0</v>
-      </c>
-      <c r="J19" s="133" t="n">
+        <v>73</v>
+      </c>
+      <c r="J19" s="134" t="n">
         <f aca="false">Ago!$B$59</f>
         <v>0</v>
       </c>
-      <c r="K19" s="132" t="n">
+      <c r="K19" s="133" t="n">
         <f aca="false">Set!$B$59</f>
         <v>0</v>
       </c>
-      <c r="L19" s="133" t="n">
+      <c r="L19" s="134" t="n">
         <f aca="false">Out!$B$59</f>
         <v>0</v>
       </c>
-      <c r="M19" s="132" t="n">
+      <c r="M19" s="133" t="n">
         <f aca="false">Nov!$B$59</f>
         <v>0</v>
       </c>
-      <c r="N19" s="134" t="n">
+      <c r="N19" s="135" t="n">
         <f aca="false">Dez!$B$59</f>
         <v>0</v>
       </c>
-      <c r="O19" s="135" t="n">
+      <c r="O19" s="136" t="n">
         <f aca="false">SUM(C19:N19)</f>
-        <v>674.84</v>
+        <v>747.84</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="131" t="s">
+      <c r="B20" s="132" t="s">
         <v>88</v>
       </c>
-      <c r="C20" s="132" t="n">
+      <c r="C20" s="133" t="n">
         <f aca="false">Jan!$B$67</f>
         <v>0</v>
       </c>
-      <c r="D20" s="133" t="n">
+      <c r="D20" s="134" t="n">
         <f aca="false">Fev!$B$67</f>
         <v>0</v>
       </c>
-      <c r="E20" s="132" t="n">
+      <c r="E20" s="133" t="n">
         <f aca="false">Mar!$B$67</f>
         <v>34.45</v>
       </c>
-      <c r="F20" s="133" t="n">
+      <c r="F20" s="134" t="n">
         <f aca="false">Abr!$B$67</f>
         <v>0</v>
       </c>
-      <c r="G20" s="132" t="n">
+      <c r="G20" s="133" t="n">
         <f aca="false">Mai!$B$67</f>
         <v>0</v>
       </c>
-      <c r="H20" s="133" t="n">
+      <c r="H20" s="134" t="n">
         <f aca="false">Jun!$B$67</f>
         <v>0</v>
       </c>
-      <c r="I20" s="132" t="n">
+      <c r="I20" s="133" t="n">
         <f aca="false">Jul!$B$67</f>
         <v>0</v>
       </c>
-      <c r="J20" s="133" t="n">
+      <c r="J20" s="134" t="n">
         <f aca="false">Ago!$B$67</f>
         <v>0</v>
       </c>
-      <c r="K20" s="132" t="n">
+      <c r="K20" s="133" t="n">
         <f aca="false">Set!$B$67</f>
         <v>0</v>
       </c>
-      <c r="L20" s="133" t="n">
+      <c r="L20" s="134" t="n">
         <f aca="false">Out!$B$67</f>
         <v>0</v>
       </c>
-      <c r="M20" s="132" t="n">
+      <c r="M20" s="133" t="n">
         <f aca="false">Nov!$B$67</f>
         <v>0</v>
       </c>
-      <c r="N20" s="134" t="n">
+      <c r="N20" s="135" t="n">
         <f aca="false">Dez!$B$67</f>
         <v>0</v>
       </c>
-      <c r="O20" s="135" t="n">
+      <c r="O20" s="136" t="n">
         <f aca="false">SUM(C20:N20)</f>
         <v>34.45</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="131" t="s">
+      <c r="B21" s="132" t="s">
         <v>77</v>
       </c>
-      <c r="C21" s="132" t="n">
+      <c r="C21" s="133" t="n">
         <f aca="false">Jan!$B$75</f>
         <v>0</v>
       </c>
-      <c r="D21" s="133" t="n">
+      <c r="D21" s="134" t="n">
         <f aca="false">Fev!$B$75</f>
         <v>0</v>
       </c>
-      <c r="E21" s="132" t="n">
+      <c r="E21" s="133" t="n">
         <f aca="false">Mar!$B$75</f>
         <v>0</v>
       </c>
-      <c r="F21" s="133" t="n">
+      <c r="F21" s="134" t="n">
         <f aca="false">Abr!$B$75</f>
         <v>0</v>
       </c>
-      <c r="G21" s="132" t="n">
+      <c r="G21" s="133" t="n">
         <f aca="false">Mai!$B$75</f>
         <v>0</v>
       </c>
-      <c r="H21" s="133" t="n">
+      <c r="H21" s="134" t="n">
         <f aca="false">Jun!$B$75</f>
         <v>0</v>
       </c>
-      <c r="I21" s="132" t="n">
+      <c r="I21" s="133" t="n">
         <f aca="false">Jul!$B$75</f>
         <v>0</v>
       </c>
-      <c r="J21" s="133" t="n">
+      <c r="J21" s="134" t="n">
         <f aca="false">Ago!$B$75</f>
         <v>0</v>
       </c>
-      <c r="K21" s="132" t="n">
+      <c r="K21" s="133" t="n">
         <f aca="false">Set!$B$75</f>
         <v>0</v>
       </c>
-      <c r="L21" s="133" t="n">
+      <c r="L21" s="134" t="n">
         <f aca="false">Out!$B$75</f>
         <v>0</v>
       </c>
-      <c r="M21" s="132" t="n">
+      <c r="M21" s="133" t="n">
         <f aca="false">Nov!$B$75</f>
         <v>0</v>
       </c>
-      <c r="N21" s="134" t="n">
+      <c r="N21" s="135" t="n">
         <f aca="false">Dez!$B$75</f>
         <v>0</v>
       </c>
-      <c r="O21" s="135" t="n">
+      <c r="O21" s="136" t="n">
         <f aca="false">SUM(C21:N21)</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="136" t="s">
+      <c r="B22" s="137" t="s">
         <v>79</v>
       </c>
-      <c r="C22" s="132" t="n">
+      <c r="C22" s="133" t="n">
         <f aca="false">Jan!$D$90</f>
         <v>0</v>
       </c>
-      <c r="D22" s="132" t="n">
+      <c r="D22" s="133" t="n">
         <f aca="false">Fev!$D$90</f>
         <v>0</v>
       </c>
-      <c r="E22" s="132" t="n">
+      <c r="E22" s="133" t="n">
         <f aca="false">Mar!$D$90</f>
         <v>0</v>
       </c>
-      <c r="F22" s="132" t="n">
+      <c r="F22" s="133" t="n">
         <f aca="false">Abr!$D$90</f>
         <v>201.64</v>
       </c>
-      <c r="G22" s="132" t="n">
+      <c r="G22" s="133" t="n">
         <f aca="false">Mai!$D$90</f>
         <v>5548.69</v>
       </c>
-      <c r="H22" s="132" t="n">
+      <c r="H22" s="133" t="n">
         <f aca="false">Jun!$D$90</f>
         <v>350</v>
       </c>
-      <c r="I22" s="132" t="n">
+      <c r="I22" s="133" t="n">
         <f aca="false">Jul!$D$90</f>
         <v>0</v>
       </c>
-      <c r="J22" s="132" t="n">
+      <c r="J22" s="133" t="n">
         <f aca="false">Ago!$D$90</f>
         <v>0</v>
       </c>
-      <c r="K22" s="132" t="n">
+      <c r="K22" s="133" t="n">
         <f aca="false">Set!$D$90</f>
         <v>0</v>
       </c>
-      <c r="L22" s="132" t="n">
+      <c r="L22" s="133" t="n">
         <f aca="false">Out!$D$90</f>
         <v>0</v>
       </c>
-      <c r="M22" s="132" t="n">
+      <c r="M22" s="133" t="n">
         <f aca="false">Nov!$D$90</f>
         <v>0</v>
       </c>
-      <c r="N22" s="132" t="n">
+      <c r="N22" s="133" t="n">
         <f aca="false">Dez!$D$90</f>
         <v>0</v>
       </c>
-      <c r="O22" s="137"/>
+      <c r="O22" s="138"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="138" t="s">
+      <c r="B23" s="139" t="s">
         <v>99</v>
       </c>
-      <c r="C23" s="139" t="n">
+      <c r="C23" s="140" t="n">
         <f aca="false">Jan!$B$83</f>
         <v>0</v>
       </c>
-      <c r="D23" s="140" t="n">
+      <c r="D23" s="141" t="n">
         <f aca="false">Fev!$B$83</f>
         <v>0</v>
       </c>
-      <c r="E23" s="139" t="n">
+      <c r="E23" s="140" t="n">
         <f aca="false">Mar!$B$83</f>
         <v>880</v>
       </c>
-      <c r="F23" s="140" t="n">
+      <c r="F23" s="141" t="n">
         <f aca="false">Abr!$B$83</f>
         <v>50</v>
       </c>
-      <c r="G23" s="139" t="n">
+      <c r="G23" s="140" t="n">
         <f aca="false">Mai!$B$83</f>
         <v>0</v>
       </c>
-      <c r="H23" s="140" t="n">
+      <c r="H23" s="141" t="n">
         <f aca="false">Jun!$B$83</f>
         <v>0</v>
       </c>
-      <c r="I23" s="139" t="n">
+      <c r="I23" s="140" t="n">
         <f aca="false">Jul!$B$83</f>
         <v>0</v>
       </c>
-      <c r="J23" s="140" t="n">
+      <c r="J23" s="141" t="n">
         <f aca="false">Ago!$B$83</f>
         <v>0</v>
       </c>
-      <c r="K23" s="139" t="n">
+      <c r="K23" s="140" t="n">
         <f aca="false">Set!$B$83</f>
         <v>0</v>
       </c>
-      <c r="L23" s="140" t="n">
+      <c r="L23" s="141" t="n">
         <f aca="false">Out!$B$83</f>
         <v>0</v>
       </c>
-      <c r="M23" s="139" t="n">
+      <c r="M23" s="140" t="n">
         <f aca="false">Nov!$B$83</f>
         <v>0</v>
       </c>
-      <c r="N23" s="141" t="n">
+      <c r="N23" s="142" t="n">
         <f aca="false">Dez!$B$83</f>
         <v>0</v>
       </c>
-      <c r="O23" s="142" t="n">
+      <c r="O23" s="143" t="n">
         <f aca="false">SUM(C23:N23)</f>
         <v>930</v>
       </c>
@@ -9041,29 +9055,29 @@
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="73" t="n">
         <f aca="false">SUM(D27:D31)</f>
-        <v>91.46</v>
+        <v>154.66</v>
       </c>
       <c r="C28" s="74" t="s">
         <v>67</v>
       </c>
       <c r="D28" s="75" t="n">
         <f aca="false">SUBTOTAL(9,Fev!D36,Fev!D36,Mar!D36,Abr!D36,Mai!D36,Jun!D36,Jul!D36,Ago!D36,Set!D36,Out!D36,Nov!D36,Dez!D36)</f>
-        <v>68.1</v>
+        <v>131.3</v>
       </c>
       <c r="F28" s="72" t="s">
         <v>66</v>
       </c>
       <c r="G28" s="71" t="n">
         <f aca="false">SUBTOTAL(9,Jan!I35,Fev!I35,Mar!I35,Abr!I35,Mai!I35,Jun!I35,Jul!I35,Ago!I35,Set!I35,Out!I35,Nov!I35,Dez!I35)</f>
-        <v>30</v>
-      </c>
-      <c r="I28" s="143" t="s">
-        <v>220</v>
-      </c>
-      <c r="J28" s="143"/>
-      <c r="K28" s="143"/>
-      <c r="L28" s="143"/>
-      <c r="M28" s="144" t="n">
+        <v>60</v>
+      </c>
+      <c r="I28" s="144" t="s">
+        <v>224</v>
+      </c>
+      <c r="J28" s="144"/>
+      <c r="K28" s="144"/>
+      <c r="L28" s="144"/>
+      <c r="M28" s="145" t="n">
         <f aca="false">SUM(L30:L44)-SUM(K30:K44)</f>
         <v>3332.14</v>
       </c>
@@ -9083,20 +9097,20 @@
         <f aca="false">SUBTOTAL(9,Jan!I36,Fev!I36,Mar!I36,Abr!I36,Mai!I36,Jun!I36,Jul!I36,Ago!I36,Set!I36,Out!I36,Nov!I36,Dez!I36)</f>
         <v>380.9</v>
       </c>
-      <c r="I29" s="145" t="s">
-        <v>221</v>
-      </c>
-      <c r="J29" s="146" t="s">
-        <v>222</v>
-      </c>
-      <c r="K29" s="146" t="s">
-        <v>223</v>
-      </c>
-      <c r="L29" s="146" t="s">
-        <v>224</v>
-      </c>
-      <c r="M29" s="147" t="s">
+      <c r="I29" s="146" t="s">
         <v>225</v>
+      </c>
+      <c r="J29" s="147" t="s">
+        <v>226</v>
+      </c>
+      <c r="K29" s="147" t="s">
+        <v>227</v>
+      </c>
+      <c r="L29" s="147" t="s">
+        <v>228</v>
+      </c>
+      <c r="M29" s="148" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9114,20 +9128,20 @@
         <f aca="false">SUBTOTAL(9,Jan!I37,Fev!I37,Mar!I37,Abr!I37,Mai!I37,Jun!I37,Jul!I37,Ago!I37,Set!I37,Out!I37,Nov!I37,Dez!I37)</f>
         <v>0</v>
       </c>
-      <c r="I30" s="148" t="s">
-        <v>226</v>
-      </c>
-      <c r="J30" s="149" t="s">
-        <v>227</v>
-      </c>
-      <c r="K30" s="149" t="n">
+      <c r="I30" s="149" t="s">
+        <v>230</v>
+      </c>
+      <c r="J30" s="150" t="s">
+        <v>231</v>
+      </c>
+      <c r="K30" s="150" t="n">
         <v>201.64</v>
       </c>
-      <c r="L30" s="149" t="n">
+      <c r="L30" s="150" t="n">
         <f aca="false">200.05+10+10+64</f>
         <v>284.05</v>
       </c>
-      <c r="M30" s="150" t="n">
+      <c r="M30" s="151" t="n">
         <f aca="false">L30-K30</f>
         <v>82.41</v>
       </c>
@@ -9145,19 +9159,19 @@
         <f aca="false">SUBTOTAL(9,Jan!I38,Fev!I38,Mar!I38,Abr!I38,Mai!I38,Jun!I38,Jul!I38,Ago!I38,Set!I38,Out!I38,Nov!I38,Dez!I38)</f>
         <v>0</v>
       </c>
-      <c r="I31" s="151" t="s">
-        <v>228</v>
-      </c>
-      <c r="J31" s="149" t="s">
-        <v>229</v>
-      </c>
-      <c r="K31" s="149" t="n">
+      <c r="I31" s="152" t="s">
+        <v>232</v>
+      </c>
+      <c r="J31" s="150" t="s">
+        <v>233</v>
+      </c>
+      <c r="K31" s="150" t="n">
         <v>1289.99</v>
       </c>
-      <c r="L31" s="149" t="n">
+      <c r="L31" s="150" t="n">
         <v>1517.64</v>
       </c>
-      <c r="M31" s="150" t="n">
+      <c r="M31" s="151" t="n">
         <f aca="false">L31-K31</f>
         <v>227.65</v>
       </c>
@@ -9172,19 +9186,19 @@
         <f aca="false">SUBTOTAL(9,Jan!I39,Fev!I39,Mar!I39,Abr!I39,Mai!I39,Jun!I39,Jul!I39,Ago!I39,Set!I39,Out!I39,Nov!I39,Dez!I39)</f>
         <v>468.64</v>
       </c>
-      <c r="I32" s="151" t="s">
-        <v>230</v>
-      </c>
-      <c r="J32" s="149" t="s">
-        <v>231</v>
-      </c>
-      <c r="K32" s="149" t="n">
+      <c r="I32" s="152" t="s">
+        <v>234</v>
+      </c>
+      <c r="J32" s="150" t="s">
+        <v>235</v>
+      </c>
+      <c r="K32" s="150" t="n">
         <v>700</v>
       </c>
-      <c r="L32" s="149" t="n">
+      <c r="L32" s="150" t="n">
         <v>1000</v>
       </c>
-      <c r="M32" s="150" t="n">
+      <c r="M32" s="151" t="n">
         <f aca="false">L32-K32</f>
         <v>300</v>
       </c>
@@ -9205,24 +9219,24 @@
       </c>
       <c r="G33" s="75" t="n">
         <f aca="false">SUBTOTAL(9,Jan!I40,Fev!I40,Mar!I40,Abr!I40,Mai!I40,Jun!I40,Jul!I40,Ago!I40,Set!I40,Out!I40,Nov!I40,Dez!I40)</f>
-        <v>710</v>
-      </c>
-      <c r="H33" s="99" t="s">
-        <v>232</v>
-      </c>
-      <c r="I33" s="151" t="s">
-        <v>233</v>
-      </c>
-      <c r="J33" s="149" t="s">
-        <v>234</v>
-      </c>
-      <c r="K33" s="149" t="n">
+        <v>970</v>
+      </c>
+      <c r="H33" s="100" t="s">
+        <v>236</v>
+      </c>
+      <c r="I33" s="152" t="s">
+        <v>237</v>
+      </c>
+      <c r="J33" s="150" t="s">
+        <v>238</v>
+      </c>
+      <c r="K33" s="150" t="n">
         <v>128</v>
       </c>
-      <c r="L33" s="149" t="n">
+      <c r="L33" s="150" t="n">
         <v>176</v>
       </c>
-      <c r="M33" s="150" t="n">
+      <c r="M33" s="151" t="n">
         <f aca="false">L33-K33</f>
         <v>48</v>
       </c>
@@ -9230,7 +9244,7 @@
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="73" t="n">
         <f aca="false">SUM(D33:D40)</f>
-        <v>427.89</v>
+        <v>546.89</v>
       </c>
       <c r="C34" s="74" t="s">
         <v>75</v>
@@ -9246,23 +9260,23 @@
         <f aca="false">SUBTOTAL(9,Jan!I41,Fev!I41,Mar!I41,Abr!I41,Mai!I41,Jun!I41,Jul!I41,Ago!I41,Set!I41,Out!I41,Nov!I41,Dez!I41)</f>
         <v>40</v>
       </c>
-      <c r="H34" s="99" t="n">
+      <c r="H34" s="100" t="n">
         <f aca="false">SUM(K30:K36)</f>
         <v>5165.22</v>
       </c>
-      <c r="I34" s="151" t="s">
-        <v>235</v>
-      </c>
-      <c r="J34" s="149" t="s">
-        <v>234</v>
-      </c>
-      <c r="K34" s="149" t="n">
+      <c r="I34" s="152" t="s">
+        <v>239</v>
+      </c>
+      <c r="J34" s="150" t="s">
+        <v>238</v>
+      </c>
+      <c r="K34" s="150" t="n">
         <v>320.74</v>
       </c>
-      <c r="L34" s="149" t="n">
+      <c r="L34" s="150" t="n">
         <v>385</v>
       </c>
-      <c r="M34" s="150" t="n">
+      <c r="M34" s="151" t="n">
         <f aca="false">L34-K34</f>
         <v>64.26</v>
       </c>
@@ -9280,21 +9294,21 @@
       </c>
       <c r="G35" s="75" t="n">
         <f aca="false">SUBTOTAL(9,Jan!I42,Fev!I42,Mar!I42,Abr!I42,Mai!I42,Jun!I42,Jul!I42,Ago!I42,Set!I42,Out!I42,Nov!I42,Dez!I42)</f>
-        <v>1889.68</v>
-      </c>
-      <c r="I35" s="151" t="s">
-        <v>236</v>
-      </c>
-      <c r="J35" s="149" t="s">
-        <v>237</v>
-      </c>
-      <c r="K35" s="149" t="n">
+        <v>2902.36</v>
+      </c>
+      <c r="I35" s="152" t="s">
+        <v>240</v>
+      </c>
+      <c r="J35" s="150" t="s">
+        <v>241</v>
+      </c>
+      <c r="K35" s="150" t="n">
         <v>1715.14</v>
       </c>
-      <c r="L35" s="149" t="n">
+      <c r="L35" s="150" t="n">
         <v>2017.8</v>
       </c>
-      <c r="M35" s="150" t="n">
+      <c r="M35" s="151" t="n">
         <f aca="false">L35-K35</f>
         <v>302.66</v>
       </c>
@@ -9314,19 +9328,19 @@
         <f aca="false">SUBTOTAL(9,Jan!I43,Fev!I43,Mar!I43,Abr!I43,Mai!I43,Jun!I43,Jul!I43,Ago!I43,Set!I43,Out!I43,Nov!I43,Dez!I43)</f>
         <v>0</v>
       </c>
-      <c r="I36" s="151" t="s">
-        <v>238</v>
-      </c>
-      <c r="J36" s="151" t="s">
-        <v>239</v>
-      </c>
-      <c r="K36" s="151" t="n">
+      <c r="I36" s="152" t="s">
+        <v>242</v>
+      </c>
+      <c r="J36" s="152" t="s">
+        <v>243</v>
+      </c>
+      <c r="K36" s="152" t="n">
         <v>809.71</v>
       </c>
-      <c r="L36" s="151" t="n">
+      <c r="L36" s="152" t="n">
         <v>1000</v>
       </c>
-      <c r="M36" s="150" t="n">
+      <c r="M36" s="151" t="n">
         <f aca="false">L36-K36</f>
         <v>190.29</v>
       </c>
@@ -9346,19 +9360,19 @@
         <f aca="false">SUBTOTAL(9,C22:N22)</f>
         <v>6100.33</v>
       </c>
-      <c r="I37" s="152" t="s">
-        <v>240</v>
-      </c>
-      <c r="J37" s="132" t="s">
-        <v>239</v>
-      </c>
-      <c r="K37" s="153" t="n">
+      <c r="I37" s="153" t="s">
+        <v>244</v>
+      </c>
+      <c r="J37" s="133" t="s">
+        <v>243</v>
+      </c>
+      <c r="K37" s="154" t="n">
         <v>2378</v>
       </c>
-      <c r="L37" s="154" t="n">
+      <c r="L37" s="155" t="n">
         <v>3669</v>
       </c>
-      <c r="M37" s="150" t="n">
+      <c r="M37" s="151" t="n">
         <f aca="false">L37-K37</f>
         <v>1291</v>
       </c>
@@ -9369,26 +9383,26 @@
       </c>
       <c r="D38" s="75" t="n">
         <f aca="false">SUBTOTAL(9,Fev!D46,Fev!D46,Mar!D46,Abr!D46,Mai!D46,Jun!D46,Jul!D46,Ago!D46,Set!D46,Out!D46,Nov!D46,Dez!D46)</f>
-        <v>225.01</v>
+        <v>344.01</v>
       </c>
       <c r="F38" s="81"/>
       <c r="G38" s="78" t="n">
         <f aca="false">SUBTOTAL(9,Jan!I45,Fev!I45,Mar!I45,Abr!I45,Mai!I45,Jun!I45,Jul!I45,Ago!I45,Set!I45,Out!I45,Nov!I45,Dez!I45)</f>
         <v>0</v>
       </c>
-      <c r="I38" s="151" t="s">
-        <v>241</v>
-      </c>
-      <c r="J38" s="149" t="s">
-        <v>239</v>
-      </c>
-      <c r="K38" s="149" t="n">
+      <c r="I38" s="152" t="s">
+        <v>245</v>
+      </c>
+      <c r="J38" s="150" t="s">
+        <v>243</v>
+      </c>
+      <c r="K38" s="150" t="n">
         <v>78.9</v>
       </c>
-      <c r="L38" s="149" t="n">
+      <c r="L38" s="150" t="n">
         <v>93.24</v>
       </c>
-      <c r="M38" s="150" t="n">
+      <c r="M38" s="151" t="n">
         <f aca="false">L38-K38</f>
         <v>14.34</v>
       </c>
@@ -9399,79 +9413,79 @@
         <f aca="false">SUBTOTAL(9,Fev!D47,Fev!D47,Mar!D47,Abr!D47,Mai!D47,Jun!D47,Jul!D47,Ago!D47,Set!D47,Out!D47,Nov!D47,Dez!D47)</f>
         <v>0</v>
       </c>
-      <c r="I39" s="151" t="s">
-        <v>242</v>
-      </c>
-      <c r="J39" s="149" t="s">
-        <v>229</v>
-      </c>
-      <c r="K39" s="149" t="n">
+      <c r="I39" s="152" t="s">
+        <v>246</v>
+      </c>
+      <c r="J39" s="150" t="s">
+        <v>233</v>
+      </c>
+      <c r="K39" s="150" t="n">
         <v>630</v>
       </c>
-      <c r="L39" s="149" t="n">
+      <c r="L39" s="150" t="n">
         <v>741</v>
       </c>
-      <c r="M39" s="150" t="n">
+      <c r="M39" s="151" t="n">
         <f aca="false">L39-K39</f>
         <v>111</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="155"/>
+      <c r="B40" s="156"/>
       <c r="C40" s="64"/>
       <c r="D40" s="78" t="n">
         <f aca="false">SUBTOTAL(9,Fev!D48,Fev!D48,Mar!D48,Abr!D48,Mai!D48,Jun!D48,Jul!D48,Ago!D48,Set!D48,Out!D48,Nov!D48,Dez!D48)</f>
         <v>0</v>
       </c>
-      <c r="I40" s="156" t="s">
-        <v>243</v>
-      </c>
-      <c r="J40" s="149" t="s">
-        <v>244</v>
-      </c>
-      <c r="K40" s="149" t="n">
+      <c r="I40" s="157" t="s">
+        <v>247</v>
+      </c>
+      <c r="J40" s="150" t="s">
+        <v>248</v>
+      </c>
+      <c r="K40" s="150" t="n">
         <v>394</v>
       </c>
-      <c r="L40" s="149" t="n">
+      <c r="L40" s="150" t="n">
         <v>765</v>
       </c>
-      <c r="M40" s="150" t="n">
+      <c r="M40" s="151" t="n">
         <f aca="false">L40-K40</f>
         <v>371</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="155"/>
+      <c r="B41" s="156"/>
       <c r="C41" s="64"/>
       <c r="D41" s="78"/>
-      <c r="I41" s="156" t="s">
-        <v>245</v>
-      </c>
-      <c r="J41" s="149" t="s">
-        <v>244</v>
-      </c>
-      <c r="K41" s="149" t="n">
+      <c r="I41" s="157" t="s">
+        <v>249</v>
+      </c>
+      <c r="J41" s="150" t="s">
+        <v>248</v>
+      </c>
+      <c r="K41" s="150" t="n">
         <v>208.14</v>
       </c>
-      <c r="L41" s="149" t="n">
+      <c r="L41" s="150" t="n">
         <v>230</v>
       </c>
-      <c r="M41" s="150"/>
+      <c r="M41" s="151"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I42" s="151" t="s">
-        <v>246</v>
-      </c>
-      <c r="J42" s="149" t="s">
-        <v>239</v>
-      </c>
-      <c r="K42" s="149" t="n">
+      <c r="I42" s="152" t="s">
+        <v>250</v>
+      </c>
+      <c r="J42" s="150" t="s">
+        <v>243</v>
+      </c>
+      <c r="K42" s="150" t="n">
         <v>59.9</v>
       </c>
-      <c r="L42" s="149" t="n">
+      <c r="L42" s="150" t="n">
         <v>103.9</v>
       </c>
-      <c r="M42" s="150" t="n">
+      <c r="M42" s="151" t="n">
         <f aca="false">L42-K42</f>
         <v>44</v>
       </c>
@@ -9485,24 +9499,24 @@
       </c>
       <c r="D43" s="71" t="n">
         <f aca="false">SUBTOTAL(9,Fev!D50,Fev!D50,Mar!D50,Abr!D50,Mai!D50,Jun!D50,Jul!D50,Ago!D50,Set!D50,Out!D50,Nov!D50,Dez!D50)</f>
-        <v>107.4</v>
-      </c>
-      <c r="H43" s="99" t="s">
-        <v>247</v>
-      </c>
-      <c r="I43" s="151" t="s">
+        <v>245.4</v>
+      </c>
+      <c r="H43" s="100" t="s">
+        <v>251</v>
+      </c>
+      <c r="I43" s="152" t="s">
+        <v>252</v>
+      </c>
+      <c r="J43" s="150" t="s">
         <v>248</v>
       </c>
-      <c r="J43" s="149" t="s">
-        <v>244</v>
-      </c>
-      <c r="K43" s="149" t="n">
+      <c r="K43" s="150" t="n">
         <v>175</v>
       </c>
-      <c r="L43" s="149" t="n">
+      <c r="L43" s="150" t="n">
         <v>373.58</v>
       </c>
-      <c r="M43" s="150" t="n">
+      <c r="M43" s="151" t="n">
         <f aca="false">L43-K43</f>
         <v>198.58</v>
       </c>
@@ -9510,7 +9524,7 @@
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="73" t="n">
         <f aca="false">SUM(D43:D49)</f>
-        <v>701.88</v>
+        <v>1047.56</v>
       </c>
       <c r="C44" s="74" t="s">
         <v>57</v>
@@ -9519,23 +9533,23 @@
         <f aca="false">SUBTOTAL(9,Fev!D51,Fev!D51,Mar!D51,Abr!D51,Mai!D51,Jun!D51,Jul!D51,Ago!D51,Set!D51,Out!D51,Nov!D51,Dez!D51)</f>
         <v>0</v>
       </c>
-      <c r="H44" s="99" t="n">
+      <c r="H44" s="100" t="n">
         <f aca="false">SUM(K38:K44)</f>
         <v>1652.7</v>
       </c>
-      <c r="I44" s="157" t="s">
-        <v>249</v>
-      </c>
-      <c r="J44" s="158" t="s">
-        <v>244</v>
-      </c>
-      <c r="K44" s="158" t="n">
+      <c r="I44" s="158" t="s">
+        <v>253</v>
+      </c>
+      <c r="J44" s="159" t="s">
+        <v>248</v>
+      </c>
+      <c r="K44" s="159" t="n">
         <v>106.76</v>
       </c>
-      <c r="L44" s="158" t="n">
+      <c r="L44" s="159" t="n">
         <v>171.85</v>
       </c>
-      <c r="M44" s="159" t="n">
+      <c r="M44" s="160" t="n">
         <f aca="false">L44-K44</f>
         <v>65.09</v>
       </c>
@@ -9557,16 +9571,16 @@
         <f aca="false">SUBTOTAL(9,Fev!D53,Fev!D53,Mar!D53,Abr!D53,Mai!D53,Jun!D53,Jul!D53,Ago!D53,Set!D53,Out!D53,Nov!D53,Dez!D53)</f>
         <v>142</v>
       </c>
-      <c r="I46" s="160" t="s">
-        <v>214</v>
-      </c>
-      <c r="J46" s="160"/>
-      <c r="K46" s="160"/>
-      <c r="L46" s="161" t="n">
+      <c r="I46" s="161" t="s">
+        <v>218</v>
+      </c>
+      <c r="J46" s="161"/>
+      <c r="K46" s="161"/>
+      <c r="L46" s="162" t="n">
         <f aca="false">SUM(H34,H44)</f>
         <v>6817.92</v>
       </c>
-      <c r="M46" s="161"/>
+      <c r="M46" s="162"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C47" s="74" t="s">
@@ -9583,7 +9597,7 @@
       </c>
       <c r="D48" s="75" t="n">
         <f aca="false">SUBTOTAL(9,Fev!D55,Fev!D55,Mar!D55,Abr!D55,Mai!D55,Jun!D55,Jul!D55,Ago!D55,Set!D55,Out!D55,Nov!D55,Dez!D55)</f>
-        <v>452.48</v>
+        <v>660.16</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9608,7 +9622,7 @@
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="73" t="n">
         <f aca="false">SUM(D51:D57)</f>
-        <v>899.18</v>
+        <v>972.18</v>
       </c>
       <c r="C52" s="74" t="s">
         <v>40</v>
@@ -9633,7 +9647,7 @@
       </c>
       <c r="D54" s="75" t="n">
         <f aca="false">SUBTOTAL(9,Fev!D61,Fev!D61,Mar!D61,Abr!D61,Mai!D61,Jun!D61,Jul!D61,Ago!D61,Set!D61,Out!D61,Nov!D61,Dez!D61)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9642,7 +9656,7 @@
       </c>
       <c r="D55" s="75" t="n">
         <f aca="false">SUBTOTAL(9,Fev!D62,Fev!D62,Mar!D62,Abr!D62,Mai!D62,Jun!D62,Jul!D62,Ago!D62,Set!D62,Out!D62,Nov!D62,Dez!D62)</f>
-        <v>422.34</v>
+        <v>480.34</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9863,10 +9877,10 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B83" s="69" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C83" s="70" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="D83" s="71" t="n">
         <f aca="false">SUBTOTAL(9,Fev!D90,Fev!D90,Mar!D90,Abr!D90,Mai!D90,Jun!D90,Jul!D90,Ago!D90,Set!D90,Out!D90,Nov!D90,Dez!D90)</f>
@@ -9973,45 +9987,45 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="C2" s="162" t="s">
+        <v>256</v>
+      </c>
+      <c r="C2" s="163" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="163"/>
+      <c r="E2" s="164"/>
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="164"/>
-      <c r="H2" s="163"/>
-      <c r="J2" s="165"/>
+      <c r="G2" s="165"/>
+      <c r="H2" s="164"/>
+      <c r="J2" s="166"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="166"/>
+      <c r="C3" s="167"/>
       <c r="D3" s="17"/>
-      <c r="E3" s="163"/>
+      <c r="E3" s="164"/>
       <c r="F3" s="11" t="n">
         <f aca="false">SUM(D3:D7)</f>
         <v>0</v>
       </c>
-      <c r="G3" s="164"/>
-      <c r="H3" s="163"/>
-      <c r="M3" s="167" t="s">
-        <v>253</v>
-      </c>
-      <c r="N3" s="167" t="s">
-        <v>254</v>
-      </c>
-      <c r="P3" s="168" t="s">
+      <c r="G3" s="165"/>
+      <c r="H3" s="164"/>
+      <c r="M3" s="168" t="s">
+        <v>257</v>
+      </c>
+      <c r="N3" s="168" t="s">
+        <v>258</v>
+      </c>
+      <c r="P3" s="169" t="s">
         <v>64</v>
       </c>
-      <c r="R3" s="169" t="s">
+      <c r="R3" s="170" t="s">
         <v>66</v>
       </c>
     </row>
@@ -10025,17 +10039,17 @@
         <f aca="false">SUM(F11:F32)</f>
         <v>0</v>
       </c>
-      <c r="M4" s="168" t="str">
+      <c r="M4" s="169" t="str">
         <f aca="false">P3</f>
         <v>Alimentação</v>
       </c>
-      <c r="N4" s="170" t="s">
+      <c r="N4" s="171" t="s">
         <v>65</v>
       </c>
-      <c r="P4" s="168" t="s">
+      <c r="P4" s="169" t="s">
         <v>50</v>
       </c>
-      <c r="R4" s="169" t="s">
+      <c r="R4" s="170" t="s">
         <v>35</v>
       </c>
     </row>
@@ -10049,13 +10063,13 @@
         <f aca="false">D4</f>
         <v>0</v>
       </c>
-      <c r="N5" s="170" t="s">
+      <c r="N5" s="171" t="s">
         <v>67</v>
       </c>
-      <c r="P5" s="168" t="s">
+      <c r="P5" s="169" t="s">
         <v>32</v>
       </c>
-      <c r="R5" s="169" t="s">
+      <c r="R5" s="170" t="s">
         <v>69</v>
       </c>
     </row>
@@ -10067,13 +10081,13 @@
         <f aca="false">SUM(K11:K22)</f>
         <v>0</v>
       </c>
-      <c r="N6" s="170" t="s">
+      <c r="N6" s="171" t="s">
         <v>154</v>
       </c>
-      <c r="P6" s="168" t="s">
-        <v>255</v>
-      </c>
-      <c r="R6" s="169" t="s">
+      <c r="P6" s="169" t="s">
+        <v>259</v>
+      </c>
+      <c r="R6" s="170" t="s">
         <v>71</v>
       </c>
     </row>
@@ -10083,30 +10097,30 @@
       </c>
       <c r="C7" s="33"/>
       <c r="D7" s="34" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="F7" s="36" t="n">
         <f aca="false">F3-F4-F6</f>
         <v>0</v>
       </c>
-      <c r="N7" s="170" t="s">
+      <c r="N7" s="171" t="s">
         <v>70</v>
       </c>
-      <c r="P7" s="168" t="s">
+      <c r="P7" s="169" t="s">
         <v>39</v>
       </c>
-      <c r="R7" s="169" t="s">
+      <c r="R7" s="170" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N8" s="170" t="s">
+      <c r="N8" s="171" t="s">
         <v>62</v>
       </c>
-      <c r="P8" s="168" t="s">
+      <c r="P8" s="169" t="s">
         <v>88</v>
       </c>
-      <c r="R8" s="169" t="s">
+      <c r="R8" s="170" t="s">
         <v>72</v>
       </c>
     </row>
@@ -10125,10 +10139,10 @@
       <c r="J9" s="38"/>
       <c r="K9" s="38"/>
       <c r="N9" s="79"/>
-      <c r="P9" s="168" t="s">
+      <c r="P9" s="169" t="s">
         <v>77</v>
       </c>
-      <c r="R9" s="169" t="s">
+      <c r="R9" s="170" t="s">
         <v>74</v>
       </c>
     </row>
@@ -10160,17 +10174,17 @@
       <c r="K10" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="M10" s="168" t="str">
+      <c r="M10" s="169" t="str">
         <f aca="false">P4</f>
         <v>Lazer</v>
       </c>
-      <c r="N10" s="170" t="s">
+      <c r="N10" s="171" t="s">
         <v>73</v>
       </c>
-      <c r="P10" s="168" t="s">
+      <c r="P10" s="169" t="s">
         <v>99</v>
       </c>
-      <c r="R10" s="169" t="s">
+      <c r="R10" s="170" t="s">
         <v>42</v>
       </c>
     </row>
@@ -10183,14 +10197,14 @@
       <c r="H11" s="50"/>
       <c r="I11" s="51"/>
       <c r="J11" s="51"/>
-      <c r="K11" s="171"/>
-      <c r="N11" s="170" t="s">
+      <c r="K11" s="172"/>
+      <c r="N11" s="171" t="s">
         <v>75</v>
       </c>
-      <c r="P11" s="168" t="s">
+      <c r="P11" s="169" t="s">
         <v>79</v>
       </c>
-      <c r="R11" s="169" t="s">
+      <c r="R11" s="170" t="s">
         <v>77</v>
       </c>
     </row>
@@ -10203,11 +10217,11 @@
       <c r="H12" s="59"/>
       <c r="I12" s="60"/>
       <c r="J12" s="60"/>
-      <c r="K12" s="172"/>
-      <c r="N12" s="170" t="s">
+      <c r="K12" s="173"/>
+      <c r="N12" s="171" t="s">
         <v>76</v>
       </c>
-      <c r="R12" s="169" t="s">
+      <c r="R12" s="170" t="s">
         <v>79</v>
       </c>
     </row>
@@ -10220,11 +10234,11 @@
       <c r="H13" s="59"/>
       <c r="I13" s="60"/>
       <c r="J13" s="60"/>
-      <c r="K13" s="172"/>
-      <c r="N13" s="170" t="s">
-        <v>257</v>
-      </c>
-      <c r="R13" s="169" t="s">
+      <c r="K13" s="173"/>
+      <c r="N13" s="171" t="s">
+        <v>194</v>
+      </c>
+      <c r="R13" s="170" t="s">
         <v>129</v>
       </c>
     </row>
@@ -10237,8 +10251,8 @@
       <c r="H14" s="59"/>
       <c r="I14" s="60"/>
       <c r="J14" s="60"/>
-      <c r="K14" s="172"/>
-      <c r="N14" s="170" t="s">
+      <c r="K14" s="173"/>
+      <c r="N14" s="171" t="s">
         <v>51</v>
       </c>
     </row>
@@ -10251,8 +10265,8 @@
       <c r="H15" s="59"/>
       <c r="I15" s="60"/>
       <c r="J15" s="60"/>
-      <c r="K15" s="172"/>
-      <c r="N15" s="170" t="s">
+      <c r="K15" s="173"/>
+      <c r="N15" s="171" t="s">
         <v>78</v>
       </c>
     </row>
@@ -10265,8 +10279,8 @@
       <c r="H16" s="59"/>
       <c r="I16" s="60"/>
       <c r="J16" s="60"/>
-      <c r="K16" s="172"/>
-      <c r="N16" s="173" t="s">
+      <c r="K16" s="173"/>
+      <c r="N16" s="174" t="s">
         <v>55</v>
       </c>
     </row>
@@ -10279,8 +10293,8 @@
       <c r="H17" s="59"/>
       <c r="I17" s="60"/>
       <c r="J17" s="60"/>
-      <c r="K17" s="172"/>
-      <c r="N17" s="169"/>
+      <c r="K17" s="173"/>
+      <c r="N17" s="170"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="56"/>
@@ -10291,7 +10305,7 @@
       <c r="H18" s="59"/>
       <c r="I18" s="60"/>
       <c r="J18" s="60"/>
-      <c r="K18" s="172"/>
+      <c r="K18" s="173"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="56"/>
@@ -10302,12 +10316,12 @@
       <c r="H19" s="59"/>
       <c r="I19" s="60"/>
       <c r="J19" s="60"/>
-      <c r="K19" s="172"/>
-      <c r="M19" s="168" t="str">
+      <c r="K19" s="173"/>
+      <c r="M19" s="169" t="str">
         <f aca="false">P5</f>
         <v>Despesas</v>
       </c>
-      <c r="N19" s="170" t="s">
+      <c r="N19" s="171" t="s">
         <v>81</v>
       </c>
     </row>
@@ -10320,8 +10334,8 @@
       <c r="H20" s="59"/>
       <c r="I20" s="60"/>
       <c r="J20" s="60"/>
-      <c r="K20" s="172"/>
-      <c r="N20" s="170" t="s">
+      <c r="K20" s="173"/>
+      <c r="N20" s="171" t="s">
         <v>57</v>
       </c>
     </row>
@@ -10334,8 +10348,8 @@
       <c r="H21" s="59"/>
       <c r="I21" s="60"/>
       <c r="J21" s="60"/>
-      <c r="K21" s="172"/>
-      <c r="N21" s="170" t="s">
+      <c r="K21" s="173"/>
+      <c r="N21" s="171" t="s">
         <v>44</v>
       </c>
     </row>
@@ -10348,8 +10362,8 @@
       <c r="H22" s="61"/>
       <c r="I22" s="62"/>
       <c r="J22" s="62"/>
-      <c r="K22" s="174"/>
-      <c r="N22" s="170" t="s">
+      <c r="K22" s="175"/>
+      <c r="N22" s="171" t="s">
         <v>33</v>
       </c>
     </row>
@@ -10359,7 +10373,7 @@
       <c r="D23" s="16"/>
       <c r="E23" s="16"/>
       <c r="F23" s="58"/>
-      <c r="N23" s="170" t="s">
+      <c r="N23" s="171" t="s">
         <v>83</v>
       </c>
     </row>
@@ -10369,7 +10383,7 @@
       <c r="D24" s="16"/>
       <c r="E24" s="16"/>
       <c r="F24" s="58"/>
-      <c r="N24" s="170" t="s">
+      <c r="N24" s="171" t="s">
         <v>59</v>
       </c>
     </row>
@@ -10379,7 +10393,7 @@
       <c r="D25" s="16"/>
       <c r="E25" s="16"/>
       <c r="F25" s="58"/>
-      <c r="N25" s="169"/>
+      <c r="N25" s="170"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="56"/>
@@ -10408,12 +10422,12 @@
       <c r="D29" s="16"/>
       <c r="E29" s="16"/>
       <c r="F29" s="58"/>
-      <c r="M29" s="168" t="str">
+      <c r="M29" s="169" t="str">
         <f aca="false">P7</f>
         <v>Transporte</v>
       </c>
-      <c r="N29" s="170" t="s">
-        <v>258</v>
+      <c r="N29" s="171" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10422,7 +10436,7 @@
       <c r="D30" s="16"/>
       <c r="E30" s="16"/>
       <c r="F30" s="58"/>
-      <c r="N30" s="170" t="s">
+      <c r="N30" s="171" t="s">
         <v>40</v>
       </c>
     </row>
@@ -10432,7 +10446,7 @@
       <c r="D31" s="16"/>
       <c r="E31" s="16"/>
       <c r="F31" s="58"/>
-      <c r="N31" s="170" t="s">
+      <c r="N31" s="171" t="s">
         <v>85</v>
       </c>
     </row>
@@ -10442,42 +10456,42 @@
       <c r="D32" s="33"/>
       <c r="E32" s="33"/>
       <c r="F32" s="68"/>
-      <c r="N32" s="170" t="s">
+      <c r="N32" s="171" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N33" s="170" t="s">
+      <c r="N33" s="171" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N34" s="170" t="s">
+      <c r="N34" s="171" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="168" t="s">
+      <c r="B35" s="169" t="s">
         <v>64</v>
       </c>
-      <c r="C35" s="170" t="s">
+      <c r="C35" s="171" t="s">
         <v>65</v>
       </c>
-      <c r="D35" s="175" t="n">
+      <c r="D35" s="176" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C35,$F$11:$F$32)</f>
         <v>0</v>
       </c>
-      <c r="N35" s="169"/>
+      <c r="N35" s="170"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="176" t="n">
+      <c r="B36" s="177" t="n">
         <f aca="false">SUBTOTAL(9,D35:D39)</f>
         <v>0</v>
       </c>
-      <c r="C36" s="170" t="s">
+      <c r="C36" s="171" t="s">
         <v>67</v>
       </c>
-      <c r="D36" s="175" t="n">
+      <c r="D36" s="176" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C36,$F$11:$F$32)</f>
         <v>0</v>
       </c>
@@ -10495,10 +10509,10 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C37" s="170" t="s">
+      <c r="C37" s="171" t="s">
         <v>68</v>
       </c>
-      <c r="D37" s="175" t="n">
+      <c r="D37" s="176" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C37,$F$11:$F$32)</f>
         <v>0</v>
       </c>
@@ -10506,19 +10520,19 @@
       <c r="I37" s="44"/>
       <c r="J37" s="45"/>
       <c r="K37" s="46"/>
-      <c r="M37" s="168" t="str">
+      <c r="M37" s="169" t="str">
         <f aca="false">P8</f>
         <v>Educação</v>
       </c>
-      <c r="N37" s="177" t="s">
-        <v>259</v>
+      <c r="N37" s="178" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C38" s="170" t="s">
+      <c r="C38" s="171" t="s">
         <v>70</v>
       </c>
-      <c r="D38" s="175" t="n">
+      <c r="D38" s="176" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C38,$F$11:$F$32)</f>
         <v>0</v>
       </c>
@@ -10526,13 +10540,13 @@
       <c r="I38" s="53"/>
       <c r="J38" s="54"/>
       <c r="K38" s="55"/>
-      <c r="N38" s="177" t="s">
+      <c r="N38" s="178" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C39" s="170"/>
-      <c r="D39" s="175" t="n">
+      <c r="C39" s="171"/>
+      <c r="D39" s="176" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C39,$F$11:$F$32)</f>
         <v>0</v>
       </c>
@@ -10540,7 +10554,7 @@
       <c r="I39" s="53"/>
       <c r="J39" s="54"/>
       <c r="K39" s="55"/>
-      <c r="N39" s="177" t="s">
+      <c r="N39" s="178" t="s">
         <v>91</v>
       </c>
     </row>
@@ -10550,18 +10564,18 @@
       <c r="I40" s="53"/>
       <c r="J40" s="54"/>
       <c r="K40" s="55"/>
-      <c r="N40" s="177" t="s">
-        <v>260</v>
+      <c r="N40" s="178" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="168" t="s">
+      <c r="B41" s="169" t="s">
         <v>50</v>
       </c>
-      <c r="C41" s="170" t="s">
+      <c r="C41" s="171" t="s">
         <v>73</v>
       </c>
-      <c r="D41" s="175" t="n">
+      <c r="D41" s="176" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C41,$F$11:$F$32)</f>
         <v>0</v>
       </c>
@@ -10569,19 +10583,19 @@
       <c r="I41" s="53"/>
       <c r="J41" s="54"/>
       <c r="K41" s="55"/>
-      <c r="N41" s="177" t="s">
+      <c r="N41" s="178" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="176" t="n">
+      <c r="B42" s="177" t="n">
         <f aca="false">SUBTOTAL(9,D41:D48)</f>
         <v>0</v>
       </c>
-      <c r="C42" s="170" t="s">
+      <c r="C42" s="171" t="s">
         <v>75</v>
       </c>
-      <c r="D42" s="175" t="n">
+      <c r="D42" s="176" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C42,$F$11:$F$32)</f>
         <v>0</v>
       </c>
@@ -10589,15 +10603,15 @@
       <c r="I42" s="53"/>
       <c r="J42" s="54"/>
       <c r="K42" s="55"/>
-      <c r="N42" s="177" t="s">
+      <c r="N42" s="178" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C43" s="170" t="s">
+      <c r="C43" s="171" t="s">
         <v>76</v>
       </c>
-      <c r="D43" s="175" t="n">
+      <c r="D43" s="176" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C43,$F$11:$F$32)</f>
         <v>0</v>
       </c>
@@ -10605,13 +10619,13 @@
       <c r="I43" s="53"/>
       <c r="J43" s="54"/>
       <c r="K43" s="55"/>
-      <c r="N43" s="178"/>
+      <c r="N43" s="179"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C44" s="170" t="s">
+      <c r="C44" s="171" t="s">
         <v>78</v>
       </c>
-      <c r="D44" s="175" t="n">
+      <c r="D44" s="176" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C44,$F$11:$F$32)</f>
         <v>0</v>
       </c>
@@ -10621,10 +10635,10 @@
       <c r="K44" s="55"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C45" s="170" t="s">
+      <c r="C45" s="171" t="s">
         <v>80</v>
       </c>
-      <c r="D45" s="175" t="n">
+      <c r="D45" s="176" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C45,$F$11:$F$32)</f>
         <v>0</v>
       </c>
@@ -10632,19 +10646,19 @@
       <c r="I45" s="53"/>
       <c r="J45" s="54"/>
       <c r="K45" s="55"/>
-      <c r="M45" s="168" t="str">
+      <c r="M45" s="169" t="str">
         <f aca="false">P9</f>
         <v>Saúde</v>
       </c>
-      <c r="N45" s="170" t="s">
+      <c r="N45" s="171" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C46" s="170" t="s">
+      <c r="C46" s="171" t="s">
         <v>51</v>
       </c>
-      <c r="D46" s="175" t="n">
+      <c r="D46" s="176" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C46,$F$11:$F$32)</f>
         <v>0</v>
       </c>
@@ -10652,13 +10666,13 @@
       <c r="I46" s="53"/>
       <c r="J46" s="54"/>
       <c r="K46" s="55"/>
-      <c r="N46" s="170" t="s">
+      <c r="N46" s="171" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C47" s="169"/>
-      <c r="D47" s="175" t="n">
+      <c r="C47" s="170"/>
+      <c r="D47" s="176" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C47,$F$11:$F$32)</f>
         <v>0</v>
       </c>
@@ -10666,13 +10680,13 @@
       <c r="I47" s="53"/>
       <c r="J47" s="54"/>
       <c r="K47" s="55"/>
-      <c r="N47" s="170" t="s">
-        <v>261</v>
+      <c r="N47" s="171" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C48" s="169"/>
-      <c r="D48" s="175" t="n">
+      <c r="C48" s="170"/>
+      <c r="D48" s="176" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C48,$F$11:$F$32)</f>
         <v>0</v>
       </c>
@@ -10680,7 +10694,7 @@
       <c r="I48" s="53"/>
       <c r="J48" s="54"/>
       <c r="K48" s="55"/>
-      <c r="N48" s="170" t="s">
+      <c r="N48" s="171" t="s">
         <v>97</v>
       </c>
     </row>
@@ -10689,18 +10703,18 @@
       <c r="I49" s="53"/>
       <c r="J49" s="54"/>
       <c r="K49" s="55"/>
-      <c r="N49" s="170" t="s">
-        <v>262</v>
+      <c r="N49" s="171" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="168" t="s">
+      <c r="B50" s="169" t="s">
         <v>32</v>
       </c>
-      <c r="C50" s="170" t="s">
+      <c r="C50" s="171" t="s">
         <v>81</v>
       </c>
-      <c r="D50" s="175" t="n">
+      <c r="D50" s="176" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C50,$F$11:$F$32)</f>
         <v>0</v>
       </c>
@@ -10708,19 +10722,19 @@
       <c r="I50" s="53"/>
       <c r="J50" s="54"/>
       <c r="K50" s="55"/>
-      <c r="N50" s="170" t="s">
+      <c r="N50" s="171" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="176" t="n">
+      <c r="B51" s="177" t="n">
         <f aca="false">SUBTOTAL(9,D50:D56)</f>
         <v>0</v>
       </c>
-      <c r="C51" s="170" t="s">
+      <c r="C51" s="171" t="s">
         <v>57</v>
       </c>
-      <c r="D51" s="175" t="n">
+      <c r="D51" s="176" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C51,$F$11:$F$32)</f>
         <v>0</v>
       </c>
@@ -10728,13 +10742,13 @@
       <c r="I51" s="53"/>
       <c r="J51" s="54"/>
       <c r="K51" s="55"/>
-      <c r="N51" s="169"/>
+      <c r="N51" s="170"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C52" s="170" t="s">
+      <c r="C52" s="171" t="s">
         <v>82</v>
       </c>
-      <c r="D52" s="175" t="n">
+      <c r="D52" s="176" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C52,$F$11:$F$32)</f>
         <v>0</v>
       </c>
@@ -10744,328 +10758,328 @@
       <c r="K52" s="63"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C53" s="170" t="s">
+      <c r="C53" s="171" t="s">
         <v>33</v>
       </c>
-      <c r="D53" s="175" t="n">
+      <c r="D53" s="176" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C53,$F$11:$F$32)</f>
         <v>0</v>
       </c>
-      <c r="M53" s="168" t="str">
+      <c r="M53" s="169" t="str">
         <f aca="false">P10</f>
         <v>Imprevistos</v>
       </c>
-      <c r="N53" s="170" t="s">
+      <c r="N53" s="171" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C54" s="170" t="s">
+      <c r="C54" s="171" t="s">
         <v>83</v>
       </c>
-      <c r="D54" s="175" t="n">
+      <c r="D54" s="176" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C54,$F$11:$F$32)</f>
         <v>0</v>
       </c>
-      <c r="N54" s="170" t="s">
+      <c r="N54" s="171" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C55" s="170" t="s">
+      <c r="C55" s="171" t="s">
         <v>59</v>
       </c>
-      <c r="D55" s="175" t="n">
+      <c r="D55" s="176" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C55,$F$11:$F$32)</f>
         <v>0</v>
       </c>
-      <c r="N55" s="170" t="s">
+      <c r="N55" s="171" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C56" s="169"/>
-      <c r="D56" s="175" t="n">
+      <c r="C56" s="170"/>
+      <c r="D56" s="176" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C56,$F$11:$F$32)</f>
         <v>0</v>
       </c>
-      <c r="N56" s="170" t="s">
+      <c r="N56" s="171" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N57" s="170" t="s">
+      <c r="N57" s="171" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B58" s="168" t="s">
+      <c r="B58" s="169" t="s">
         <v>39</v>
       </c>
-      <c r="C58" s="170" t="s">
+      <c r="C58" s="171" t="s">
         <v>84</v>
       </c>
-      <c r="D58" s="175" t="n">
+      <c r="D58" s="176" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C58,$F$11:$F$32)</f>
         <v>0</v>
       </c>
-      <c r="N58" s="170" t="s">
+      <c r="N58" s="171" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B59" s="176" t="n">
+      <c r="B59" s="177" t="n">
         <f aca="false">SUBTOTAL(9,D58:D64)</f>
         <v>0</v>
       </c>
-      <c r="C59" s="170" t="s">
+      <c r="C59" s="171" t="s">
         <v>40</v>
       </c>
-      <c r="D59" s="175" t="n">
+      <c r="D59" s="176" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C59,$F$11:$F$32)</f>
         <v>0</v>
       </c>
-      <c r="N59" s="169"/>
+      <c r="N59" s="170"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C60" s="170" t="s">
+      <c r="C60" s="171" t="s">
         <v>85</v>
       </c>
-      <c r="D60" s="175" t="n">
+      <c r="D60" s="176" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C60,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C61" s="170" t="s">
+      <c r="C61" s="171" t="s">
         <v>86</v>
       </c>
-      <c r="D61" s="175" t="n">
+      <c r="D61" s="176" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C61,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C62" s="170" t="s">
+      <c r="C62" s="171" t="s">
         <v>47</v>
       </c>
-      <c r="D62" s="175" t="n">
+      <c r="D62" s="176" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C62,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C63" s="170" t="s">
+      <c r="C63" s="171" t="s">
         <v>87</v>
       </c>
-      <c r="D63" s="175" t="n">
+      <c r="D63" s="176" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C63,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C64" s="169"/>
-      <c r="D64" s="175" t="n">
+      <c r="C64" s="170"/>
+      <c r="D64" s="176" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C64,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B66" s="168" t="s">
+      <c r="B66" s="169" t="s">
         <v>88</v>
       </c>
-      <c r="C66" s="177" t="s">
+      <c r="C66" s="178" t="s">
         <v>89</v>
       </c>
-      <c r="D66" s="175" t="n">
+      <c r="D66" s="176" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C66,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B67" s="176" t="n">
+      <c r="B67" s="177" t="n">
         <f aca="false">SUBTOTAL(9,D66:D72)</f>
         <v>0</v>
       </c>
-      <c r="C67" s="177" t="s">
+      <c r="C67" s="178" t="s">
         <v>90</v>
       </c>
-      <c r="D67" s="175" t="n">
+      <c r="D67" s="176" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C67,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C68" s="177" t="s">
+      <c r="C68" s="178" t="s">
         <v>91</v>
       </c>
-      <c r="D68" s="175" t="n">
+      <c r="D68" s="176" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C68,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C69" s="177" t="s">
+      <c r="C69" s="178" t="s">
         <v>92</v>
       </c>
-      <c r="D69" s="175" t="n">
+      <c r="D69" s="176" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C69,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C70" s="177" t="s">
+      <c r="C70" s="178" t="s">
         <v>93</v>
       </c>
-      <c r="D70" s="175" t="n">
+      <c r="D70" s="176" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C70,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C71" s="177" t="s">
+      <c r="C71" s="178" t="s">
         <v>94</v>
       </c>
-      <c r="D71" s="175" t="n">
+      <c r="D71" s="176" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C71,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C72" s="178"/>
-      <c r="D72" s="175" t="n">
+      <c r="C72" s="179"/>
+      <c r="D72" s="176" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C72,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B74" s="168" t="s">
+      <c r="B74" s="169" t="s">
         <v>77</v>
       </c>
-      <c r="C74" s="170" t="s">
+      <c r="C74" s="171" t="s">
         <v>95</v>
       </c>
-      <c r="D74" s="175" t="n">
+      <c r="D74" s="176" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C74,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B75" s="176" t="n">
+      <c r="B75" s="177" t="n">
         <f aca="false">SUBTOTAL(9,D74:D80)</f>
         <v>0</v>
       </c>
-      <c r="C75" s="170" t="s">
+      <c r="C75" s="171" t="s">
         <v>96</v>
       </c>
-      <c r="D75" s="175" t="n">
+      <c r="D75" s="176" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C75,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C76" s="170" t="s">
+      <c r="C76" s="171" t="s">
         <v>97</v>
       </c>
-      <c r="D76" s="175" t="n">
+      <c r="D76" s="176" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C76,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C77" s="170" t="s">
+      <c r="C77" s="171" t="s">
         <v>98</v>
       </c>
-      <c r="D77" s="175" t="n">
+      <c r="D77" s="176" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C77,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C78" s="169"/>
-      <c r="D78" s="175" t="n">
+      <c r="C78" s="170"/>
+      <c r="D78" s="176" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C78,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C79" s="169"/>
-      <c r="D79" s="175" t="n">
+      <c r="C79" s="170"/>
+      <c r="D79" s="176" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C79,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C80" s="169"/>
-      <c r="D80" s="175" t="n">
+      <c r="C80" s="170"/>
+      <c r="D80" s="176" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C80,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B82" s="168" t="s">
+      <c r="B82" s="169" t="s">
         <v>99</v>
       </c>
-      <c r="C82" s="170" t="s">
+      <c r="C82" s="171" t="s">
         <v>100</v>
       </c>
-      <c r="D82" s="175" t="n">
+      <c r="D82" s="176" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C82,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B83" s="176" t="n">
+      <c r="B83" s="177" t="n">
         <f aca="false">SUBTOTAL(9,D82:D88)</f>
         <v>0</v>
       </c>
-      <c r="C83" s="170" t="s">
+      <c r="C83" s="171" t="s">
         <v>101</v>
       </c>
-      <c r="D83" s="175" t="n">
+      <c r="D83" s="176" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C83,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C84" s="170" t="s">
+      <c r="C84" s="171" t="s">
         <v>102</v>
       </c>
-      <c r="D84" s="175" t="n">
+      <c r="D84" s="176" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C84,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C85" s="170" t="s">
+      <c r="C85" s="171" t="s">
         <v>103</v>
       </c>
-      <c r="D85" s="175" t="n">
+      <c r="D85" s="176" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C85,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C86" s="170" t="s">
+      <c r="C86" s="171" t="s">
         <v>104</v>
       </c>
-      <c r="D86" s="175" t="n">
+      <c r="D86" s="176" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C86,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C87" s="170" t="s">
+      <c r="C87" s="171" t="s">
         <v>105</v>
       </c>
-      <c r="D87" s="175" t="n">
+      <c r="D87" s="176" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C87,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C88" s="169"/>
-      <c r="D88" s="175" t="n">
+      <c r="C88" s="170"/>
+      <c r="D88" s="176" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C88,$F$11:$F$32)</f>
         <v>0</v>
       </c>
@@ -11172,7 +11186,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46209</v>
+        <v>46221</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -12365,7 +12379,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46209</v>
+        <v>46221</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -13573,7 +13587,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46209</v>
+        <v>46221</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -14856,7 +14870,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46209</v>
+        <v>46221</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>150</v>
@@ -16105,14 +16119,14 @@
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="9" t="n">
-        <v>2100</v>
+        <v>2318</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F3" s="11" t="n">
         <f aca="false">SUM(D3,D5,D6,D7,D4)</f>
-        <v>2091.7</v>
+        <v>2309.7</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>6</v>
@@ -16142,7 +16156,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46209</v>
+        <v>46221</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>170</v>
@@ -16211,7 +16225,7 @@
       </c>
       <c r="F7" s="36" t="n">
         <f aca="false">F3-F4-F6</f>
-        <v>69.9999999999998</v>
+        <v>288.000000000001</v>
       </c>
       <c r="I7" s="89"/>
     </row>
@@ -17329,8 +17343,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="17.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="13.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="11.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="34.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="8.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="28.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="12.27"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="13" style="1" width="12"/>
   </cols>
   <sheetData>
@@ -17358,13 +17372,15 @@
         <v>4</v>
       </c>
       <c r="C3" s="8"/>
-      <c r="D3" s="9"/>
+      <c r="D3" s="9" t="n">
+        <v>2637</v>
+      </c>
       <c r="E3" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F3" s="11" t="n">
         <f aca="false">SUM(D3,D5,D6,D7,D4)</f>
-        <v>69.9999999999998</v>
+        <v>3135</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>6</v>
@@ -17372,7 +17388,15 @@
       <c r="K3" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="L3" s="14"/>
+      <c r="L3" s="14" t="n">
+        <v>809.19</v>
+      </c>
+      <c r="M3" s="1" t="n">
+        <v>601</v>
+      </c>
+      <c r="N3" s="1" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="15" t="s">
@@ -17381,18 +17405,18 @@
       <c r="C4" s="16"/>
       <c r="D4" s="17" t="n">
         <f aca="false">SUM(P10:P25)</f>
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="E4" s="18" t="s">
         <v>9</v>
       </c>
       <c r="F4" s="19" t="n">
         <f aca="false">SUM(F11:F32)</f>
-        <v>179.7</v>
+        <v>780.58</v>
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46209</v>
+        <v>46221</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -17410,7 +17434,7 @@
       </c>
       <c r="F5" s="25" t="n">
         <f aca="false">D4</f>
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="I5" s="26" t="s">
         <v>14</v>
@@ -17420,7 +17444,7 @@
       </c>
       <c r="L5" s="14" t="n">
         <f aca="false">SUM(P10:P25)</f>
-        <v>0</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17434,15 +17458,18 @@
       </c>
       <c r="F6" s="28" t="n">
         <f aca="false">SUM(K11:K22)</f>
-        <v>20</v>
+        <v>1357.68</v>
       </c>
       <c r="I6" s="29" t="n">
-        <v>45847</v>
+        <v>46221</v>
       </c>
       <c r="K6" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="L6" s="31"/>
+      <c r="L6" s="92" t="n">
+        <f aca="false">217-SUM(F16:F32)</f>
+        <v>-42.7</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="32" t="s">
@@ -17451,14 +17478,14 @@
       <c r="C7" s="33"/>
       <c r="D7" s="34" t="n">
         <f aca="false">Jun!F7</f>
-        <v>69.9999999999998</v>
+        <v>288.000000000001</v>
       </c>
       <c r="E7" s="35" t="s">
         <v>19</v>
       </c>
       <c r="F7" s="36" t="n">
         <f aca="false">F3-F4-F6</f>
-        <v>-129.7</v>
+        <v>996.740000000001</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17519,14 +17546,22 @@
       <c r="M10" s="43"/>
       <c r="N10" s="44"/>
       <c r="O10" s="45"/>
-      <c r="P10" s="46"/>
+      <c r="P10" s="46" t="n">
+        <v>210</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="47"/>
-      <c r="C11" s="92"/>
-      <c r="D11" s="92"/>
+      <c r="B11" s="47" t="n">
+        <v>46209</v>
+      </c>
+      <c r="C11" s="48" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="48" t="s">
+        <v>194</v>
+      </c>
       <c r="E11" s="48" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F11" s="49" t="n">
         <v>179.7</v>
@@ -17545,16 +17580,30 @@
       <c r="P11" s="55"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="56"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="58"/>
+      <c r="B12" s="56" t="n">
+        <v>46210</v>
+      </c>
+      <c r="C12" s="57" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" s="57" t="s">
+        <v>67</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="F12" s="58" t="n">
+        <v>33.5</v>
+      </c>
       <c r="H12" s="59"/>
-      <c r="I12" s="51"/>
-      <c r="J12" s="60"/>
-      <c r="K12" s="55" t="s">
-        <v>195</v>
+      <c r="I12" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="J12" s="60" t="s">
+        <v>159</v>
+      </c>
+      <c r="K12" s="55" t="n">
+        <v>1012.68</v>
       </c>
       <c r="M12" s="52"/>
       <c r="N12" s="53"/>
@@ -17563,14 +17612,25 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="56"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
+      <c r="C13" s="57" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" s="57" t="s">
+        <v>59</v>
+      </c>
       <c r="E13" s="16"/>
-      <c r="F13" s="58"/>
+      <c r="F13" s="58" t="n">
+        <f aca="false">19.5+3.68</f>
+        <v>23.18</v>
+      </c>
       <c r="H13" s="59"/>
-      <c r="I13" s="51"/>
+      <c r="I13" s="51" t="s">
+        <v>129</v>
+      </c>
       <c r="J13" s="60"/>
-      <c r="K13" s="55"/>
+      <c r="K13" s="55" t="n">
+        <v>35</v>
+      </c>
       <c r="M13" s="52"/>
       <c r="N13" s="53"/>
       <c r="O13" s="54"/>
@@ -17578,14 +17638,26 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="56"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="58"/>
+      <c r="C14" s="57" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="57" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="F14" s="58" t="n">
+        <v>100</v>
+      </c>
       <c r="H14" s="59"/>
-      <c r="I14" s="51"/>
+      <c r="I14" s="51" t="s">
+        <v>66</v>
+      </c>
       <c r="J14" s="60"/>
-      <c r="K14" s="55"/>
+      <c r="K14" s="55" t="n">
+        <v>30</v>
+      </c>
       <c r="M14" s="52"/>
       <c r="N14" s="53"/>
       <c r="O14" s="54"/>
@@ -17593,14 +17665,26 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="56"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="58"/>
+      <c r="C15" s="57" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="57" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="F15" s="58" t="n">
+        <v>184.5</v>
+      </c>
       <c r="H15" s="59"/>
-      <c r="I15" s="51"/>
+      <c r="I15" s="51" t="s">
+        <v>72</v>
+      </c>
       <c r="J15" s="60"/>
-      <c r="K15" s="55"/>
+      <c r="K15" s="55" t="n">
+        <v>260</v>
+      </c>
       <c r="M15" s="52"/>
       <c r="N15" s="53"/>
       <c r="O15" s="54"/>
@@ -17608,10 +17692,18 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="56"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="58"/>
+      <c r="C16" s="57" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" s="57" t="s">
+        <v>51</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="F16" s="58" t="n">
+        <v>19</v>
+      </c>
       <c r="H16" s="59"/>
       <c r="I16" s="51"/>
       <c r="J16" s="60"/>
@@ -17623,10 +17715,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="56"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
+      <c r="C17" s="57" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17" s="57" t="s">
+        <v>67</v>
+      </c>
       <c r="E17" s="16"/>
-      <c r="F17" s="58"/>
+      <c r="F17" s="58" t="n">
+        <v>25.9</v>
+      </c>
       <c r="H17" s="59"/>
       <c r="I17" s="51"/>
       <c r="J17" s="60"/>
@@ -17638,10 +17736,16 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="56"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
+      <c r="C18" s="57" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="57" t="s">
+        <v>47</v>
+      </c>
       <c r="E18" s="16"/>
-      <c r="F18" s="58"/>
+      <c r="F18" s="58" t="n">
+        <v>58</v>
+      </c>
       <c r="H18" s="59"/>
       <c r="I18" s="51"/>
       <c r="J18" s="60"/>
@@ -17653,10 +17757,16 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="56"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
+      <c r="C19" s="57" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" s="57" t="s">
+        <v>86</v>
+      </c>
       <c r="E19" s="16"/>
-      <c r="F19" s="58"/>
+      <c r="F19" s="58" t="n">
+        <v>15</v>
+      </c>
       <c r="H19" s="59"/>
       <c r="I19" s="51"/>
       <c r="J19" s="60"/>
@@ -17668,10 +17778,16 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="56"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
+      <c r="C20" s="57" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" s="57" t="s">
+        <v>67</v>
+      </c>
       <c r="E20" s="16"/>
-      <c r="F20" s="58"/>
+      <c r="F20" s="58" t="n">
+        <v>3.8</v>
+      </c>
       <c r="H20" s="59"/>
       <c r="I20" s="51"/>
       <c r="J20" s="60"/>
@@ -17683,10 +17799,16 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="56"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
+      <c r="C21" s="57" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="57" t="s">
+        <v>81</v>
+      </c>
       <c r="E21" s="16"/>
-      <c r="F21" s="58"/>
+      <c r="F21" s="58" t="n">
+        <v>120</v>
+      </c>
       <c r="H21" s="59"/>
       <c r="I21" s="51"/>
       <c r="J21" s="60"/>
@@ -17698,10 +17820,16 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="56"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
+      <c r="C22" s="57" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="57" t="s">
+        <v>81</v>
+      </c>
       <c r="E22" s="16"/>
-      <c r="F22" s="58"/>
+      <c r="F22" s="58" t="n">
+        <v>18</v>
+      </c>
       <c r="H22" s="61"/>
       <c r="I22" s="62"/>
       <c r="J22" s="62"/>
@@ -17713,13 +17841,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="56"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
+      <c r="C23" s="57"/>
+      <c r="D23" s="57"/>
       <c r="E23" s="16"/>
       <c r="F23" s="58"/>
       <c r="K23" s="12" t="n">
         <f aca="false">SUM(K11:K22)</f>
-        <v>20</v>
+        <v>1357.68</v>
       </c>
       <c r="M23" s="52"/>
       <c r="N23" s="53"/>
@@ -17728,8 +17856,8 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="56"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
+      <c r="C24" s="57"/>
+      <c r="D24" s="57"/>
       <c r="E24" s="16"/>
       <c r="F24" s="58"/>
       <c r="M24" s="52"/>
@@ -17739,8 +17867,8 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="56"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
+      <c r="C25" s="57"/>
+      <c r="D25" s="57"/>
       <c r="E25" s="16"/>
       <c r="F25" s="58"/>
       <c r="M25" s="64"/>
@@ -17750,43 +17878,43 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="56"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
+      <c r="C26" s="57"/>
+      <c r="D26" s="57"/>
       <c r="E26" s="16"/>
       <c r="F26" s="58"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="56"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
+      <c r="C27" s="57"/>
+      <c r="D27" s="57"/>
       <c r="E27" s="16"/>
       <c r="F27" s="58"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="56"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
+      <c r="C28" s="57"/>
+      <c r="D28" s="57"/>
       <c r="E28" s="16"/>
       <c r="F28" s="58"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="56"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="16"/>
+      <c r="C29" s="57"/>
+      <c r="D29" s="57"/>
       <c r="E29" s="16"/>
       <c r="F29" s="58"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="56"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
+      <c r="C30" s="57"/>
+      <c r="D30" s="57"/>
       <c r="E30" s="16"/>
       <c r="F30" s="58"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="56"/>
-      <c r="C31" s="16"/>
-      <c r="D31" s="16"/>
+      <c r="C31" s="57"/>
+      <c r="D31" s="57"/>
       <c r="E31" s="16"/>
       <c r="F31" s="58"/>
     </row>
@@ -17813,20 +17941,20 @@
       </c>
       <c r="I35" s="71" t="n">
         <f aca="false">SUMIF($I$11:$I$22,H35,$K$11:$K$22)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="73" t="n">
         <f aca="false">SUM(D35:D39)</f>
-        <v>0</v>
+        <v>63.2</v>
       </c>
       <c r="C36" s="74" t="s">
         <v>67</v>
       </c>
       <c r="D36" s="75" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C36,$F$11:$F$32)</f>
-        <v>0</v>
+        <v>63.2</v>
       </c>
       <c r="H36" s="76" t="s">
         <v>35</v>
@@ -17890,7 +18018,7 @@
       </c>
       <c r="I40" s="75" t="n">
         <f aca="false">SUMIF($I$11:$I$22,H40,$K$11:$K$22)</f>
-        <v>0</v>
+        <v>260</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17915,7 +18043,7 @@
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="73" t="n">
         <f aca="false">SUBTOTAL(9,D41:D48)</f>
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="C42" s="74" t="s">
         <v>75</v>
@@ -17929,7 +18057,7 @@
       </c>
       <c r="I42" s="75" t="n">
         <f aca="false">SUMIF($I$11:$I$22,H42,$K$11:$K$22)</f>
-        <v>0</v>
+        <v>1012.68</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17984,7 +18112,7 @@
       </c>
       <c r="D46" s="75" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C46,$F$11:$F$32)</f>
-        <v>0</v>
+        <v>119</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18013,13 +18141,13 @@
       </c>
       <c r="D50" s="71" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C50,$F$11:$F$32)</f>
-        <v>0</v>
+        <v>138</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="73" t="n">
         <f aca="false">SUM(D50:D56)</f>
-        <v>0</v>
+        <v>345.68</v>
       </c>
       <c r="C51" s="74" t="s">
         <v>57</v>
@@ -18062,7 +18190,7 @@
       </c>
       <c r="D55" s="75" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C55,$F$11:$F$32)</f>
-        <v>0</v>
+        <v>207.68</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18090,7 +18218,7 @@
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="73" t="n">
         <f aca="false">SUM(D58:D64)</f>
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="C59" s="74" t="s">
         <v>40</v>
@@ -18115,7 +18243,7 @@
       </c>
       <c r="D61" s="75" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C61,$F$11:$F$32)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18124,7 +18252,7 @@
       </c>
       <c r="D62" s="75" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C62,$F$11:$F$32)</f>
-        <v>0</v>
+        <v>58</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18418,7 +18546,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -18446,7 +18574,7 @@
       </c>
       <c r="F3" s="11" t="n">
         <f aca="false">SUM(D3,D5,D6,D7,D4)</f>
-        <v>-129.7</v>
+        <v>996.740000000001</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>6</v>
@@ -18461,7 +18589,7 @@
         <v>8</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="D4" s="17" t="n">
         <f aca="false">SUM(P10:P25)</f>
@@ -18476,7 +18604,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46209</v>
+        <v>46221</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -18535,14 +18663,14 @@
       <c r="C7" s="33"/>
       <c r="D7" s="34" t="n">
         <f aca="false">Jul!F7</f>
-        <v>-129.7</v>
+        <v>996.740000000001</v>
       </c>
       <c r="E7" s="35" t="s">
         <v>19</v>
       </c>
       <c r="F7" s="36" t="n">
         <f aca="false">F3-F4-F6</f>
-        <v>-129.7</v>
+        <v>996.740000000001</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19492,7 +19620,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -19520,7 +19648,7 @@
       </c>
       <c r="F3" s="11" t="n">
         <f aca="false">SUM(D3,D5,D6,D7,D4)</f>
-        <v>-129.7</v>
+        <v>996.740000000001</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>6</v>
@@ -19548,7 +19676,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46209</v>
+        <v>46221</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -19607,14 +19735,14 @@
       <c r="C7" s="33"/>
       <c r="D7" s="34" t="n">
         <f aca="false">Ago!F7</f>
-        <v>-129.7</v>
+        <v>996.740000000001</v>
       </c>
       <c r="E7" s="35" t="s">
         <v>19</v>
       </c>
       <c r="F7" s="36" t="n">
         <f aca="false">F3-F4-F6</f>
-        <v>-129.7</v>
+        <v>996.740000000001</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19679,8 +19807,8 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="47"/>
-      <c r="C11" s="92"/>
-      <c r="D11" s="92"/>
+      <c r="C11" s="94"/>
+      <c r="D11" s="94"/>
       <c r="E11" s="48"/>
       <c r="F11" s="49"/>
       <c r="H11" s="50"/>

--- a/arquivos extras/Planilha.xlsx
+++ b/arquivos extras/Planilha.xlsx
@@ -70,13 +70,13 @@
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>10</xdr:col>
-                <xdr:colOff>145</xdr:colOff>
+                <xdr:colOff>193</xdr:colOff>
                 <xdr:row>9</xdr:row>
-                <xdr:rowOff>12</xdr:rowOff>
+                <xdr:rowOff>16</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>-24</xdr:colOff>
+                <xdr:colOff>-32</xdr:colOff>
                 <xdr:row>13</xdr:row>
                 <xdr:rowOff>20</xdr:rowOff>
               </xdr:to>
@@ -91,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1653" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1661" uniqueCount="268">
   <si>
     <t xml:space="preserve">JAN</t>
   </si>
@@ -675,10 +675,16 @@
     <t xml:space="preserve">JUL</t>
   </si>
   <si>
+    <t xml:space="preserve">renovaocao dos votos</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jogos / Games / Aplicativos pagos</t>
   </si>
   <si>
     <t xml:space="preserve">cartao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">renovacao dos votos</t>
   </si>
   <si>
     <t xml:space="preserve">bugao</t>
@@ -2370,10 +2376,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.0673863509020956"/>
-          <c:y val="0.102161218469689"/>
-          <c:w val="0.74823503044339"/>
-          <c:h val="0.815483715610138"/>
+          <c:x val="0.0673913855579215"/>
+          <c:y val="0.102173520380517"/>
+          <c:w val="0.748216220254772"/>
+          <c:h val="0.815341080137275"/>
         </c:manualLayout>
       </c:layout>
       <c:pie3DChart>
@@ -3357,9 +3363,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>46080</xdr:colOff>
+      <xdr:colOff>45360</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>20880</xdr:rowOff>
+      <xdr:rowOff>20160</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3368,7 +3374,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
-        <a:ext cx="9637200" cy="5979600"/>
+        <a:ext cx="9636480" cy="5978880"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3646,7 +3652,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46221</v>
+        <v>46227</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -4813,7 +4819,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -4841,7 +4847,7 @@
       </c>
       <c r="F3" s="11" t="n">
         <f aca="false">SUM(D3,D5,D6,D7,D4)</f>
-        <v>996.740000000001</v>
+        <v>1020.64</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>6</v>
@@ -4869,7 +4875,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46221</v>
+        <v>46227</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -4928,14 +4934,14 @@
       <c r="C7" s="33"/>
       <c r="D7" s="34" t="n">
         <f aca="false">Set!F7</f>
-        <v>996.740000000001</v>
+        <v>1020.64</v>
       </c>
       <c r="E7" s="35" t="s">
         <v>19</v>
       </c>
       <c r="F7" s="36" t="n">
         <f aca="false">F3-F4-F6</f>
-        <v>996.740000000001</v>
+        <v>1020.64</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5885,7 +5891,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -5913,7 +5919,7 @@
       </c>
       <c r="F3" s="11" t="n">
         <f aca="false">SUM(D3,D5,D6,D7,D4)</f>
-        <v>996.740000000001</v>
+        <v>1020.64</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>6</v>
@@ -5941,7 +5947,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46221</v>
+        <v>46227</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -6000,14 +6006,14 @@
       <c r="C7" s="33"/>
       <c r="D7" s="34" t="n">
         <f aca="false">Out!F7</f>
-        <v>996.740000000001</v>
+        <v>1020.64</v>
       </c>
       <c r="E7" s="35" t="s">
         <v>19</v>
       </c>
       <c r="F7" s="36" t="n">
         <f aca="false">F3-F4-F6</f>
-        <v>996.740000000001</v>
+        <v>1020.64</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6960,7 +6966,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -6988,7 +6994,7 @@
       </c>
       <c r="F3" s="11" t="n">
         <f aca="false">SUM(D3,D5,D6,D7,D4)</f>
-        <v>996.740000000001</v>
+        <v>1020.64</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>6</v>
@@ -7016,7 +7022,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46221</v>
+        <v>46227</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -7075,14 +7081,14 @@
       <c r="C7" s="33"/>
       <c r="D7" s="34" t="n">
         <f aca="false">Nov!F7</f>
-        <v>996.740000000001</v>
+        <v>1020.64</v>
       </c>
       <c r="E7" s="35" t="s">
         <v>19</v>
       </c>
       <c r="F7" s="36" t="n">
         <f aca="false">F3-F4-F6</f>
-        <v>996.740000000001</v>
+        <v>1020.64</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8018,7 +8024,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="99" width="21.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="100" width="15.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="100" width="23.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="100" width="14.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="100" width="19.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="100" width="14.57"/>
@@ -8037,46 +8043,46 @@
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="101" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C2" s="102" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D2" s="103" t="s">
         <v>106</v>
       </c>
       <c r="E2" s="103" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F2" s="103" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G2" s="103" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H2" s="103" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I2" s="103" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J2" s="103" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K2" s="103" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L2" s="103" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M2" s="103" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="N2" s="104" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="O2" s="104" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8109,36 +8115,36 @@
       </c>
       <c r="I3" s="107" t="n">
         <f aca="false">Jul!$F$3</f>
-        <v>3135</v>
+        <v>3291.25</v>
       </c>
       <c r="J3" s="107" t="n">
         <f aca="false">Ago!$F$3</f>
-        <v>996.740000000001</v>
+        <v>1020.64</v>
       </c>
       <c r="K3" s="107" t="n">
         <f aca="false">Set!$F$3</f>
-        <v>996.740000000001</v>
+        <v>1020.64</v>
       </c>
       <c r="L3" s="107" t="n">
         <f aca="false">Out!$F$3</f>
-        <v>996.740000000001</v>
+        <v>1020.64</v>
       </c>
       <c r="M3" s="107" t="n">
         <f aca="false">Nov!$F$3</f>
-        <v>996.740000000001</v>
+        <v>1020.64</v>
       </c>
       <c r="N3" s="108" t="n">
         <f aca="false">Dez!$F$3</f>
-        <v>996.740000000001</v>
+        <v>1020.64</v>
       </c>
       <c r="O3" s="108" t="n">
         <f aca="false">SUM(C3:N3)</f>
-        <v>24240.07</v>
+        <v>24515.82</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="109" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C4" s="110" t="n">
         <f aca="false">Jan!$F$4</f>
@@ -8166,7 +8172,7 @@
       </c>
       <c r="I4" s="110" t="n">
         <f aca="false">Jul!$F$4</f>
-        <v>780.58</v>
+        <v>912.93</v>
       </c>
       <c r="J4" s="110" t="n">
         <f aca="false">Ago!$F$4</f>
@@ -8190,12 +8196,12 @@
       </c>
       <c r="O4" s="111" t="n">
         <f aca="false">SUM(C4:N4)</f>
-        <v>8401.93</v>
+        <v>8534.28</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="109" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C5" s="112" t="n">
         <f aca="false">Jan!$F$6</f>
@@ -8309,7 +8315,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="109" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C7" s="117" t="n">
         <f aca="false">Jan!$L$4</f>
@@ -8366,7 +8372,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="109" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C8" s="120" t="n">
         <f aca="false">C4+C5</f>
@@ -8394,7 +8400,7 @@
       </c>
       <c r="I8" s="120" t="n">
         <f aca="false">I4+I5</f>
-        <v>2138.26</v>
+        <v>2270.61</v>
       </c>
       <c r="J8" s="120" t="n">
         <f aca="false">J4+J5</f>
@@ -8418,7 +8424,7 @@
       </c>
       <c r="O8" s="121" t="n">
         <f aca="false">SUM(C8:N8)</f>
-        <v>13398.83</v>
+        <v>13531.18</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8451,31 +8457,31 @@
       </c>
       <c r="I9" s="122" t="n">
         <f aca="false">I3-I8</f>
-        <v>996.740000000001</v>
+        <v>1020.64</v>
       </c>
       <c r="J9" s="122" t="n">
         <f aca="false">J3-J8</f>
-        <v>996.740000000001</v>
+        <v>1020.64</v>
       </c>
       <c r="K9" s="122" t="n">
         <f aca="false">K3-K8</f>
-        <v>996.740000000001</v>
+        <v>1020.64</v>
       </c>
       <c r="L9" s="122" t="n">
         <f aca="false">L3-L8</f>
-        <v>996.740000000001</v>
+        <v>1020.64</v>
       </c>
       <c r="M9" s="122" t="n">
         <f aca="false">M3-M8</f>
-        <v>996.740000000001</v>
+        <v>1020.64</v>
       </c>
       <c r="N9" s="123" t="n">
         <f aca="false">N3-N8</f>
-        <v>996.740000000001</v>
+        <v>1020.64</v>
       </c>
       <c r="O9" s="123" t="n">
         <f aca="false">N9</f>
-        <v>996.740000000001</v>
+        <v>1020.64</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8508,7 +8514,7 @@
       </c>
       <c r="I10" s="125" t="n">
         <f aca="false">Jul!D4</f>
-        <v>210</v>
+        <v>366.25</v>
       </c>
       <c r="J10" s="125" t="n">
         <f aca="false">Ago!D4</f>
@@ -8532,7 +8538,7 @@
       </c>
       <c r="O10" s="126" t="n">
         <f aca="false">SUM(C10:N10)</f>
-        <v>669.83</v>
+        <v>826.08</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -8545,46 +8551,46 @@
     <row r="14" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="101" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C15" s="102" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D15" s="103" t="s">
         <v>106</v>
       </c>
       <c r="E15" s="103" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F15" s="103" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G15" s="103" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H15" s="103" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I15" s="103" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J15" s="103" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K15" s="103" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L15" s="103" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M15" s="103" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="N15" s="104" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="O15" s="104" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8617,7 +8623,7 @@
       </c>
       <c r="I16" s="128" t="n">
         <f aca="false">Jul!$B$36</f>
-        <v>63.2</v>
+        <v>85.05</v>
       </c>
       <c r="J16" s="129" t="n">
         <f aca="false">Ago!$B$36</f>
@@ -8641,7 +8647,7 @@
       </c>
       <c r="O16" s="131" t="n">
         <f aca="false">SUM(C16:N16)</f>
-        <v>154.66</v>
+        <v>176.51</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8674,7 +8680,7 @@
       </c>
       <c r="I17" s="133" t="n">
         <f aca="false">Jul!$B$42</f>
-        <v>119</v>
+        <v>176.5</v>
       </c>
       <c r="J17" s="134" t="n">
         <f aca="false">Ago!$B$42</f>
@@ -8698,7 +8704,7 @@
       </c>
       <c r="O17" s="136" t="n">
         <f aca="false">SUM(C17:N17)</f>
-        <v>531.58</v>
+        <v>589.08</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8731,7 +8737,7 @@
       </c>
       <c r="I18" s="133" t="n">
         <f aca="false">Jul!$B$51</f>
-        <v>345.68</v>
+        <v>398.68</v>
       </c>
       <c r="J18" s="134" t="n">
         <f aca="false">Ago!$B$51</f>
@@ -8755,7 +8761,7 @@
       </c>
       <c r="O18" s="136" t="n">
         <f aca="false">SUM(C18:N18)</f>
-        <v>915.27</v>
+        <v>968.27</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9049,13 +9055,13 @@
       </c>
       <c r="D27" s="71" t="n">
         <f aca="false">SUBTOTAL(9,Fev!D35,Fev!D35,Mar!D35,Abr!D35,Mai!D35,Jun!D35,Jul!D35,Ago!D35,Set!D35,Out!D35,Nov!D35,Dez!D35)</f>
-        <v>23.36</v>
+        <v>45.21</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="73" t="n">
         <f aca="false">SUM(D27:D31)</f>
-        <v>154.66</v>
+        <v>176.51</v>
       </c>
       <c r="C28" s="74" t="s">
         <v>67</v>
@@ -9072,7 +9078,7 @@
         <v>60</v>
       </c>
       <c r="I28" s="144" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="J28" s="144"/>
       <c r="K28" s="144"/>
@@ -9098,19 +9104,19 @@
         <v>380.9</v>
       </c>
       <c r="I29" s="146" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="J29" s="147" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K29" s="147" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L29" s="147" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M29" s="148" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9129,10 +9135,10 @@
         <v>0</v>
       </c>
       <c r="I30" s="149" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="J30" s="150" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="K30" s="150" t="n">
         <v>201.64</v>
@@ -9160,10 +9166,10 @@
         <v>0</v>
       </c>
       <c r="I31" s="152" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J31" s="150" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="K31" s="150" t="n">
         <v>1289.99</v>
@@ -9187,10 +9193,10 @@
         <v>468.64</v>
       </c>
       <c r="I32" s="152" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="J32" s="150" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K32" s="150" t="n">
         <v>700</v>
@@ -9222,13 +9228,13 @@
         <v>970</v>
       </c>
       <c r="H33" s="100" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I33" s="152" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J33" s="150" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="K33" s="150" t="n">
         <v>128</v>
@@ -9244,7 +9250,7 @@
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="73" t="n">
         <f aca="false">SUM(D33:D40)</f>
-        <v>546.89</v>
+        <v>604.39</v>
       </c>
       <c r="C34" s="74" t="s">
         <v>75</v>
@@ -9265,10 +9271,10 @@
         <v>5165.22</v>
       </c>
       <c r="I34" s="152" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J34" s="150" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="K34" s="150" t="n">
         <v>320.74</v>
@@ -9297,10 +9303,10 @@
         <v>2902.36</v>
       </c>
       <c r="I35" s="152" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="J35" s="150" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="K35" s="150" t="n">
         <v>1715.14</v>
@@ -9329,10 +9335,10 @@
         <v>0</v>
       </c>
       <c r="I36" s="152" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="J36" s="152" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="K36" s="152" t="n">
         <v>809.71</v>
@@ -9361,10 +9367,10 @@
         <v>6100.33</v>
       </c>
       <c r="I37" s="153" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="J37" s="133" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="K37" s="154" t="n">
         <v>2378</v>
@@ -9383,7 +9389,7 @@
       </c>
       <c r="D38" s="75" t="n">
         <f aca="false">SUBTOTAL(9,Fev!D46,Fev!D46,Mar!D46,Abr!D46,Mai!D46,Jun!D46,Jul!D46,Ago!D46,Set!D46,Out!D46,Nov!D46,Dez!D46)</f>
-        <v>344.01</v>
+        <v>401.51</v>
       </c>
       <c r="F38" s="81"/>
       <c r="G38" s="78" t="n">
@@ -9391,10 +9397,10 @@
         <v>0</v>
       </c>
       <c r="I38" s="152" t="s">
+        <v>247</v>
+      </c>
+      <c r="J38" s="150" t="s">
         <v>245</v>
-      </c>
-      <c r="J38" s="150" t="s">
-        <v>243</v>
       </c>
       <c r="K38" s="150" t="n">
         <v>78.9</v>
@@ -9414,10 +9420,10 @@
         <v>0</v>
       </c>
       <c r="I39" s="152" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="J39" s="150" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="K39" s="150" t="n">
         <v>630</v>
@@ -9438,10 +9444,10 @@
         <v>0</v>
       </c>
       <c r="I40" s="157" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J40" s="150" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K40" s="150" t="n">
         <v>394</v>
@@ -9459,10 +9465,10 @@
       <c r="C41" s="64"/>
       <c r="D41" s="78"/>
       <c r="I41" s="157" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="J41" s="150" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K41" s="150" t="n">
         <v>208.14</v>
@@ -9474,10 +9480,10 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I42" s="152" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="J42" s="150" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="K42" s="150" t="n">
         <v>59.9</v>
@@ -9499,16 +9505,16 @@
       </c>
       <c r="D43" s="71" t="n">
         <f aca="false">SUBTOTAL(9,Fev!D50,Fev!D50,Mar!D50,Abr!D50,Mai!D50,Jun!D50,Jul!D50,Ago!D50,Set!D50,Out!D50,Nov!D50,Dez!D50)</f>
-        <v>245.4</v>
+        <v>298.4</v>
       </c>
       <c r="H43" s="100" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="I43" s="152" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="J43" s="150" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K43" s="150" t="n">
         <v>175</v>
@@ -9524,7 +9530,7 @@
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="73" t="n">
         <f aca="false">SUM(D43:D49)</f>
-        <v>1047.56</v>
+        <v>1100.56</v>
       </c>
       <c r="C44" s="74" t="s">
         <v>57</v>
@@ -9538,10 +9544,10 @@
         <v>1652.7</v>
       </c>
       <c r="I44" s="158" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="J44" s="159" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K44" s="159" t="n">
         <v>106.76</v>
@@ -9572,7 +9578,7 @@
         <v>142</v>
       </c>
       <c r="I46" s="161" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="J46" s="161"/>
       <c r="K46" s="161"/>
@@ -9877,10 +9883,10 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B83" s="69" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C83" s="70" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D83" s="71" t="n">
         <f aca="false">SUBTOTAL(9,Fev!D90,Fev!D90,Mar!D90,Abr!D90,Mai!D90,Jun!D90,Jul!D90,Ago!D90,Set!D90,Out!D90,Nov!D90,Dez!D90)</f>
@@ -9987,7 +9993,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C2" s="163" t="s">
         <v>1</v>
@@ -10017,10 +10023,10 @@
       <c r="G3" s="165"/>
       <c r="H3" s="164"/>
       <c r="M3" s="168" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N3" s="168" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="P3" s="169" t="s">
         <v>64</v>
@@ -10085,7 +10091,7 @@
         <v>154</v>
       </c>
       <c r="P6" s="169" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="R6" s="170" t="s">
         <v>71</v>
@@ -10097,7 +10103,7 @@
       </c>
       <c r="C7" s="33"/>
       <c r="D7" s="34" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F7" s="36" t="n">
         <f aca="false">F3-F4-F6</f>
@@ -10236,7 +10242,7 @@
       <c r="J13" s="60"/>
       <c r="K13" s="173"/>
       <c r="N13" s="171" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="R13" s="170" t="s">
         <v>129</v>
@@ -10427,7 +10433,7 @@
         <v>Transporte</v>
       </c>
       <c r="N29" s="171" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10525,7 +10531,7 @@
         <v>Educação</v>
       </c>
       <c r="N37" s="178" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10565,7 +10571,7 @@
       <c r="J40" s="54"/>
       <c r="K40" s="55"/>
       <c r="N40" s="178" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10681,7 +10687,7 @@
       <c r="J47" s="54"/>
       <c r="K47" s="55"/>
       <c r="N47" s="171" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10704,7 +10710,7 @@
       <c r="J49" s="54"/>
       <c r="K49" s="55"/>
       <c r="N49" s="171" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11186,7 +11192,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46221</v>
+        <v>46227</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -12379,7 +12385,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46221</v>
+        <v>46227</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -13587,7 +13593,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46221</v>
+        <v>46227</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -14870,7 +14876,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46221</v>
+        <v>46227</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>150</v>
@@ -16156,7 +16162,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46221</v>
+        <v>46227</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>170</v>
@@ -17380,7 +17386,7 @@
       </c>
       <c r="F3" s="11" t="n">
         <f aca="false">SUM(D3,D5,D6,D7,D4)</f>
-        <v>3135</v>
+        <v>3291.25</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>6</v>
@@ -17405,18 +17411,18 @@
       <c r="C4" s="16"/>
       <c r="D4" s="17" t="n">
         <f aca="false">SUM(P10:P25)</f>
-        <v>210</v>
+        <v>366.25</v>
       </c>
       <c r="E4" s="18" t="s">
         <v>9</v>
       </c>
       <c r="F4" s="19" t="n">
         <f aca="false">SUM(F11:F32)</f>
-        <v>780.58</v>
+        <v>912.93</v>
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46221</v>
+        <v>46227</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -17434,7 +17440,7 @@
       </c>
       <c r="F5" s="25" t="n">
         <f aca="false">D4</f>
-        <v>210</v>
+        <v>366.25</v>
       </c>
       <c r="I5" s="26" t="s">
         <v>14</v>
@@ -17444,7 +17450,7 @@
       </c>
       <c r="L5" s="14" t="n">
         <f aca="false">SUM(P10:P25)</f>
-        <v>210</v>
+        <v>366.25</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17468,7 +17474,7 @@
       </c>
       <c r="L6" s="92" t="n">
         <f aca="false">217-SUM(F16:F32)</f>
-        <v>-42.7</v>
+        <v>-175.05</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17485,7 +17491,7 @@
       </c>
       <c r="F7" s="36" t="n">
         <f aca="false">F3-F4-F6</f>
-        <v>996.740000000001</v>
+        <v>1020.64</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17543,11 +17549,13 @@
       <c r="K10" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="M10" s="43"/>
+      <c r="M10" s="43" t="s">
+        <v>194</v>
+      </c>
       <c r="N10" s="44"/>
       <c r="O10" s="45"/>
       <c r="P10" s="46" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17558,10 +17566,10 @@
         <v>50</v>
       </c>
       <c r="D11" s="48" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E11" s="48" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F11" s="49" t="n">
         <v>179.7</v>
@@ -17574,10 +17582,15 @@
       <c r="K11" s="46" t="n">
         <v>20</v>
       </c>
-      <c r="M11" s="52"/>
+      <c r="M11" s="52" t="s">
+        <v>197</v>
+      </c>
       <c r="N11" s="53"/>
       <c r="O11" s="54"/>
-      <c r="P11" s="55"/>
+      <c r="P11" s="55" t="n">
+        <f aca="false">200-33.75</f>
+        <v>166.25</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="56" t="n">
@@ -17590,7 +17603,7 @@
         <v>67</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F12" s="58" t="n">
         <v>33.5</v>
@@ -17645,7 +17658,7 @@
         <v>51</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F14" s="58" t="n">
         <v>100</v>
@@ -17672,7 +17685,7 @@
         <v>59</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F15" s="58" t="n">
         <v>184.5</v>
@@ -17699,7 +17712,7 @@
         <v>51</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F16" s="58" t="n">
         <v>19</v>
@@ -17841,10 +17854,16 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="56"/>
-      <c r="C23" s="57"/>
-      <c r="D23" s="57"/>
+      <c r="C23" s="57" t="s">
+        <v>64</v>
+      </c>
+      <c r="D23" s="57" t="s">
+        <v>65</v>
+      </c>
       <c r="E23" s="16"/>
-      <c r="F23" s="58"/>
+      <c r="F23" s="58" t="n">
+        <v>21.85</v>
+      </c>
       <c r="K23" s="12" t="n">
         <f aca="false">SUM(K11:K22)</f>
         <v>1357.68</v>
@@ -17856,10 +17875,16 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="56"/>
-      <c r="C24" s="57"/>
-      <c r="D24" s="57"/>
+      <c r="C24" s="57" t="s">
+        <v>50</v>
+      </c>
+      <c r="D24" s="57" t="s">
+        <v>51</v>
+      </c>
       <c r="E24" s="16"/>
-      <c r="F24" s="58"/>
+      <c r="F24" s="58" t="n">
+        <v>57.5</v>
+      </c>
       <c r="M24" s="52"/>
       <c r="N24" s="53"/>
       <c r="O24" s="54"/>
@@ -17867,10 +17892,16 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="56"/>
-      <c r="C25" s="57"/>
-      <c r="D25" s="57"/>
+      <c r="C25" s="57" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25" s="57" t="s">
+        <v>81</v>
+      </c>
       <c r="E25" s="16"/>
-      <c r="F25" s="58"/>
+      <c r="F25" s="58" t="n">
+        <v>53</v>
+      </c>
       <c r="M25" s="64"/>
       <c r="N25" s="65"/>
       <c r="O25" s="66"/>
@@ -17934,7 +17965,7 @@
       </c>
       <c r="D35" s="71" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C35,$F$11:$F$32)</f>
-        <v>0</v>
+        <v>21.85</v>
       </c>
       <c r="H35" s="72" t="s">
         <v>66</v>
@@ -17947,7 +17978,7 @@
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="73" t="n">
         <f aca="false">SUM(D35:D39)</f>
-        <v>63.2</v>
+        <v>85.05</v>
       </c>
       <c r="C36" s="74" t="s">
         <v>67</v>
@@ -18043,7 +18074,7 @@
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="73" t="n">
         <f aca="false">SUBTOTAL(9,D41:D48)</f>
-        <v>119</v>
+        <v>176.5</v>
       </c>
       <c r="C42" s="74" t="s">
         <v>75</v>
@@ -18112,7 +18143,7 @@
       </c>
       <c r="D46" s="75" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C46,$F$11:$F$32)</f>
-        <v>119</v>
+        <v>176.5</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18141,13 +18172,13 @@
       </c>
       <c r="D50" s="71" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C50,$F$11:$F$32)</f>
-        <v>138</v>
+        <v>191</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="73" t="n">
         <f aca="false">SUM(D50:D56)</f>
-        <v>345.68</v>
+        <v>398.68</v>
       </c>
       <c r="C51" s="74" t="s">
         <v>57</v>
@@ -18546,7 +18577,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -18574,7 +18605,7 @@
       </c>
       <c r="F3" s="11" t="n">
         <f aca="false">SUM(D3,D5,D6,D7,D4)</f>
-        <v>996.740000000001</v>
+        <v>1020.64</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>6</v>
@@ -18589,7 +18620,7 @@
         <v>8</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D4" s="17" t="n">
         <f aca="false">SUM(P10:P25)</f>
@@ -18604,7 +18635,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46221</v>
+        <v>46227</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -18663,14 +18694,14 @@
       <c r="C7" s="33"/>
       <c r="D7" s="34" t="n">
         <f aca="false">Jul!F7</f>
-        <v>996.740000000001</v>
+        <v>1020.64</v>
       </c>
       <c r="E7" s="35" t="s">
         <v>19</v>
       </c>
       <c r="F7" s="36" t="n">
         <f aca="false">F3-F4-F6</f>
-        <v>996.740000000001</v>
+        <v>1020.64</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19620,7 +19651,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -19648,7 +19679,7 @@
       </c>
       <c r="F3" s="11" t="n">
         <f aca="false">SUM(D3,D5,D6,D7,D4)</f>
-        <v>996.740000000001</v>
+        <v>1020.64</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>6</v>
@@ -19676,7 +19707,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46221</v>
+        <v>46227</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -19735,14 +19766,14 @@
       <c r="C7" s="33"/>
       <c r="D7" s="34" t="n">
         <f aca="false">Ago!F7</f>
-        <v>996.740000000001</v>
+        <v>1020.64</v>
       </c>
       <c r="E7" s="35" t="s">
         <v>19</v>
       </c>
       <c r="F7" s="36" t="n">
         <f aca="false">F3-F4-F6</f>
-        <v>996.740000000001</v>
+        <v>1020.64</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/arquivos extras/Planilha.xlsx
+++ b/arquivos extras/Planilha.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Jan" sheetId="1" state="visible" r:id="rId3"/>
@@ -78,7 +78,7 @@
                 <xdr:col>11</xdr:col>
                 <xdr:colOff>-32</xdr:colOff>
                 <xdr:row>13</xdr:row>
-                <xdr:rowOff>20</xdr:rowOff>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -91,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1661" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1678" uniqueCount="268">
   <si>
     <t xml:space="preserve">JAN</t>
   </si>
@@ -702,7 +702,7 @@
     <t xml:space="preserve">AGO</t>
   </si>
   <si>
-    <t xml:space="preserve">minha mãe me mandou 100 reias</t>
+    <t xml:space="preserve">08.08</t>
   </si>
   <si>
     <t xml:space="preserve">SET</t>
@@ -1907,12 +1907,12 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="27" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="27" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -2376,10 +2376,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.0673913855579215"/>
-          <c:y val="0.102173520380517"/>
-          <c:w val="0.748216220254772"/>
-          <c:h val="0.815341080137275"/>
+          <c:x val="0.0673989389524023"/>
+          <c:y val="0.102191978802842"/>
+          <c:w val="0.748187999701113"/>
+          <c:h val="0.815127062507527"/>
         </c:manualLayout>
       </c:layout>
       <c:pie3DChart>
@@ -3022,10 +3022,10 @@
                 <c:formatCode>_-"R$ "* #,##0.00_-;"-R$ "* #,##0.00_-;_-"R$ "* \-??_-;_-@_-</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>60</c:v>
+                  <c:v>90</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>380.9</c:v>
+                  <c:v>397.6</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -3034,16 +3034,16 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>468.64</c:v>
+                  <c:v>541.3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>970</c:v>
+                  <c:v>1220</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2902.36</c:v>
+                  <c:v>3914.36</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -3363,9 +3363,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>45360</xdr:colOff>
+      <xdr:colOff>44280</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>20160</xdr:rowOff>
+      <xdr:rowOff>19080</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3374,7 +3374,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
-        <a:ext cx="9636480" cy="5978880"/>
+        <a:ext cx="9635400" cy="5977800"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46227</v>
+        <v>46242</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -4847,7 +4847,7 @@
       </c>
       <c r="F3" s="11" t="n">
         <f aca="false">SUM(D3,D5,D6,D7,D4)</f>
-        <v>1020.64</v>
+        <v>1008.11</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>6</v>
@@ -4875,7 +4875,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46227</v>
+        <v>46242</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -4934,14 +4934,14 @@
       <c r="C7" s="33"/>
       <c r="D7" s="34" t="n">
         <f aca="false">Set!F7</f>
-        <v>1020.64</v>
+        <v>1008.11</v>
       </c>
       <c r="E7" s="35" t="s">
         <v>19</v>
       </c>
       <c r="F7" s="36" t="n">
         <f aca="false">F3-F4-F6</f>
-        <v>1020.64</v>
+        <v>1008.11</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5006,12 +5006,12 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="47"/>
-      <c r="C11" s="94"/>
-      <c r="D11" s="94"/>
+      <c r="C11" s="93"/>
+      <c r="D11" s="93"/>
       <c r="E11" s="48"/>
       <c r="F11" s="49"/>
       <c r="H11" s="50"/>
-      <c r="I11" s="93"/>
+      <c r="I11" s="94"/>
       <c r="J11" s="51"/>
       <c r="K11" s="46"/>
       <c r="M11" s="52"/>
@@ -5026,7 +5026,7 @@
       <c r="E12" s="16"/>
       <c r="F12" s="58"/>
       <c r="H12" s="59"/>
-      <c r="I12" s="93"/>
+      <c r="I12" s="94"/>
       <c r="J12" s="60"/>
       <c r="K12" s="55"/>
       <c r="M12" s="52"/>
@@ -5041,7 +5041,7 @@
       <c r="E13" s="16"/>
       <c r="F13" s="58"/>
       <c r="H13" s="59"/>
-      <c r="I13" s="93"/>
+      <c r="I13" s="94"/>
       <c r="J13" s="60"/>
       <c r="K13" s="55"/>
       <c r="M13" s="52"/>
@@ -5056,7 +5056,7 @@
       <c r="E14" s="16"/>
       <c r="F14" s="58"/>
       <c r="H14" s="59"/>
-      <c r="I14" s="93"/>
+      <c r="I14" s="94"/>
       <c r="J14" s="60"/>
       <c r="K14" s="55"/>
       <c r="M14" s="52"/>
@@ -5071,7 +5071,7 @@
       <c r="E15" s="16"/>
       <c r="F15" s="58"/>
       <c r="H15" s="59"/>
-      <c r="I15" s="93"/>
+      <c r="I15" s="94"/>
       <c r="J15" s="60"/>
       <c r="K15" s="55"/>
       <c r="M15" s="52"/>
@@ -5086,7 +5086,7 @@
       <c r="E16" s="16"/>
       <c r="F16" s="58"/>
       <c r="H16" s="59"/>
-      <c r="I16" s="93"/>
+      <c r="I16" s="94"/>
       <c r="J16" s="60"/>
       <c r="K16" s="55"/>
       <c r="M16" s="52"/>
@@ -5101,7 +5101,7 @@
       <c r="E17" s="16"/>
       <c r="F17" s="58"/>
       <c r="H17" s="59"/>
-      <c r="I17" s="93"/>
+      <c r="I17" s="94"/>
       <c r="J17" s="60"/>
       <c r="K17" s="55"/>
       <c r="M17" s="52"/>
@@ -5116,7 +5116,7 @@
       <c r="E18" s="16"/>
       <c r="F18" s="58"/>
       <c r="H18" s="59"/>
-      <c r="I18" s="93"/>
+      <c r="I18" s="94"/>
       <c r="J18" s="60"/>
       <c r="K18" s="55"/>
       <c r="M18" s="52"/>
@@ -5131,7 +5131,7 @@
       <c r="E19" s="16"/>
       <c r="F19" s="58"/>
       <c r="H19" s="59"/>
-      <c r="I19" s="93"/>
+      <c r="I19" s="94"/>
       <c r="J19" s="60"/>
       <c r="K19" s="55"/>
       <c r="M19" s="52"/>
@@ -5146,7 +5146,7 @@
       <c r="E20" s="16"/>
       <c r="F20" s="58"/>
       <c r="H20" s="59"/>
-      <c r="I20" s="93"/>
+      <c r="I20" s="94"/>
       <c r="J20" s="60"/>
       <c r="K20" s="55"/>
       <c r="M20" s="52"/>
@@ -5161,7 +5161,7 @@
       <c r="E21" s="16"/>
       <c r="F21" s="58"/>
       <c r="H21" s="59"/>
-      <c r="I21" s="93"/>
+      <c r="I21" s="94"/>
       <c r="J21" s="60"/>
       <c r="K21" s="55"/>
       <c r="M21" s="52"/>
@@ -5919,7 +5919,7 @@
       </c>
       <c r="F3" s="11" t="n">
         <f aca="false">SUM(D3,D5,D6,D7,D4)</f>
-        <v>1020.64</v>
+        <v>1008.11</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>6</v>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46227</v>
+        <v>46242</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -6006,14 +6006,14 @@
       <c r="C7" s="33"/>
       <c r="D7" s="34" t="n">
         <f aca="false">Out!F7</f>
-        <v>1020.64</v>
+        <v>1008.11</v>
       </c>
       <c r="E7" s="35" t="s">
         <v>19</v>
       </c>
       <c r="F7" s="36" t="n">
         <f aca="false">F3-F4-F6</f>
-        <v>1020.64</v>
+        <v>1008.11</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6078,12 +6078,12 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="47"/>
-      <c r="C11" s="94"/>
-      <c r="D11" s="94"/>
+      <c r="C11" s="93"/>
+      <c r="D11" s="93"/>
       <c r="E11" s="48"/>
       <c r="F11" s="49"/>
       <c r="H11" s="50"/>
-      <c r="I11" s="93"/>
+      <c r="I11" s="94"/>
       <c r="J11" s="51"/>
       <c r="K11" s="46"/>
       <c r="M11" s="52"/>
@@ -6098,7 +6098,7 @@
       <c r="E12" s="16"/>
       <c r="F12" s="58"/>
       <c r="H12" s="59"/>
-      <c r="I12" s="93"/>
+      <c r="I12" s="94"/>
       <c r="J12" s="60"/>
       <c r="K12" s="55"/>
       <c r="M12" s="52"/>
@@ -6113,7 +6113,7 @@
       <c r="E13" s="16"/>
       <c r="F13" s="58"/>
       <c r="H13" s="59"/>
-      <c r="I13" s="93"/>
+      <c r="I13" s="94"/>
       <c r="J13" s="60"/>
       <c r="K13" s="55"/>
       <c r="M13" s="52"/>
@@ -6128,7 +6128,7 @@
       <c r="E14" s="16"/>
       <c r="F14" s="58"/>
       <c r="H14" s="59"/>
-      <c r="I14" s="93"/>
+      <c r="I14" s="94"/>
       <c r="J14" s="60"/>
       <c r="K14" s="55"/>
       <c r="M14" s="52"/>
@@ -6143,7 +6143,7 @@
       <c r="E15" s="16"/>
       <c r="F15" s="58"/>
       <c r="H15" s="59"/>
-      <c r="I15" s="93"/>
+      <c r="I15" s="94"/>
       <c r="J15" s="60"/>
       <c r="K15" s="55"/>
       <c r="M15" s="52"/>
@@ -6158,7 +6158,7 @@
       <c r="E16" s="16"/>
       <c r="F16" s="58"/>
       <c r="H16" s="59"/>
-      <c r="I16" s="93"/>
+      <c r="I16" s="94"/>
       <c r="J16" s="60"/>
       <c r="K16" s="55"/>
       <c r="M16" s="52"/>
@@ -6173,7 +6173,7 @@
       <c r="E17" s="16"/>
       <c r="F17" s="58"/>
       <c r="H17" s="59"/>
-      <c r="I17" s="93"/>
+      <c r="I17" s="94"/>
       <c r="J17" s="60"/>
       <c r="K17" s="55"/>
       <c r="M17" s="52"/>
@@ -6188,7 +6188,7 @@
       <c r="E18" s="16"/>
       <c r="F18" s="58"/>
       <c r="H18" s="59"/>
-      <c r="I18" s="93"/>
+      <c r="I18" s="94"/>
       <c r="J18" s="60"/>
       <c r="K18" s="55"/>
       <c r="M18" s="52"/>
@@ -6203,7 +6203,7 @@
       <c r="E19" s="16"/>
       <c r="F19" s="58"/>
       <c r="H19" s="59"/>
-      <c r="I19" s="93"/>
+      <c r="I19" s="94"/>
       <c r="J19" s="60"/>
       <c r="K19" s="55"/>
       <c r="M19" s="52"/>
@@ -6218,7 +6218,7 @@
       <c r="E20" s="16"/>
       <c r="F20" s="58"/>
       <c r="H20" s="59"/>
-      <c r="I20" s="93"/>
+      <c r="I20" s="94"/>
       <c r="J20" s="60"/>
       <c r="K20" s="55"/>
       <c r="M20" s="52"/>
@@ -6233,7 +6233,7 @@
       <c r="E21" s="16"/>
       <c r="F21" s="58"/>
       <c r="H21" s="59"/>
-      <c r="I21" s="93"/>
+      <c r="I21" s="94"/>
       <c r="J21" s="60"/>
       <c r="K21" s="55"/>
       <c r="M21" s="52"/>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="F3" s="11" t="n">
         <f aca="false">SUM(D3,D5,D6,D7,D4)</f>
-        <v>1020.64</v>
+        <v>1008.11</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>6</v>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46227</v>
+        <v>46242</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -7081,14 +7081,14 @@
       <c r="C7" s="33"/>
       <c r="D7" s="34" t="n">
         <f aca="false">Nov!F7</f>
-        <v>1020.64</v>
+        <v>1008.11</v>
       </c>
       <c r="E7" s="35" t="s">
         <v>19</v>
       </c>
       <c r="F7" s="36" t="n">
         <f aca="false">F3-F4-F6</f>
-        <v>1020.64</v>
+        <v>1008.11</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7153,12 +7153,12 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="47"/>
-      <c r="C11" s="94"/>
-      <c r="D11" s="94"/>
+      <c r="C11" s="93"/>
+      <c r="D11" s="93"/>
       <c r="E11" s="48"/>
       <c r="F11" s="49"/>
       <c r="H11" s="50"/>
-      <c r="I11" s="93"/>
+      <c r="I11" s="94"/>
       <c r="J11" s="51"/>
       <c r="K11" s="46"/>
       <c r="M11" s="52"/>
@@ -7173,7 +7173,7 @@
       <c r="E12" s="16"/>
       <c r="F12" s="58"/>
       <c r="H12" s="59"/>
-      <c r="I12" s="93"/>
+      <c r="I12" s="94"/>
       <c r="J12" s="60"/>
       <c r="K12" s="55"/>
       <c r="M12" s="52"/>
@@ -7188,7 +7188,7 @@
       <c r="E13" s="16"/>
       <c r="F13" s="58"/>
       <c r="H13" s="59"/>
-      <c r="I13" s="93"/>
+      <c r="I13" s="94"/>
       <c r="J13" s="60"/>
       <c r="K13" s="55"/>
       <c r="M13" s="52"/>
@@ -7203,7 +7203,7 @@
       <c r="E14" s="16"/>
       <c r="F14" s="58"/>
       <c r="H14" s="59"/>
-      <c r="I14" s="93"/>
+      <c r="I14" s="94"/>
       <c r="J14" s="60"/>
       <c r="K14" s="55"/>
       <c r="M14" s="52"/>
@@ -7218,7 +7218,7 @@
       <c r="E15" s="16"/>
       <c r="F15" s="58"/>
       <c r="H15" s="59"/>
-      <c r="I15" s="93"/>
+      <c r="I15" s="94"/>
       <c r="J15" s="60"/>
       <c r="K15" s="55"/>
       <c r="M15" s="52"/>
@@ -7233,7 +7233,7 @@
       <c r="E16" s="16"/>
       <c r="F16" s="58"/>
       <c r="H16" s="59"/>
-      <c r="I16" s="93"/>
+      <c r="I16" s="94"/>
       <c r="J16" s="60"/>
       <c r="K16" s="55"/>
       <c r="M16" s="52"/>
@@ -7248,7 +7248,7 @@
       <c r="E17" s="16"/>
       <c r="F17" s="58"/>
       <c r="H17" s="59"/>
-      <c r="I17" s="93"/>
+      <c r="I17" s="94"/>
       <c r="J17" s="60"/>
       <c r="K17" s="55"/>
       <c r="M17" s="52"/>
@@ -7263,7 +7263,7 @@
       <c r="E18" s="16"/>
       <c r="F18" s="58"/>
       <c r="H18" s="59"/>
-      <c r="I18" s="93"/>
+      <c r="I18" s="94"/>
       <c r="J18" s="60"/>
       <c r="K18" s="55"/>
       <c r="M18" s="52"/>
@@ -7278,7 +7278,7 @@
       <c r="E19" s="16"/>
       <c r="F19" s="58"/>
       <c r="H19" s="59"/>
-      <c r="I19" s="93"/>
+      <c r="I19" s="94"/>
       <c r="J19" s="60"/>
       <c r="K19" s="55"/>
       <c r="M19" s="52"/>
@@ -7293,7 +7293,7 @@
       <c r="E20" s="16"/>
       <c r="F20" s="58"/>
       <c r="H20" s="59"/>
-      <c r="I20" s="93"/>
+      <c r="I20" s="94"/>
       <c r="J20" s="60"/>
       <c r="K20" s="55"/>
       <c r="M20" s="52"/>
@@ -7308,7 +7308,7 @@
       <c r="E21" s="16"/>
       <c r="F21" s="58"/>
       <c r="H21" s="59"/>
-      <c r="I21" s="93"/>
+      <c r="I21" s="94"/>
       <c r="J21" s="60"/>
       <c r="K21" s="55"/>
       <c r="M21" s="52"/>
@@ -8119,27 +8119,27 @@
       </c>
       <c r="J3" s="107" t="n">
         <f aca="false">Ago!$F$3</f>
-        <v>1020.64</v>
+        <v>2737.14</v>
       </c>
       <c r="K3" s="107" t="n">
         <f aca="false">Set!$F$3</f>
-        <v>1020.64</v>
+        <v>1008.11</v>
       </c>
       <c r="L3" s="107" t="n">
         <f aca="false">Out!$F$3</f>
-        <v>1020.64</v>
+        <v>1008.11</v>
       </c>
       <c r="M3" s="107" t="n">
         <f aca="false">Nov!$F$3</f>
-        <v>1020.64</v>
+        <v>1008.11</v>
       </c>
       <c r="N3" s="108" t="n">
         <f aca="false">Dez!$F$3</f>
-        <v>1020.64</v>
+        <v>1008.11</v>
       </c>
       <c r="O3" s="108" t="n">
         <f aca="false">SUM(C3:N3)</f>
-        <v>24515.82</v>
+        <v>26182.2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8172,11 +8172,11 @@
       </c>
       <c r="I4" s="110" t="n">
         <f aca="false">Jul!$F$4</f>
-        <v>912.93</v>
+        <v>1736.43</v>
       </c>
       <c r="J4" s="110" t="n">
         <f aca="false">Ago!$F$4</f>
-        <v>0</v>
+        <v>312.67</v>
       </c>
       <c r="K4" s="110" t="n">
         <f aca="false">Set!$F$4</f>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="O4" s="111" t="n">
         <f aca="false">SUM(C4:N4)</f>
-        <v>8534.28</v>
+        <v>9670.45</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="J5" s="112" t="n">
         <f aca="false">Ago!$F$6</f>
-        <v>0</v>
+        <v>1416.36</v>
       </c>
       <c r="K5" s="112" t="n">
         <f aca="false">Set!$F$6</f>
@@ -8253,7 +8253,7 @@
       </c>
       <c r="O5" s="113" t="n">
         <f aca="false">SUM(C5:N5)</f>
-        <v>4996.9</v>
+        <v>6413.26</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8290,7 +8290,7 @@
       </c>
       <c r="J6" s="114" t="n">
         <f aca="false">Ago!$L$3</f>
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="K6" s="114" t="n">
         <f aca="false">Set!$L$3</f>
@@ -8310,7 +8310,7 @@
       </c>
       <c r="O6" s="116" t="n">
         <f aca="false">SUM(C6:N6)</f>
-        <v>4855.19</v>
+        <v>5195.19</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8347,7 +8347,7 @@
       </c>
       <c r="J7" s="117" t="n">
         <f aca="false">Ago!$L$4</f>
-        <v>0</v>
+        <v>522.75</v>
       </c>
       <c r="K7" s="117" t="n">
         <f aca="false">Set!$L$4</f>
@@ -8367,7 +8367,7 @@
       </c>
       <c r="O7" s="119" t="n">
         <f aca="false">SUM(C7:N7)</f>
-        <v>983.93</v>
+        <v>1506.68</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8400,11 +8400,11 @@
       </c>
       <c r="I8" s="120" t="n">
         <f aca="false">I4+I5</f>
-        <v>2270.61</v>
+        <v>3094.11</v>
       </c>
       <c r="J8" s="120" t="n">
         <f aca="false">J4+J5</f>
-        <v>0</v>
+        <v>1729.03</v>
       </c>
       <c r="K8" s="120" t="n">
         <f aca="false">K4+K5</f>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="O8" s="121" t="n">
         <f aca="false">SUM(C8:N8)</f>
-        <v>13531.18</v>
+        <v>16083.71</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8457,31 +8457,31 @@
       </c>
       <c r="I9" s="122" t="n">
         <f aca="false">I3-I8</f>
-        <v>1020.64</v>
+        <v>197.14</v>
       </c>
       <c r="J9" s="122" t="n">
         <f aca="false">J3-J8</f>
-        <v>1020.64</v>
+        <v>1008.11</v>
       </c>
       <c r="K9" s="122" t="n">
         <f aca="false">K3-K8</f>
-        <v>1020.64</v>
+        <v>1008.11</v>
       </c>
       <c r="L9" s="122" t="n">
         <f aca="false">L3-L8</f>
-        <v>1020.64</v>
+        <v>1008.11</v>
       </c>
       <c r="M9" s="122" t="n">
         <f aca="false">M3-M8</f>
-        <v>1020.64</v>
+        <v>1008.11</v>
       </c>
       <c r="N9" s="123" t="n">
         <f aca="false">N3-N8</f>
-        <v>1020.64</v>
+        <v>1008.11</v>
       </c>
       <c r="O9" s="123" t="n">
         <f aca="false">N9</f>
-        <v>1020.64</v>
+        <v>1008.11</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8680,7 +8680,7 @@
       </c>
       <c r="I17" s="133" t="n">
         <f aca="false">Jul!$B$42</f>
-        <v>176.5</v>
+        <v>245.5</v>
       </c>
       <c r="J17" s="134" t="n">
         <f aca="false">Ago!$B$42</f>
@@ -8704,7 +8704,7 @@
       </c>
       <c r="O17" s="136" t="n">
         <f aca="false">SUM(C17:N17)</f>
-        <v>589.08</v>
+        <v>658.08</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="J18" s="134" t="n">
         <f aca="false">Ago!$B$51</f>
-        <v>0</v>
+        <v>265.82</v>
       </c>
       <c r="K18" s="133" t="n">
         <f aca="false">Set!$B$51</f>
@@ -8761,7 +8761,7 @@
       </c>
       <c r="O18" s="136" t="n">
         <f aca="false">SUM(C18:N18)</f>
-        <v>968.27</v>
+        <v>1234.09</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8794,7 +8794,7 @@
       </c>
       <c r="I19" s="133" t="n">
         <f aca="false">Jul!$B$59</f>
-        <v>73</v>
+        <v>823</v>
       </c>
       <c r="J19" s="134" t="n">
         <f aca="false">Ago!$B$59</f>
@@ -8818,7 +8818,7 @@
       </c>
       <c r="O19" s="136" t="n">
         <f aca="false">SUM(C19:N19)</f>
-        <v>747.84</v>
+        <v>1497.84</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9075,7 +9075,7 @@
       </c>
       <c r="G28" s="71" t="n">
         <f aca="false">SUBTOTAL(9,Jan!I35,Fev!I35,Mar!I35,Abr!I35,Mai!I35,Jun!I35,Jul!I35,Ago!I35,Set!I35,Out!I35,Nov!I35,Dez!I35)</f>
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="I28" s="144" t="s">
         <v>226</v>
@@ -9101,7 +9101,7 @@
       </c>
       <c r="G29" s="75" t="n">
         <f aca="false">SUBTOTAL(9,Jan!I36,Fev!I36,Mar!I36,Abr!I36,Mai!I36,Jun!I36,Jul!I36,Ago!I36,Set!I36,Out!I36,Nov!I36,Dez!I36)</f>
-        <v>380.9</v>
+        <v>397.6</v>
       </c>
       <c r="I29" s="146" t="s">
         <v>227</v>
@@ -9190,7 +9190,7 @@
       </c>
       <c r="G32" s="75" t="n">
         <f aca="false">SUBTOTAL(9,Jan!I39,Fev!I39,Mar!I39,Abr!I39,Mai!I39,Jun!I39,Jul!I39,Ago!I39,Set!I39,Out!I39,Nov!I39,Dez!I39)</f>
-        <v>468.64</v>
+        <v>541.3</v>
       </c>
       <c r="I32" s="152" t="s">
         <v>236</v>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="G33" s="75" t="n">
         <f aca="false">SUBTOTAL(9,Jan!I40,Fev!I40,Mar!I40,Abr!I40,Mai!I40,Jun!I40,Jul!I40,Ago!I40,Set!I40,Out!I40,Nov!I40,Dez!I40)</f>
-        <v>970</v>
+        <v>1220</v>
       </c>
       <c r="H33" s="100" t="s">
         <v>238</v>
@@ -9250,7 +9250,7 @@
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="73" t="n">
         <f aca="false">SUM(D33:D40)</f>
-        <v>604.39</v>
+        <v>673.39</v>
       </c>
       <c r="C34" s="74" t="s">
         <v>75</v>
@@ -9300,7 +9300,7 @@
       </c>
       <c r="G35" s="75" t="n">
         <f aca="false">SUBTOTAL(9,Jan!I42,Fev!I42,Mar!I42,Abr!I42,Mai!I42,Jun!I42,Jul!I42,Ago!I42,Set!I42,Out!I42,Nov!I42,Dez!I42)</f>
-        <v>2902.36</v>
+        <v>3914.36</v>
       </c>
       <c r="I35" s="152" t="s">
         <v>242</v>
@@ -9389,7 +9389,7 @@
       </c>
       <c r="D38" s="75" t="n">
         <f aca="false">SUBTOTAL(9,Fev!D46,Fev!D46,Mar!D46,Abr!D46,Mai!D46,Jun!D46,Jul!D46,Ago!D46,Set!D46,Out!D46,Nov!D46,Dez!D46)</f>
-        <v>401.51</v>
+        <v>470.51</v>
       </c>
       <c r="F38" s="81"/>
       <c r="G38" s="78" t="n">
@@ -9530,7 +9530,7 @@
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="73" t="n">
         <f aca="false">SUM(D43:D49)</f>
-        <v>1100.56</v>
+        <v>1366.38</v>
       </c>
       <c r="C44" s="74" t="s">
         <v>57</v>
@@ -9575,7 +9575,7 @@
       </c>
       <c r="D46" s="75" t="n">
         <f aca="false">SUBTOTAL(9,Fev!D53,Fev!D53,Mar!D53,Abr!D53,Mai!D53,Jun!D53,Jul!D53,Ago!D53,Set!D53,Out!D53,Nov!D53,Dez!D53)</f>
-        <v>142</v>
+        <v>407.82</v>
       </c>
       <c r="I46" s="161" t="s">
         <v>220</v>
@@ -9628,7 +9628,7 @@
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="73" t="n">
         <f aca="false">SUM(D51:D57)</f>
-        <v>972.18</v>
+        <v>1722.18</v>
       </c>
       <c r="C52" s="74" t="s">
         <v>40</v>
@@ -9662,7 +9662,7 @@
       </c>
       <c r="D55" s="75" t="n">
         <f aca="false">SUBTOTAL(9,Fev!D62,Fev!D62,Mar!D62,Abr!D62,Mai!D62,Jun!D62,Jul!D62,Ago!D62,Set!D62,Out!D62,Nov!D62,Dez!D62)</f>
-        <v>480.34</v>
+        <v>1230.34</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11192,7 +11192,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46227</v>
+        <v>46242</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -12385,7 +12385,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46227</v>
+        <v>46242</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -13593,7 +13593,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46227</v>
+        <v>46242</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -14876,7 +14876,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46227</v>
+        <v>46242</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>150</v>
@@ -16162,7 +16162,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46227</v>
+        <v>46242</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>170</v>
@@ -17397,12 +17397,6 @@
       <c r="L3" s="14" t="n">
         <v>809.19</v>
       </c>
-      <c r="M3" s="1" t="n">
-        <v>601</v>
-      </c>
-      <c r="N3" s="1" t="n">
-        <v>77</v>
-      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="15" t="s">
@@ -17418,11 +17412,11 @@
       </c>
       <c r="F4" s="19" t="n">
         <f aca="false">SUM(F11:F32)</f>
-        <v>912.93</v>
+        <v>1736.43</v>
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46227</v>
+        <v>46242</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -17467,14 +17461,14 @@
         <v>1357.68</v>
       </c>
       <c r="I6" s="29" t="n">
-        <v>46221</v>
+        <v>46233</v>
       </c>
       <c r="K6" s="30" t="s">
         <v>18</v>
       </c>
       <c r="L6" s="92" t="n">
         <f aca="false">217-SUM(F16:F32)</f>
-        <v>-175.05</v>
+        <v>-998.55</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17491,7 +17485,7 @@
       </c>
       <c r="F7" s="36" t="n">
         <f aca="false">F3-F4-F6</f>
-        <v>1020.64</v>
+        <v>197.14</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17909,24 +17903,39 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="56"/>
-      <c r="C26" s="57"/>
-      <c r="D26" s="57"/>
+      <c r="C26" s="57" t="s">
+        <v>50</v>
+      </c>
+      <c r="D26" s="57" t="s">
+        <v>51</v>
+      </c>
       <c r="E26" s="16"/>
-      <c r="F26" s="58"/>
+      <c r="F26" s="58" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="56"/>
-      <c r="C27" s="57"/>
-      <c r="D27" s="57"/>
+      <c r="C27" s="57" t="s">
+        <v>39</v>
+      </c>
+      <c r="D27" s="57" t="s">
+        <v>47</v>
+      </c>
       <c r="E27" s="16"/>
-      <c r="F27" s="58"/>
+      <c r="F27" s="58" t="n">
+        <v>750</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="56"/>
       <c r="C28" s="57"/>
       <c r="D28" s="57"/>
       <c r="E28" s="16"/>
-      <c r="F28" s="58"/>
+      <c r="F28" s="58" t="n">
+        <f aca="false">4.5</f>
+        <v>4.5</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="56"/>
@@ -18074,7 +18083,7 @@
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="73" t="n">
         <f aca="false">SUBTOTAL(9,D41:D48)</f>
-        <v>176.5</v>
+        <v>245.5</v>
       </c>
       <c r="C42" s="74" t="s">
         <v>75</v>
@@ -18143,7 +18152,7 @@
       </c>
       <c r="D46" s="75" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C46,$F$11:$F$32)</f>
-        <v>176.5</v>
+        <v>245.5</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18249,7 +18258,7 @@
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="73" t="n">
         <f aca="false">SUM(D58:D64)</f>
-        <v>73</v>
+        <v>823</v>
       </c>
       <c r="C59" s="74" t="s">
         <v>40</v>
@@ -18283,7 +18292,7 @@
       </c>
       <c r="D62" s="75" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C62,$F$11:$F$32)</f>
-        <v>58</v>
+        <v>808</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18571,7 +18580,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="13.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="18.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="34.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="8.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="10.35"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="13" style="1" width="12"/>
   </cols>
   <sheetData>
@@ -18599,13 +18608,15 @@
         <v>4</v>
       </c>
       <c r="C3" s="8"/>
-      <c r="D3" s="9"/>
+      <c r="D3" s="9" t="n">
+        <v>2540</v>
+      </c>
       <c r="E3" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F3" s="11" t="n">
         <f aca="false">SUM(D3,D5,D6,D7,D4)</f>
-        <v>1020.64</v>
+        <v>2737.14</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>6</v>
@@ -18613,15 +18624,15 @@
       <c r="K3" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="L3" s="14"/>
+      <c r="L3" s="14" t="n">
+        <v>340</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="16" t="s">
-        <v>203</v>
-      </c>
+      <c r="C4" s="16"/>
       <c r="D4" s="17" t="n">
         <f aca="false">SUM(P10:P25)</f>
         <v>0</v>
@@ -18631,16 +18642,18 @@
       </c>
       <c r="F4" s="19" t="n">
         <f aca="false">SUM(F11:F32)</f>
-        <v>0</v>
+        <v>312.67</v>
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46227</v>
+        <v>46242</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="L4" s="14"/>
+      <c r="L4" s="14" t="n">
+        <v>522.75</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="21" t="s">
@@ -18677,15 +18690,18 @@
       </c>
       <c r="F6" s="28" t="n">
         <f aca="false">SUM(K11:K22)</f>
-        <v>0</v>
-      </c>
-      <c r="I6" s="29" t="n">
-        <v>45879</v>
+        <v>1416.36</v>
+      </c>
+      <c r="I6" s="29" t="s">
+        <v>203</v>
       </c>
       <c r="K6" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="L6" s="31"/>
+      <c r="L6" s="92" t="n">
+        <f aca="false">246-SUM(F15:F32)</f>
+        <v>246</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="32" t="s">
@@ -18694,14 +18710,14 @@
       <c r="C7" s="33"/>
       <c r="D7" s="34" t="n">
         <f aca="false">Jul!F7</f>
-        <v>1020.64</v>
+        <v>197.14</v>
       </c>
       <c r="E7" s="35" t="s">
         <v>19</v>
       </c>
       <c r="F7" s="36" t="n">
         <f aca="false">F3-F4-F6</f>
-        <v>1020.64</v>
+        <v>1008.11</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18766,14 +18782,24 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="47"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
+      <c r="C11" s="57" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="57" t="s">
+        <v>55</v>
+      </c>
       <c r="E11" s="48"/>
-      <c r="F11" s="49"/>
+      <c r="F11" s="49" t="n">
+        <v>20</v>
+      </c>
       <c r="H11" s="50"/>
-      <c r="I11" s="93"/>
+      <c r="I11" s="51" t="s">
+        <v>129</v>
+      </c>
       <c r="J11" s="51"/>
-      <c r="K11" s="46"/>
+      <c r="K11" s="46" t="n">
+        <v>35</v>
+      </c>
       <c r="M11" s="52"/>
       <c r="N11" s="53"/>
       <c r="O11" s="54"/>
@@ -18781,14 +18807,22 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="56"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
+      <c r="C12" s="57" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" s="57"/>
       <c r="E12" s="16"/>
-      <c r="F12" s="58"/>
+      <c r="F12" s="58" t="n">
+        <v>4</v>
+      </c>
       <c r="H12" s="59"/>
-      <c r="I12" s="93"/>
+      <c r="I12" s="51" t="s">
+        <v>49</v>
+      </c>
       <c r="J12" s="60"/>
-      <c r="K12" s="55"/>
+      <c r="K12" s="55" t="n">
+        <v>72.66</v>
+      </c>
       <c r="M12" s="52"/>
       <c r="N12" s="53"/>
       <c r="O12" s="54"/>
@@ -18796,14 +18830,24 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="56"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
+      <c r="C13" s="57" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" s="57" t="s">
+        <v>33</v>
+      </c>
       <c r="E13" s="16"/>
-      <c r="F13" s="58"/>
+      <c r="F13" s="58" t="n">
+        <v>265.82</v>
+      </c>
       <c r="H13" s="59"/>
-      <c r="I13" s="93"/>
+      <c r="I13" s="51" t="s">
+        <v>42</v>
+      </c>
       <c r="J13" s="60"/>
-      <c r="K13" s="55"/>
+      <c r="K13" s="55" t="n">
+        <v>1012</v>
+      </c>
       <c r="M13" s="52"/>
       <c r="N13" s="53"/>
       <c r="O13" s="54"/>
@@ -18811,14 +18855,24 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="56"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
+      <c r="C14" s="57" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="57" t="s">
+        <v>55</v>
+      </c>
       <c r="E14" s="16"/>
-      <c r="F14" s="58"/>
+      <c r="F14" s="58" t="n">
+        <v>22.85</v>
+      </c>
       <c r="H14" s="59"/>
-      <c r="I14" s="93"/>
+      <c r="I14" s="51" t="s">
+        <v>72</v>
+      </c>
       <c r="J14" s="60"/>
-      <c r="K14" s="55"/>
+      <c r="K14" s="55" t="n">
+        <v>250</v>
+      </c>
       <c r="M14" s="52"/>
       <c r="N14" s="53"/>
       <c r="O14" s="54"/>
@@ -18826,14 +18880,18 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="56"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
+      <c r="C15" s="57"/>
+      <c r="D15" s="57"/>
       <c r="E15" s="16"/>
       <c r="F15" s="58"/>
       <c r="H15" s="59"/>
-      <c r="I15" s="93"/>
+      <c r="I15" s="51" t="s">
+        <v>66</v>
+      </c>
       <c r="J15" s="60"/>
-      <c r="K15" s="55"/>
+      <c r="K15" s="55" t="n">
+        <v>30</v>
+      </c>
       <c r="M15" s="52"/>
       <c r="N15" s="53"/>
       <c r="O15" s="54"/>
@@ -18841,14 +18899,19 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="56"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
+      <c r="C16" s="57"/>
+      <c r="D16" s="57"/>
       <c r="E16" s="16"/>
       <c r="F16" s="58"/>
       <c r="H16" s="59"/>
-      <c r="I16" s="93"/>
+      <c r="I16" s="51" t="s">
+        <v>35</v>
+      </c>
       <c r="J16" s="60"/>
-      <c r="K16" s="55"/>
+      <c r="K16" s="55" t="n">
+        <f aca="false">10+6.7</f>
+        <v>16.7</v>
+      </c>
       <c r="M16" s="52"/>
       <c r="N16" s="53"/>
       <c r="O16" s="54"/>
@@ -18856,12 +18919,12 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="56"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
+      <c r="C17" s="57"/>
+      <c r="D17" s="57"/>
       <c r="E17" s="16"/>
       <c r="F17" s="58"/>
       <c r="H17" s="59"/>
-      <c r="I17" s="93"/>
+      <c r="I17" s="51"/>
       <c r="J17" s="60"/>
       <c r="K17" s="55"/>
       <c r="M17" s="52"/>
@@ -18871,12 +18934,12 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="56"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
+      <c r="C18" s="57"/>
+      <c r="D18" s="57"/>
       <c r="E18" s="16"/>
       <c r="F18" s="58"/>
       <c r="H18" s="59"/>
-      <c r="I18" s="93"/>
+      <c r="I18" s="51"/>
       <c r="J18" s="60"/>
       <c r="K18" s="55"/>
       <c r="M18" s="52"/>
@@ -18886,12 +18949,12 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="56"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="57"/>
       <c r="E19" s="16"/>
       <c r="F19" s="58"/>
       <c r="H19" s="59"/>
-      <c r="I19" s="93"/>
+      <c r="I19" s="51"/>
       <c r="J19" s="60"/>
       <c r="K19" s="55"/>
       <c r="M19" s="52"/>
@@ -18901,12 +18964,12 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="56"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
+      <c r="C20" s="57"/>
+      <c r="D20" s="57"/>
       <c r="E20" s="16"/>
       <c r="F20" s="58"/>
       <c r="H20" s="59"/>
-      <c r="I20" s="93"/>
+      <c r="I20" s="51"/>
       <c r="J20" s="60"/>
       <c r="K20" s="55"/>
       <c r="M20" s="52"/>
@@ -18916,12 +18979,12 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="56"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
+      <c r="C21" s="57"/>
+      <c r="D21" s="57"/>
       <c r="E21" s="16"/>
       <c r="F21" s="58"/>
       <c r="H21" s="59"/>
-      <c r="I21" s="93"/>
+      <c r="I21" s="51"/>
       <c r="J21" s="60"/>
       <c r="K21" s="55"/>
       <c r="M21" s="52"/>
@@ -18931,8 +18994,8 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="56"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
+      <c r="C22" s="57"/>
+      <c r="D22" s="57"/>
       <c r="E22" s="16"/>
       <c r="F22" s="58"/>
       <c r="H22" s="61"/>
@@ -18946,13 +19009,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="56"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
+      <c r="C23" s="57"/>
+      <c r="D23" s="57"/>
       <c r="E23" s="16"/>
       <c r="F23" s="58"/>
       <c r="K23" s="12" t="n">
         <f aca="false">SUM(K11:K22)</f>
-        <v>0</v>
+        <v>1416.36</v>
       </c>
       <c r="M23" s="52"/>
       <c r="N23" s="53"/>
@@ -18961,8 +19024,8 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="56"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
+      <c r="C24" s="57"/>
+      <c r="D24" s="57"/>
       <c r="E24" s="16"/>
       <c r="F24" s="58"/>
       <c r="M24" s="52"/>
@@ -18972,8 +19035,8 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="56"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
+      <c r="C25" s="57"/>
+      <c r="D25" s="57"/>
       <c r="E25" s="16"/>
       <c r="F25" s="58"/>
       <c r="M25" s="64"/>
@@ -18983,43 +19046,43 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="56"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
+      <c r="C26" s="57"/>
+      <c r="D26" s="57"/>
       <c r="E26" s="16"/>
       <c r="F26" s="58"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="56"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
+      <c r="C27" s="57"/>
+      <c r="D27" s="57"/>
       <c r="E27" s="16"/>
       <c r="F27" s="58"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="56"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
+      <c r="C28" s="57"/>
+      <c r="D28" s="57"/>
       <c r="E28" s="16"/>
       <c r="F28" s="58"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="56"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="16"/>
+      <c r="C29" s="57"/>
+      <c r="D29" s="57"/>
       <c r="E29" s="16"/>
       <c r="F29" s="58"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="56"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
+      <c r="C30" s="57"/>
+      <c r="D30" s="57"/>
       <c r="E30" s="16"/>
       <c r="F30" s="58"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="56"/>
-      <c r="C31" s="16"/>
-      <c r="D31" s="16"/>
+      <c r="C31" s="57"/>
+      <c r="D31" s="57"/>
       <c r="E31" s="16"/>
       <c r="F31" s="58"/>
     </row>
@@ -19046,7 +19109,7 @@
       </c>
       <c r="I35" s="71" t="n">
         <f aca="false">SUMIF($I$11:$I$22,H35,$K$11:$K$22)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19066,7 +19129,7 @@
       </c>
       <c r="I36" s="75" t="n">
         <f aca="false">SUMIF($I$11:$I$22,H36,$K$11:$K$22)</f>
-        <v>0</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19112,7 +19175,7 @@
       </c>
       <c r="I39" s="75" t="n">
         <f aca="false">SUMIF($I$11:$I$22,H39,$K$11:$K$22)</f>
-        <v>0</v>
+        <v>72.66</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19123,7 +19186,7 @@
       </c>
       <c r="I40" s="75" t="n">
         <f aca="false">SUMIF($I$11:$I$22,H40,$K$11:$K$22)</f>
-        <v>0</v>
+        <v>250</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19162,7 +19225,7 @@
       </c>
       <c r="I42" s="75" t="n">
         <f aca="false">SUMIF($I$11:$I$22,H42,$K$11:$K$22)</f>
-        <v>0</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19252,7 +19315,7 @@
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="73" t="n">
         <f aca="false">SUM(D50:D56)</f>
-        <v>0</v>
+        <v>265.82</v>
       </c>
       <c r="C51" s="74" t="s">
         <v>57</v>
@@ -19277,7 +19340,7 @@
       </c>
       <c r="D53" s="75" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C53,$F$11:$F$32)</f>
-        <v>0</v>
+        <v>265.82</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19679,7 +19742,7 @@
       </c>
       <c r="F3" s="11" t="n">
         <f aca="false">SUM(D3,D5,D6,D7,D4)</f>
-        <v>1020.64</v>
+        <v>1008.11</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>6</v>
@@ -19707,7 +19770,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46227</v>
+        <v>46242</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -19766,14 +19829,14 @@
       <c r="C7" s="33"/>
       <c r="D7" s="34" t="n">
         <f aca="false">Ago!F7</f>
-        <v>1020.64</v>
+        <v>1008.11</v>
       </c>
       <c r="E7" s="35" t="s">
         <v>19</v>
       </c>
       <c r="F7" s="36" t="n">
         <f aca="false">F3-F4-F6</f>
-        <v>1020.64</v>
+        <v>1008.11</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19838,12 +19901,12 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="47"/>
-      <c r="C11" s="94"/>
-      <c r="D11" s="94"/>
+      <c r="C11" s="93"/>
+      <c r="D11" s="93"/>
       <c r="E11" s="48"/>
       <c r="F11" s="49"/>
       <c r="H11" s="50"/>
-      <c r="I11" s="93"/>
+      <c r="I11" s="94"/>
       <c r="J11" s="51"/>
       <c r="K11" s="46"/>
       <c r="M11" s="52"/>
@@ -19858,7 +19921,7 @@
       <c r="E12" s="16"/>
       <c r="F12" s="58"/>
       <c r="H12" s="59"/>
-      <c r="I12" s="93"/>
+      <c r="I12" s="94"/>
       <c r="J12" s="60"/>
       <c r="K12" s="55"/>
       <c r="M12" s="52"/>
@@ -19873,7 +19936,7 @@
       <c r="E13" s="16"/>
       <c r="F13" s="58"/>
       <c r="H13" s="59"/>
-      <c r="I13" s="93"/>
+      <c r="I13" s="94"/>
       <c r="J13" s="60"/>
       <c r="K13" s="55"/>
       <c r="M13" s="52"/>
@@ -19888,7 +19951,7 @@
       <c r="E14" s="16"/>
       <c r="F14" s="58"/>
       <c r="H14" s="59"/>
-      <c r="I14" s="93"/>
+      <c r="I14" s="94"/>
       <c r="J14" s="60"/>
       <c r="K14" s="55"/>
       <c r="M14" s="52"/>
@@ -19903,7 +19966,7 @@
       <c r="E15" s="16"/>
       <c r="F15" s="58"/>
       <c r="H15" s="59"/>
-      <c r="I15" s="93"/>
+      <c r="I15" s="94"/>
       <c r="J15" s="60"/>
       <c r="K15" s="55"/>
       <c r="M15" s="52"/>
@@ -19918,7 +19981,7 @@
       <c r="E16" s="16"/>
       <c r="F16" s="58"/>
       <c r="H16" s="59"/>
-      <c r="I16" s="93"/>
+      <c r="I16" s="94"/>
       <c r="J16" s="60"/>
       <c r="K16" s="55"/>
       <c r="M16" s="52"/>
@@ -19933,7 +19996,7 @@
       <c r="E17" s="16"/>
       <c r="F17" s="58"/>
       <c r="H17" s="59"/>
-      <c r="I17" s="93"/>
+      <c r="I17" s="94"/>
       <c r="J17" s="60"/>
       <c r="K17" s="55"/>
       <c r="M17" s="52"/>
@@ -19948,7 +20011,7 @@
       <c r="E18" s="16"/>
       <c r="F18" s="58"/>
       <c r="H18" s="59"/>
-      <c r="I18" s="93"/>
+      <c r="I18" s="94"/>
       <c r="J18" s="60"/>
       <c r="K18" s="55"/>
       <c r="M18" s="52"/>
@@ -19963,7 +20026,7 @@
       <c r="E19" s="16"/>
       <c r="F19" s="58"/>
       <c r="H19" s="59"/>
-      <c r="I19" s="93"/>
+      <c r="I19" s="94"/>
       <c r="J19" s="60"/>
       <c r="K19" s="55"/>
       <c r="M19" s="52"/>
@@ -19978,7 +20041,7 @@
       <c r="E20" s="16"/>
       <c r="F20" s="58"/>
       <c r="H20" s="59"/>
-      <c r="I20" s="93"/>
+      <c r="I20" s="94"/>
       <c r="J20" s="60"/>
       <c r="K20" s="55"/>
       <c r="M20" s="52"/>
@@ -19993,7 +20056,7 @@
       <c r="E21" s="16"/>
       <c r="F21" s="58"/>
       <c r="H21" s="59"/>
-      <c r="I21" s="93"/>
+      <c r="I21" s="94"/>
       <c r="J21" s="60"/>
       <c r="K21" s="55"/>
       <c r="M21" s="52"/>

--- a/arquivos extras/Planilha.xlsx
+++ b/arquivos extras/Planilha.xlsx
@@ -76,7 +76,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>-32</xdr:colOff>
+                <xdr:colOff>-33</xdr:colOff>
                 <xdr:row>13</xdr:row>
                 <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
@@ -91,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1678" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1688" uniqueCount="268">
   <si>
     <t xml:space="preserve">JAN</t>
   </si>
@@ -2376,10 +2376,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.0673989389524023"/>
-          <c:y val="0.102191978802842"/>
-          <c:w val="0.748187999701113"/>
-          <c:h val="0.815127062507527"/>
+          <c:x val="0.0674014571268448"/>
+          <c:y val="0.102198133092442"/>
+          <c:w val="0.74817859144405"/>
+          <c:h val="0.815055706112617"/>
         </c:manualLayout>
       </c:layout>
       <c:pie3DChart>
@@ -3363,9 +3363,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>44280</xdr:colOff>
+      <xdr:colOff>43920</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>19080</xdr:rowOff>
+      <xdr:rowOff>18720</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3374,7 +3374,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
-        <a:ext cx="9635400" cy="5977800"/>
+        <a:ext cx="9635040" cy="5977440"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46242</v>
+        <v>46252</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -4847,7 +4847,7 @@
       </c>
       <c r="F3" s="11" t="n">
         <f aca="false">SUM(D3,D5,D6,D7,D4)</f>
-        <v>1008.11</v>
+        <v>900.45</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>6</v>
@@ -4875,7 +4875,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46242</v>
+        <v>46252</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -4934,14 +4934,14 @@
       <c r="C7" s="33"/>
       <c r="D7" s="34" t="n">
         <f aca="false">Set!F7</f>
-        <v>1008.11</v>
+        <v>900.45</v>
       </c>
       <c r="E7" s="35" t="s">
         <v>19</v>
       </c>
       <c r="F7" s="36" t="n">
         <f aca="false">F3-F4-F6</f>
-        <v>1008.11</v>
+        <v>900.45</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="F3" s="11" t="n">
         <f aca="false">SUM(D3,D5,D6,D7,D4)</f>
-        <v>1008.11</v>
+        <v>900.45</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>6</v>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46242</v>
+        <v>46252</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -6006,14 +6006,14 @@
       <c r="C7" s="33"/>
       <c r="D7" s="34" t="n">
         <f aca="false">Out!F7</f>
-        <v>1008.11</v>
+        <v>900.45</v>
       </c>
       <c r="E7" s="35" t="s">
         <v>19</v>
       </c>
       <c r="F7" s="36" t="n">
         <f aca="false">F3-F4-F6</f>
-        <v>1008.11</v>
+        <v>900.45</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6994,7 +6994,7 @@
       </c>
       <c r="F3" s="11" t="n">
         <f aca="false">SUM(D3,D5,D6,D7,D4)</f>
-        <v>1008.11</v>
+        <v>900.45</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>6</v>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46242</v>
+        <v>46252</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -7081,14 +7081,14 @@
       <c r="C7" s="33"/>
       <c r="D7" s="34" t="n">
         <f aca="false">Nov!F7</f>
-        <v>1008.11</v>
+        <v>900.45</v>
       </c>
       <c r="E7" s="35" t="s">
         <v>19</v>
       </c>
       <c r="F7" s="36" t="n">
         <f aca="false">F3-F4-F6</f>
-        <v>1008.11</v>
+        <v>900.45</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8123,23 +8123,23 @@
       </c>
       <c r="K3" s="107" t="n">
         <f aca="false">Set!$F$3</f>
-        <v>1008.11</v>
+        <v>900.45</v>
       </c>
       <c r="L3" s="107" t="n">
         <f aca="false">Out!$F$3</f>
-        <v>1008.11</v>
+        <v>900.45</v>
       </c>
       <c r="M3" s="107" t="n">
         <f aca="false">Nov!$F$3</f>
-        <v>1008.11</v>
+        <v>900.45</v>
       </c>
       <c r="N3" s="108" t="n">
         <f aca="false">Dez!$F$3</f>
-        <v>1008.11</v>
+        <v>900.45</v>
       </c>
       <c r="O3" s="108" t="n">
         <f aca="false">SUM(C3:N3)</f>
-        <v>26182.2</v>
+        <v>25751.56</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="J4" s="110" t="n">
         <f aca="false">Ago!$F$4</f>
-        <v>312.67</v>
+        <v>420.33</v>
       </c>
       <c r="K4" s="110" t="n">
         <f aca="false">Set!$F$4</f>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="O4" s="111" t="n">
         <f aca="false">SUM(C4:N4)</f>
-        <v>9670.45</v>
+        <v>9778.11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8404,7 +8404,7 @@
       </c>
       <c r="J8" s="120" t="n">
         <f aca="false">J4+J5</f>
-        <v>1729.03</v>
+        <v>1836.69</v>
       </c>
       <c r="K8" s="120" t="n">
         <f aca="false">K4+K5</f>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="O8" s="121" t="n">
         <f aca="false">SUM(C8:N8)</f>
-        <v>16083.71</v>
+        <v>16191.37</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8461,27 +8461,27 @@
       </c>
       <c r="J9" s="122" t="n">
         <f aca="false">J3-J8</f>
-        <v>1008.11</v>
+        <v>900.45</v>
       </c>
       <c r="K9" s="122" t="n">
         <f aca="false">K3-K8</f>
-        <v>1008.11</v>
+        <v>900.45</v>
       </c>
       <c r="L9" s="122" t="n">
         <f aca="false">L3-L8</f>
-        <v>1008.11</v>
+        <v>900.45</v>
       </c>
       <c r="M9" s="122" t="n">
         <f aca="false">M3-M8</f>
-        <v>1008.11</v>
+        <v>900.45</v>
       </c>
       <c r="N9" s="123" t="n">
         <f aca="false">N3-N8</f>
-        <v>1008.11</v>
+        <v>900.45</v>
       </c>
       <c r="O9" s="123" t="n">
         <f aca="false">N9</f>
-        <v>1008.11</v>
+        <v>900.45</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8627,7 +8627,7 @@
       </c>
       <c r="J16" s="129" t="n">
         <f aca="false">Ago!$B$36</f>
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="K16" s="128" t="n">
         <f aca="false">Set!$B$36</f>
@@ -8647,7 +8647,7 @@
       </c>
       <c r="O16" s="131" t="n">
         <f aca="false">SUM(C16:N16)</f>
-        <v>176.51</v>
+        <v>180.81</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8684,7 +8684,7 @@
       </c>
       <c r="J17" s="134" t="n">
         <f aca="false">Ago!$B$42</f>
-        <v>0</v>
+        <v>28.48</v>
       </c>
       <c r="K17" s="133" t="n">
         <f aca="false">Set!$B$42</f>
@@ -8704,7 +8704,7 @@
       </c>
       <c r="O17" s="136" t="n">
         <f aca="false">SUM(C17:N17)</f>
-        <v>658.08</v>
+        <v>686.56</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="J18" s="134" t="n">
         <f aca="false">Ago!$B$51</f>
-        <v>265.82</v>
+        <v>331.82</v>
       </c>
       <c r="K18" s="133" t="n">
         <f aca="false">Set!$B$51</f>
@@ -8761,7 +8761,7 @@
       </c>
       <c r="O18" s="136" t="n">
         <f aca="false">SUM(C18:N18)</f>
-        <v>1234.09</v>
+        <v>1300.09</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9061,14 +9061,14 @@
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="73" t="n">
         <f aca="false">SUM(D27:D31)</f>
-        <v>176.51</v>
+        <v>180.81</v>
       </c>
       <c r="C28" s="74" t="s">
         <v>67</v>
       </c>
       <c r="D28" s="75" t="n">
         <f aca="false">SUBTOTAL(9,Fev!D36,Fev!D36,Mar!D36,Abr!D36,Mai!D36,Jun!D36,Jul!D36,Ago!D36,Set!D36,Out!D36,Nov!D36,Dez!D36)</f>
-        <v>131.3</v>
+        <v>135.6</v>
       </c>
       <c r="F28" s="72" t="s">
         <v>66</v>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="D33" s="71" t="n">
         <f aca="false">SUBTOTAL(9,Fev!D41,Fev!D41,Mar!D41,Abr!D41,Mai!D41,Jun!D41,Jul!D41,Ago!D41,Set!D41,Out!D41,Nov!D41,Dez!D41)</f>
-        <v>47.88</v>
+        <v>76.36</v>
       </c>
       <c r="F33" s="76" t="s">
         <v>72</v>
@@ -9250,7 +9250,7 @@
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="73" t="n">
         <f aca="false">SUM(D33:D40)</f>
-        <v>673.39</v>
+        <v>701.87</v>
       </c>
       <c r="C34" s="74" t="s">
         <v>75</v>
@@ -9505,7 +9505,7 @@
       </c>
       <c r="D43" s="71" t="n">
         <f aca="false">SUBTOTAL(9,Fev!D50,Fev!D50,Mar!D50,Abr!D50,Mai!D50,Jun!D50,Jul!D50,Ago!D50,Set!D50,Out!D50,Nov!D50,Dez!D50)</f>
-        <v>298.4</v>
+        <v>354.4</v>
       </c>
       <c r="H43" s="100" t="s">
         <v>253</v>
@@ -9530,14 +9530,14 @@
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="73" t="n">
         <f aca="false">SUM(D43:D49)</f>
-        <v>1366.38</v>
+        <v>1432.38</v>
       </c>
       <c r="C44" s="74" t="s">
         <v>57</v>
       </c>
       <c r="D44" s="75" t="n">
         <f aca="false">SUBTOTAL(9,Fev!D51,Fev!D51,Mar!D51,Abr!D51,Mai!D51,Jun!D51,Jul!D51,Ago!D51,Set!D51,Out!D51,Nov!D51,Dez!D51)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H44" s="100" t="n">
         <f aca="false">SUM(K38:K44)</f>
@@ -11192,7 +11192,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46242</v>
+        <v>46252</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -12385,7 +12385,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46242</v>
+        <v>46252</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -13593,7 +13593,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46242</v>
+        <v>46252</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -14876,7 +14876,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46242</v>
+        <v>46252</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>150</v>
@@ -16162,7 +16162,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46242</v>
+        <v>46252</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>170</v>
@@ -17416,7 +17416,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46242</v>
+        <v>46252</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -18642,14 +18642,14 @@
       </c>
       <c r="F4" s="19" t="n">
         <f aca="false">SUM(F11:F32)</f>
-        <v>312.67</v>
+        <v>420.33</v>
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46242</v>
+        <v>46252</v>
       </c>
       <c r="K4" s="13" t="s">
-        <v>11</v>
+        <v>150</v>
       </c>
       <c r="L4" s="14" t="n">
         <v>522.75</v>
@@ -18700,7 +18700,7 @@
       </c>
       <c r="L6" s="92" t="n">
         <f aca="false">246-SUM(F15:F32)</f>
-        <v>246</v>
+        <v>138.34</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18717,7 +18717,7 @@
       </c>
       <c r="F7" s="36" t="n">
         <f aca="false">F3-F4-F6</f>
-        <v>1008.11</v>
+        <v>900.45</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18880,10 +18880,16 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="56"/>
-      <c r="C15" s="57"/>
-      <c r="D15" s="57"/>
+      <c r="C15" s="57" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" s="57" t="s">
+        <v>55</v>
+      </c>
       <c r="E15" s="16"/>
-      <c r="F15" s="58"/>
+      <c r="F15" s="58" t="n">
+        <v>8.88</v>
+      </c>
       <c r="H15" s="59"/>
       <c r="I15" s="51" t="s">
         <v>66</v>
@@ -18899,10 +18905,16 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="56"/>
-      <c r="C16" s="57"/>
-      <c r="D16" s="57"/>
+      <c r="C16" s="57" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" s="57" t="s">
+        <v>81</v>
+      </c>
       <c r="E16" s="16"/>
-      <c r="F16" s="58"/>
+      <c r="F16" s="58" t="n">
+        <v>56</v>
+      </c>
       <c r="H16" s="59"/>
       <c r="I16" s="51" t="s">
         <v>35</v>
@@ -18919,10 +18931,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="56"/>
-      <c r="C17" s="57"/>
-      <c r="D17" s="57"/>
+      <c r="C17" s="57" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" s="57" t="s">
+        <v>57</v>
+      </c>
       <c r="E17" s="16"/>
-      <c r="F17" s="58"/>
+      <c r="F17" s="58" t="n">
+        <v>10</v>
+      </c>
       <c r="H17" s="59"/>
       <c r="I17" s="51"/>
       <c r="J17" s="60"/>
@@ -18934,10 +18952,16 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="56"/>
-      <c r="C18" s="57"/>
-      <c r="D18" s="57"/>
+      <c r="C18" s="57" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="57" t="s">
+        <v>73</v>
+      </c>
       <c r="E18" s="16"/>
-      <c r="F18" s="58"/>
+      <c r="F18" s="58" t="n">
+        <v>28.48</v>
+      </c>
       <c r="H18" s="59"/>
       <c r="I18" s="51"/>
       <c r="J18" s="60"/>
@@ -18949,10 +18973,16 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="56"/>
-      <c r="C19" s="57"/>
-      <c r="D19" s="57"/>
+      <c r="C19" s="57" t="s">
+        <v>64</v>
+      </c>
+      <c r="D19" s="57" t="s">
+        <v>67</v>
+      </c>
       <c r="E19" s="16"/>
-      <c r="F19" s="58"/>
+      <c r="F19" s="58" t="n">
+        <v>4.3</v>
+      </c>
       <c r="H19" s="59"/>
       <c r="I19" s="51"/>
       <c r="J19" s="60"/>
@@ -19115,14 +19145,14 @@
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="73" t="n">
         <f aca="false">SUM(D35:D39)</f>
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="C36" s="74" t="s">
         <v>67</v>
       </c>
       <c r="D36" s="75" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C36,$F$11:$F$32)</f>
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="H36" s="76" t="s">
         <v>35</v>
@@ -19198,7 +19228,7 @@
       </c>
       <c r="D41" s="71" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C41,$F$11:$F$32)</f>
-        <v>0</v>
+        <v>28.48</v>
       </c>
       <c r="H41" s="76" t="s">
         <v>74</v>
@@ -19211,7 +19241,7 @@
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="73" t="n">
         <f aca="false">SUBTOTAL(9,D41:D48)</f>
-        <v>0</v>
+        <v>28.48</v>
       </c>
       <c r="C42" s="74" t="s">
         <v>75</v>
@@ -19309,20 +19339,20 @@
       </c>
       <c r="D50" s="71" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C50,$F$11:$F$32)</f>
-        <v>0</v>
+        <v>56</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="73" t="n">
         <f aca="false">SUM(D50:D56)</f>
-        <v>265.82</v>
+        <v>331.82</v>
       </c>
       <c r="C51" s="74" t="s">
         <v>57</v>
       </c>
       <c r="D51" s="75" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C51,$F$11:$F$32)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19742,7 +19772,7 @@
       </c>
       <c r="F3" s="11" t="n">
         <f aca="false">SUM(D3,D5,D6,D7,D4)</f>
-        <v>1008.11</v>
+        <v>900.45</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>6</v>
@@ -19770,7 +19800,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46242</v>
+        <v>46252</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -19829,14 +19859,14 @@
       <c r="C7" s="33"/>
       <c r="D7" s="34" t="n">
         <f aca="false">Ago!F7</f>
-        <v>1008.11</v>
+        <v>900.45</v>
       </c>
       <c r="E7" s="35" t="s">
         <v>19</v>
       </c>
       <c r="F7" s="36" t="n">
         <f aca="false">F3-F4-F6</f>
-        <v>1008.11</v>
+        <v>900.45</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/arquivos extras/Planilha.xlsx
+++ b/arquivos extras/Planilha.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="7"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Jan" sheetId="1" state="visible" r:id="rId3"/>
@@ -91,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1688" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1727" uniqueCount="273">
   <si>
     <t xml:space="preserve">JAN</t>
   </si>
@@ -706,6 +706,21 @@
   </si>
   <si>
     <t xml:space="preserve">SET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">metade dese dinheiro esta com o meu pai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">o saldo está errado divergente com a realidade, pois emprestei dinheiro para meu pai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Praia – geral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vólei 2 semanas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Praia – pessoal</t>
   </si>
   <si>
     <t xml:space="preserve">OUT</t>
@@ -1534,7 +1549,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="180">
+  <cellXfs count="181">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1904,6 +1919,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="169" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2376,10 +2395,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.0674014571268448"/>
-          <c:y val="0.102198133092442"/>
-          <c:w val="0.74817859144405"/>
-          <c:h val="0.815055706112617"/>
+          <c:x val="0.0674064940402795"/>
+          <c:y val="0.102210443895682"/>
+          <c:w val="0.748159772820685"/>
+          <c:h val="0.814912967535988"/>
         </c:manualLayout>
       </c:layout>
       <c:pie3DChart>
@@ -3025,7 +3044,7 @@
                   <c:v>90</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>397.6</c:v>
+                  <c:v>427.6</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -3034,10 +3053,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>541.3</c:v>
+                  <c:v>691.26</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1220</c:v>
+                  <c:v>1530</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>40</c:v>
@@ -3363,9 +3382,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>43920</xdr:colOff>
+      <xdr:colOff>43200</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>18720</xdr:rowOff>
+      <xdr:rowOff>18000</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3374,7 +3393,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
-        <a:ext cx="9635040" cy="5977440"/>
+        <a:ext cx="9634320" cy="5976720"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3652,7 +3671,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46252</v>
+        <v>46278</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -4813,13 +4832,13 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="11.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="34.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="8.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="11.78"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="13" style="1" width="12"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -4847,7 +4866,7 @@
       </c>
       <c r="F3" s="11" t="n">
         <f aca="false">SUM(D3,D5,D6,D7,D4)</f>
-        <v>900.45</v>
+        <v>841.13</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>6</v>
@@ -4855,7 +4874,10 @@
       <c r="K3" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="L3" s="14"/>
+      <c r="L3" s="14" t="n">
+        <f aca="false">Set!L3</f>
+        <v>1840</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="15" t="s">
@@ -4875,12 +4897,15 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46252</v>
+        <v>46278</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="L4" s="14"/>
+      <c r="L4" s="14" t="n">
+        <f aca="false">Set!L4</f>
+        <v>522.75</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="21" t="s">
@@ -4934,14 +4959,14 @@
       <c r="C7" s="33"/>
       <c r="D7" s="34" t="n">
         <f aca="false">Set!F7</f>
-        <v>900.45</v>
+        <v>841.13</v>
       </c>
       <c r="E7" s="35" t="s">
         <v>19</v>
       </c>
       <c r="F7" s="36" t="n">
         <f aca="false">F3-F4-F6</f>
-        <v>900.45</v>
+        <v>841.13</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5006,12 +5031,12 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="47"/>
-      <c r="C11" s="93"/>
-      <c r="D11" s="93"/>
+      <c r="C11" s="94"/>
+      <c r="D11" s="94"/>
       <c r="E11" s="48"/>
       <c r="F11" s="49"/>
       <c r="H11" s="50"/>
-      <c r="I11" s="94"/>
+      <c r="I11" s="95"/>
       <c r="J11" s="51"/>
       <c r="K11" s="46"/>
       <c r="M11" s="52"/>
@@ -5026,7 +5051,7 @@
       <c r="E12" s="16"/>
       <c r="F12" s="58"/>
       <c r="H12" s="59"/>
-      <c r="I12" s="94"/>
+      <c r="I12" s="95"/>
       <c r="J12" s="60"/>
       <c r="K12" s="55"/>
       <c r="M12" s="52"/>
@@ -5041,7 +5066,7 @@
       <c r="E13" s="16"/>
       <c r="F13" s="58"/>
       <c r="H13" s="59"/>
-      <c r="I13" s="94"/>
+      <c r="I13" s="95"/>
       <c r="J13" s="60"/>
       <c r="K13" s="55"/>
       <c r="M13" s="52"/>
@@ -5056,7 +5081,7 @@
       <c r="E14" s="16"/>
       <c r="F14" s="58"/>
       <c r="H14" s="59"/>
-      <c r="I14" s="94"/>
+      <c r="I14" s="95"/>
       <c r="J14" s="60"/>
       <c r="K14" s="55"/>
       <c r="M14" s="52"/>
@@ -5071,7 +5096,7 @@
       <c r="E15" s="16"/>
       <c r="F15" s="58"/>
       <c r="H15" s="59"/>
-      <c r="I15" s="94"/>
+      <c r="I15" s="95"/>
       <c r="J15" s="60"/>
       <c r="K15" s="55"/>
       <c r="M15" s="52"/>
@@ -5086,7 +5111,7 @@
       <c r="E16" s="16"/>
       <c r="F16" s="58"/>
       <c r="H16" s="59"/>
-      <c r="I16" s="94"/>
+      <c r="I16" s="95"/>
       <c r="J16" s="60"/>
       <c r="K16" s="55"/>
       <c r="M16" s="52"/>
@@ -5101,7 +5126,7 @@
       <c r="E17" s="16"/>
       <c r="F17" s="58"/>
       <c r="H17" s="59"/>
-      <c r="I17" s="94"/>
+      <c r="I17" s="95"/>
       <c r="J17" s="60"/>
       <c r="K17" s="55"/>
       <c r="M17" s="52"/>
@@ -5116,7 +5141,7 @@
       <c r="E18" s="16"/>
       <c r="F18" s="58"/>
       <c r="H18" s="59"/>
-      <c r="I18" s="94"/>
+      <c r="I18" s="95"/>
       <c r="J18" s="60"/>
       <c r="K18" s="55"/>
       <c r="M18" s="52"/>
@@ -5131,7 +5156,7 @@
       <c r="E19" s="16"/>
       <c r="F19" s="58"/>
       <c r="H19" s="59"/>
-      <c r="I19" s="94"/>
+      <c r="I19" s="95"/>
       <c r="J19" s="60"/>
       <c r="K19" s="55"/>
       <c r="M19" s="52"/>
@@ -5146,7 +5171,7 @@
       <c r="E20" s="16"/>
       <c r="F20" s="58"/>
       <c r="H20" s="59"/>
-      <c r="I20" s="94"/>
+      <c r="I20" s="95"/>
       <c r="J20" s="60"/>
       <c r="K20" s="55"/>
       <c r="M20" s="52"/>
@@ -5161,7 +5186,7 @@
       <c r="E21" s="16"/>
       <c r="F21" s="58"/>
       <c r="H21" s="59"/>
-      <c r="I21" s="94"/>
+      <c r="I21" s="95"/>
       <c r="J21" s="60"/>
       <c r="K21" s="55"/>
       <c r="M21" s="52"/>
@@ -5891,7 +5916,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -5919,7 +5944,7 @@
       </c>
       <c r="F3" s="11" t="n">
         <f aca="false">SUM(D3,D5,D6,D7,D4)</f>
-        <v>900.45</v>
+        <v>841.13</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>6</v>
@@ -5927,7 +5952,10 @@
       <c r="K3" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="L3" s="14"/>
+      <c r="L3" s="14" t="n">
+        <f aca="false">Out!L3</f>
+        <v>1840</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="15" t="s">
@@ -5947,12 +5975,15 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46252</v>
+        <v>46278</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="L4" s="14"/>
+      <c r="L4" s="14" t="n">
+        <f aca="false">Out!L4</f>
+        <v>522.75</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="21" t="s">
@@ -6006,14 +6037,14 @@
       <c r="C7" s="33"/>
       <c r="D7" s="34" t="n">
         <f aca="false">Out!F7</f>
-        <v>900.45</v>
+        <v>841.13</v>
       </c>
       <c r="E7" s="35" t="s">
         <v>19</v>
       </c>
       <c r="F7" s="36" t="n">
         <f aca="false">F3-F4-F6</f>
-        <v>900.45</v>
+        <v>841.13</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6078,12 +6109,12 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="47"/>
-      <c r="C11" s="93"/>
-      <c r="D11" s="93"/>
+      <c r="C11" s="94"/>
+      <c r="D11" s="94"/>
       <c r="E11" s="48"/>
       <c r="F11" s="49"/>
       <c r="H11" s="50"/>
-      <c r="I11" s="94"/>
+      <c r="I11" s="95"/>
       <c r="J11" s="51"/>
       <c r="K11" s="46"/>
       <c r="M11" s="52"/>
@@ -6098,7 +6129,7 @@
       <c r="E12" s="16"/>
       <c r="F12" s="58"/>
       <c r="H12" s="59"/>
-      <c r="I12" s="94"/>
+      <c r="I12" s="95"/>
       <c r="J12" s="60"/>
       <c r="K12" s="55"/>
       <c r="M12" s="52"/>
@@ -6113,7 +6144,7 @@
       <c r="E13" s="16"/>
       <c r="F13" s="58"/>
       <c r="H13" s="59"/>
-      <c r="I13" s="94"/>
+      <c r="I13" s="95"/>
       <c r="J13" s="60"/>
       <c r="K13" s="55"/>
       <c r="M13" s="52"/>
@@ -6128,7 +6159,7 @@
       <c r="E14" s="16"/>
       <c r="F14" s="58"/>
       <c r="H14" s="59"/>
-      <c r="I14" s="94"/>
+      <c r="I14" s="95"/>
       <c r="J14" s="60"/>
       <c r="K14" s="55"/>
       <c r="M14" s="52"/>
@@ -6143,7 +6174,7 @@
       <c r="E15" s="16"/>
       <c r="F15" s="58"/>
       <c r="H15" s="59"/>
-      <c r="I15" s="94"/>
+      <c r="I15" s="95"/>
       <c r="J15" s="60"/>
       <c r="K15" s="55"/>
       <c r="M15" s="52"/>
@@ -6158,7 +6189,7 @@
       <c r="E16" s="16"/>
       <c r="F16" s="58"/>
       <c r="H16" s="59"/>
-      <c r="I16" s="94"/>
+      <c r="I16" s="95"/>
       <c r="J16" s="60"/>
       <c r="K16" s="55"/>
       <c r="M16" s="52"/>
@@ -6173,7 +6204,7 @@
       <c r="E17" s="16"/>
       <c r="F17" s="58"/>
       <c r="H17" s="59"/>
-      <c r="I17" s="94"/>
+      <c r="I17" s="95"/>
       <c r="J17" s="60"/>
       <c r="K17" s="55"/>
       <c r="M17" s="52"/>
@@ -6188,7 +6219,7 @@
       <c r="E18" s="16"/>
       <c r="F18" s="58"/>
       <c r="H18" s="59"/>
-      <c r="I18" s="94"/>
+      <c r="I18" s="95"/>
       <c r="J18" s="60"/>
       <c r="K18" s="55"/>
       <c r="M18" s="52"/>
@@ -6203,7 +6234,7 @@
       <c r="E19" s="16"/>
       <c r="F19" s="58"/>
       <c r="H19" s="59"/>
-      <c r="I19" s="94"/>
+      <c r="I19" s="95"/>
       <c r="J19" s="60"/>
       <c r="K19" s="55"/>
       <c r="M19" s="52"/>
@@ -6218,7 +6249,7 @@
       <c r="E20" s="16"/>
       <c r="F20" s="58"/>
       <c r="H20" s="59"/>
-      <c r="I20" s="94"/>
+      <c r="I20" s="95"/>
       <c r="J20" s="60"/>
       <c r="K20" s="55"/>
       <c r="M20" s="52"/>
@@ -6233,7 +6264,7 @@
       <c r="E21" s="16"/>
       <c r="F21" s="58"/>
       <c r="H21" s="59"/>
-      <c r="I21" s="94"/>
+      <c r="I21" s="95"/>
       <c r="J21" s="60"/>
       <c r="K21" s="55"/>
       <c r="M21" s="52"/>
@@ -6959,14 +6990,14 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="34.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="8.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="95" width="10.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="96" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="15.85"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -6994,7 +7025,7 @@
       </c>
       <c r="F3" s="11" t="n">
         <f aca="false">SUM(D3,D5,D6,D7,D4)</f>
-        <v>900.45</v>
+        <v>841.13</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>6</v>
@@ -7002,7 +7033,10 @@
       <c r="K3" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="L3" s="14"/>
+      <c r="L3" s="14" t="n">
+        <f aca="false">Nov!L3</f>
+        <v>1840</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="15" t="s">
@@ -7022,12 +7056,15 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46252</v>
+        <v>46278</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="L4" s="14"/>
+      <c r="L4" s="14" t="n">
+        <f aca="false">Nov!L4</f>
+        <v>522.75</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="21" t="s">
@@ -7081,14 +7118,14 @@
       <c r="C7" s="33"/>
       <c r="D7" s="34" t="n">
         <f aca="false">Nov!F7</f>
-        <v>900.45</v>
+        <v>841.13</v>
       </c>
       <c r="E7" s="35" t="s">
         <v>19</v>
       </c>
       <c r="F7" s="36" t="n">
         <f aca="false">F3-F4-F6</f>
-        <v>900.45</v>
+        <v>841.13</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7147,22 +7184,22 @@
         <v>2</v>
       </c>
       <c r="M10" s="43"/>
-      <c r="N10" s="96"/>
+      <c r="N10" s="97"/>
       <c r="O10" s="45"/>
       <c r="P10" s="46"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="47"/>
-      <c r="C11" s="93"/>
-      <c r="D11" s="93"/>
+      <c r="C11" s="94"/>
+      <c r="D11" s="94"/>
       <c r="E11" s="48"/>
       <c r="F11" s="49"/>
       <c r="H11" s="50"/>
-      <c r="I11" s="94"/>
+      <c r="I11" s="95"/>
       <c r="J11" s="51"/>
       <c r="K11" s="46"/>
       <c r="M11" s="52"/>
-      <c r="N11" s="97"/>
+      <c r="N11" s="98"/>
       <c r="O11" s="54"/>
       <c r="P11" s="55"/>
     </row>
@@ -7173,11 +7210,11 @@
       <c r="E12" s="16"/>
       <c r="F12" s="58"/>
       <c r="H12" s="59"/>
-      <c r="I12" s="94"/>
+      <c r="I12" s="95"/>
       <c r="J12" s="60"/>
       <c r="K12" s="55"/>
       <c r="M12" s="52"/>
-      <c r="N12" s="97"/>
+      <c r="N12" s="98"/>
       <c r="O12" s="54"/>
       <c r="P12" s="55"/>
     </row>
@@ -7188,11 +7225,11 @@
       <c r="E13" s="16"/>
       <c r="F13" s="58"/>
       <c r="H13" s="59"/>
-      <c r="I13" s="94"/>
+      <c r="I13" s="95"/>
       <c r="J13" s="60"/>
       <c r="K13" s="55"/>
       <c r="M13" s="52"/>
-      <c r="N13" s="97"/>
+      <c r="N13" s="98"/>
       <c r="O13" s="54"/>
       <c r="P13" s="55"/>
     </row>
@@ -7203,11 +7240,11 @@
       <c r="E14" s="16"/>
       <c r="F14" s="58"/>
       <c r="H14" s="59"/>
-      <c r="I14" s="94"/>
+      <c r="I14" s="95"/>
       <c r="J14" s="60"/>
       <c r="K14" s="55"/>
       <c r="M14" s="52"/>
-      <c r="N14" s="97"/>
+      <c r="N14" s="98"/>
       <c r="O14" s="54"/>
       <c r="P14" s="55"/>
     </row>
@@ -7218,11 +7255,11 @@
       <c r="E15" s="16"/>
       <c r="F15" s="58"/>
       <c r="H15" s="59"/>
-      <c r="I15" s="94"/>
+      <c r="I15" s="95"/>
       <c r="J15" s="60"/>
       <c r="K15" s="55"/>
       <c r="M15" s="52"/>
-      <c r="N15" s="97"/>
+      <c r="N15" s="98"/>
       <c r="O15" s="54"/>
       <c r="P15" s="55"/>
     </row>
@@ -7233,11 +7270,11 @@
       <c r="E16" s="16"/>
       <c r="F16" s="58"/>
       <c r="H16" s="59"/>
-      <c r="I16" s="94"/>
+      <c r="I16" s="95"/>
       <c r="J16" s="60"/>
       <c r="K16" s="55"/>
       <c r="M16" s="52"/>
-      <c r="N16" s="97"/>
+      <c r="N16" s="98"/>
       <c r="O16" s="54"/>
       <c r="P16" s="55"/>
     </row>
@@ -7248,11 +7285,11 @@
       <c r="E17" s="16"/>
       <c r="F17" s="58"/>
       <c r="H17" s="59"/>
-      <c r="I17" s="94"/>
+      <c r="I17" s="95"/>
       <c r="J17" s="60"/>
       <c r="K17" s="55"/>
       <c r="M17" s="52"/>
-      <c r="N17" s="97"/>
+      <c r="N17" s="98"/>
       <c r="O17" s="54"/>
       <c r="P17" s="55"/>
     </row>
@@ -7263,11 +7300,11 @@
       <c r="E18" s="16"/>
       <c r="F18" s="58"/>
       <c r="H18" s="59"/>
-      <c r="I18" s="94"/>
+      <c r="I18" s="95"/>
       <c r="J18" s="60"/>
       <c r="K18" s="55"/>
       <c r="M18" s="52"/>
-      <c r="N18" s="97"/>
+      <c r="N18" s="98"/>
       <c r="O18" s="54"/>
       <c r="P18" s="55"/>
     </row>
@@ -7278,11 +7315,11 @@
       <c r="E19" s="16"/>
       <c r="F19" s="58"/>
       <c r="H19" s="59"/>
-      <c r="I19" s="94"/>
+      <c r="I19" s="95"/>
       <c r="J19" s="60"/>
       <c r="K19" s="55"/>
       <c r="M19" s="52"/>
-      <c r="N19" s="97"/>
+      <c r="N19" s="98"/>
       <c r="O19" s="54"/>
       <c r="P19" s="55"/>
     </row>
@@ -7293,11 +7330,11 @@
       <c r="E20" s="16"/>
       <c r="F20" s="58"/>
       <c r="H20" s="59"/>
-      <c r="I20" s="94"/>
+      <c r="I20" s="95"/>
       <c r="J20" s="60"/>
       <c r="K20" s="55"/>
       <c r="M20" s="52"/>
-      <c r="N20" s="97"/>
+      <c r="N20" s="98"/>
       <c r="O20" s="54"/>
       <c r="P20" s="55"/>
     </row>
@@ -7308,11 +7345,11 @@
       <c r="E21" s="16"/>
       <c r="F21" s="58"/>
       <c r="H21" s="59"/>
-      <c r="I21" s="94"/>
+      <c r="I21" s="95"/>
       <c r="J21" s="60"/>
       <c r="K21" s="55"/>
       <c r="M21" s="52"/>
-      <c r="N21" s="97"/>
+      <c r="N21" s="98"/>
       <c r="O21" s="54"/>
       <c r="P21" s="55"/>
     </row>
@@ -7327,7 +7364,7 @@
       <c r="J22" s="62"/>
       <c r="K22" s="63"/>
       <c r="M22" s="52"/>
-      <c r="N22" s="97"/>
+      <c r="N22" s="98"/>
       <c r="O22" s="54"/>
       <c r="P22" s="55"/>
     </row>
@@ -7342,7 +7379,7 @@
         <v>0</v>
       </c>
       <c r="M23" s="52"/>
-      <c r="N23" s="97"/>
+      <c r="N23" s="98"/>
       <c r="O23" s="54"/>
       <c r="P23" s="55"/>
     </row>
@@ -7353,7 +7390,7 @@
       <c r="E24" s="16"/>
       <c r="F24" s="58"/>
       <c r="M24" s="52"/>
-      <c r="N24" s="97"/>
+      <c r="N24" s="98"/>
       <c r="O24" s="54"/>
       <c r="P24" s="55"/>
     </row>
@@ -7364,7 +7401,7 @@
       <c r="E25" s="16"/>
       <c r="F25" s="58"/>
       <c r="M25" s="64"/>
-      <c r="N25" s="98"/>
+      <c r="N25" s="99"/>
       <c r="O25" s="66"/>
       <c r="P25" s="63"/>
     </row>
@@ -8023,18 +8060,18 @@
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="99" width="21.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="100" width="23.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="100" width="14.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="100" width="19.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="100" width="14.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="100" width="14.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="100" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="100" width="17.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="100" width="14.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="100" width="20.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="100" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="100" width="14.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="100" width="21.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="101" width="23.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="101" width="14.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="101" width="19.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="101" width="14.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="101" width="14.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="101" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="101" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="101" width="14.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="101" width="20.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="101" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="101" width="14.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="15.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="19.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="13.15"/>
@@ -8042,1006 +8079,1006 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="101" t="s">
-        <v>208</v>
-      </c>
-      <c r="C2" s="102" t="s">
-        <v>209</v>
-      </c>
-      <c r="D2" s="103" t="s">
+      <c r="B2" s="102" t="s">
+        <v>213</v>
+      </c>
+      <c r="C2" s="103" t="s">
+        <v>214</v>
+      </c>
+      <c r="D2" s="104" t="s">
         <v>106</v>
       </c>
-      <c r="E2" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="F2" s="103" t="s">
-        <v>211</v>
-      </c>
-      <c r="G2" s="103" t="s">
-        <v>212</v>
-      </c>
-      <c r="H2" s="103" t="s">
-        <v>213</v>
-      </c>
-      <c r="I2" s="103" t="s">
-        <v>214</v>
-      </c>
-      <c r="J2" s="103" t="s">
+      <c r="E2" s="104" t="s">
         <v>215</v>
       </c>
-      <c r="K2" s="103" t="s">
+      <c r="F2" s="104" t="s">
         <v>216</v>
       </c>
-      <c r="L2" s="103" t="s">
+      <c r="G2" s="104" t="s">
         <v>217</v>
       </c>
-      <c r="M2" s="103" t="s">
+      <c r="H2" s="104" t="s">
         <v>218</v>
       </c>
-      <c r="N2" s="104" t="s">
+      <c r="I2" s="104" t="s">
         <v>219</v>
       </c>
-      <c r="O2" s="104" t="s">
+      <c r="J2" s="104" t="s">
         <v>220</v>
       </c>
+      <c r="K2" s="104" t="s">
+        <v>221</v>
+      </c>
+      <c r="L2" s="104" t="s">
+        <v>222</v>
+      </c>
+      <c r="M2" s="104" t="s">
+        <v>223</v>
+      </c>
+      <c r="N2" s="105" t="s">
+        <v>224</v>
+      </c>
+      <c r="O2" s="105" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="105" t="s">
+      <c r="B3" s="106" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="106" t="n">
+      <c r="C3" s="107" t="n">
         <f aca="false">Jan!$F$3</f>
         <v>2246.57</v>
       </c>
-      <c r="D3" s="107" t="n">
+      <c r="D3" s="108" t="n">
         <f aca="false">Fev!$F$3</f>
         <v>2281.55</v>
       </c>
-      <c r="E3" s="107" t="n">
+      <c r="E3" s="108" t="n">
         <f aca="false">Mar!$F$3</f>
         <v>2080.77</v>
       </c>
-      <c r="F3" s="107" t="n">
+      <c r="F3" s="108" t="n">
         <f aca="false">Abr!$F$3</f>
         <v>2679.04</v>
       </c>
-      <c r="G3" s="107" t="n">
+      <c r="G3" s="108" t="n">
         <f aca="false">Mai!$F$3</f>
         <v>4523.74</v>
       </c>
-      <c r="H3" s="107" t="n">
+      <c r="H3" s="108" t="n">
         <f aca="false">Jun!$F$3</f>
         <v>2309.7</v>
       </c>
-      <c r="I3" s="107" t="n">
+      <c r="I3" s="108" t="n">
         <f aca="false">Jul!$F$3</f>
         <v>3291.25</v>
       </c>
-      <c r="J3" s="107" t="n">
+      <c r="J3" s="108" t="n">
         <f aca="false">Ago!$F$3</f>
         <v>2737.14</v>
       </c>
-      <c r="K3" s="107" t="n">
+      <c r="K3" s="108" t="n">
         <f aca="false">Set!$F$3</f>
-        <v>900.45</v>
-      </c>
-      <c r="L3" s="107" t="n">
+        <v>2369.34</v>
+      </c>
+      <c r="L3" s="108" t="n">
         <f aca="false">Out!$F$3</f>
-        <v>900.45</v>
-      </c>
-      <c r="M3" s="107" t="n">
+        <v>841.13</v>
+      </c>
+      <c r="M3" s="108" t="n">
         <f aca="false">Nov!$F$3</f>
-        <v>900.45</v>
-      </c>
-      <c r="N3" s="108" t="n">
+        <v>841.13</v>
+      </c>
+      <c r="N3" s="109" t="n">
         <f aca="false">Dez!$F$3</f>
-        <v>900.45</v>
-      </c>
-      <c r="O3" s="108" t="n">
+        <v>841.13</v>
+      </c>
+      <c r="O3" s="109" t="n">
         <f aca="false">SUM(C3:N3)</f>
-        <v>25751.56</v>
+        <v>27042.49</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="109" t="s">
-        <v>221</v>
-      </c>
-      <c r="C4" s="110" t="n">
+      <c r="B4" s="110" t="s">
+        <v>226</v>
+      </c>
+      <c r="C4" s="111" t="n">
         <f aca="false">Jan!$F$4</f>
         <v>568.02</v>
       </c>
-      <c r="D4" s="110" t="n">
+      <c r="D4" s="111" t="n">
         <f aca="false">Fev!$F$4</f>
         <v>561.58</v>
       </c>
-      <c r="E4" s="110" t="n">
+      <c r="E4" s="111" t="n">
         <f aca="false">Mar!$F$4</f>
         <v>1203.63</v>
       </c>
-      <c r="F4" s="110" t="n">
+      <c r="F4" s="111" t="n">
         <f aca="false">Abr!$F$4</f>
         <v>723.11</v>
       </c>
-      <c r="G4" s="110" t="n">
+      <c r="G4" s="111" t="n">
         <f aca="false">Mai!$F$4</f>
         <v>3935.01</v>
       </c>
-      <c r="H4" s="110" t="n">
+      <c r="H4" s="111" t="n">
         <f aca="false">Jun!$F$4</f>
         <v>630</v>
       </c>
-      <c r="I4" s="110" t="n">
+      <c r="I4" s="111" t="n">
         <f aca="false">Jul!$F$4</f>
         <v>1736.43</v>
       </c>
-      <c r="J4" s="110" t="n">
+      <c r="J4" s="111" t="n">
         <f aca="false">Ago!$F$4</f>
-        <v>420.33</v>
-      </c>
-      <c r="K4" s="110" t="n">
+        <v>519.69</v>
+      </c>
+      <c r="K4" s="111" t="n">
         <f aca="false">Set!$F$4</f>
-        <v>0</v>
-      </c>
-      <c r="L4" s="110" t="n">
+        <v>1085</v>
+      </c>
+      <c r="L4" s="111" t="n">
         <f aca="false">Out!$F$4</f>
         <v>0</v>
       </c>
-      <c r="M4" s="110" t="n">
+      <c r="M4" s="111" t="n">
         <f aca="false">Nov!$F$4</f>
         <v>0</v>
       </c>
-      <c r="N4" s="111" t="n">
+      <c r="N4" s="112" t="n">
         <f aca="false">Dez!$F$4</f>
         <v>0</v>
       </c>
-      <c r="O4" s="111" t="n">
+      <c r="O4" s="112" t="n">
         <f aca="false">SUM(C4:N4)</f>
-        <v>9778.11</v>
+        <v>10962.47</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="109" t="s">
-        <v>222</v>
-      </c>
-      <c r="C5" s="112" t="n">
+      <c r="B5" s="110" t="s">
+        <v>227</v>
+      </c>
+      <c r="C5" s="113" t="n">
         <f aca="false">Jan!$F$6</f>
         <v>337</v>
       </c>
-      <c r="D5" s="112" t="n">
+      <c r="D5" s="113" t="n">
         <f aca="false">Fev!$F$6</f>
         <v>362.2</v>
       </c>
-      <c r="E5" s="112" t="n">
+      <c r="E5" s="113" t="n">
         <f aca="false">Mar!$F$6</f>
         <v>434.6</v>
       </c>
-      <c r="F5" s="112" t="n">
+      <c r="F5" s="113" t="n">
         <f aca="false">Abr!$F$6</f>
         <v>516.69</v>
       </c>
-      <c r="G5" s="112" t="n">
+      <c r="G5" s="113" t="n">
         <f aca="false">Mai!$F$6</f>
         <v>597.03</v>
       </c>
-      <c r="H5" s="112" t="n">
+      <c r="H5" s="113" t="n">
         <f aca="false">Jun!$F$6</f>
         <v>1391.7</v>
       </c>
-      <c r="I5" s="112" t="n">
+      <c r="I5" s="113" t="n">
         <f aca="false">Jul!$F$6</f>
         <v>1357.68</v>
       </c>
-      <c r="J5" s="112" t="n">
+      <c r="J5" s="113" t="n">
         <f aca="false">Ago!$F$6</f>
-        <v>1416.36</v>
-      </c>
-      <c r="K5" s="112" t="n">
+        <v>1498.11</v>
+      </c>
+      <c r="K5" s="113" t="n">
         <f aca="false">Set!$F$6</f>
-        <v>0</v>
-      </c>
-      <c r="L5" s="112" t="n">
+        <v>443.21</v>
+      </c>
+      <c r="L5" s="113" t="n">
         <f aca="false">Out!$F$6</f>
         <v>0</v>
       </c>
-      <c r="M5" s="112" t="n">
+      <c r="M5" s="113" t="n">
         <f aca="false">Nov!$F$6</f>
         <v>0</v>
       </c>
-      <c r="N5" s="113" t="n">
+      <c r="N5" s="114" t="n">
         <f aca="false">Dez!$F$6</f>
         <v>0</v>
       </c>
-      <c r="O5" s="113" t="n">
+      <c r="O5" s="114" t="n">
         <f aca="false">SUM(C5:N5)</f>
-        <v>6413.26</v>
+        <v>6938.22</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="109" t="s">
+      <c r="B6" s="110" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="114" t="n">
+      <c r="C6" s="115" t="n">
         <f aca="false">Jan!$L$3</f>
         <v>0</v>
       </c>
-      <c r="D6" s="114" t="n">
+      <c r="D6" s="115" t="n">
         <f aca="false">Fev!$L$3</f>
         <v>0</v>
       </c>
-      <c r="E6" s="114" t="n">
+      <c r="E6" s="115" t="n">
         <f aca="false">Mar!$L$3</f>
         <v>0</v>
       </c>
-      <c r="F6" s="114" t="n">
+      <c r="F6" s="115" t="n">
         <f aca="false">Abr!$L$3</f>
         <v>1343</v>
       </c>
-      <c r="G6" s="114" t="n">
+      <c r="G6" s="115" t="n">
         <f aca="false">Mai!$L$3</f>
         <v>2503</v>
       </c>
-      <c r="H6" s="114" t="n">
+      <c r="H6" s="115" t="n">
         <f aca="false">Jun!$L$3</f>
         <v>200</v>
       </c>
-      <c r="I6" s="114" t="n">
+      <c r="I6" s="115" t="n">
         <f aca="false">Jul!$L$3</f>
         <v>809.19</v>
       </c>
-      <c r="J6" s="114" t="n">
+      <c r="J6" s="115" t="n">
         <f aca="false">Ago!$L$3</f>
         <v>340</v>
       </c>
-      <c r="K6" s="114" t="n">
+      <c r="K6" s="115" t="n">
         <f aca="false">Set!$L$3</f>
-        <v>0</v>
-      </c>
-      <c r="L6" s="114" t="n">
+        <v>1840</v>
+      </c>
+      <c r="L6" s="115" t="n">
         <f aca="false">Out!$L$3</f>
-        <v>0</v>
-      </c>
-      <c r="M6" s="114" t="n">
+        <v>1840</v>
+      </c>
+      <c r="M6" s="115" t="n">
         <f aca="false">Nov!$L$3</f>
-        <v>0</v>
-      </c>
-      <c r="N6" s="115" t="n">
+        <v>1840</v>
+      </c>
+      <c r="N6" s="116" t="n">
         <f aca="false">Dez!$L$3</f>
-        <v>0</v>
-      </c>
-      <c r="O6" s="116" t="n">
+        <v>1840</v>
+      </c>
+      <c r="O6" s="117" t="n">
         <f aca="false">SUM(C6:N6)</f>
-        <v>5195.19</v>
+        <v>12555.19</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="109" t="s">
-        <v>223</v>
-      </c>
-      <c r="C7" s="117" t="n">
+      <c r="B7" s="110" t="s">
+        <v>228</v>
+      </c>
+      <c r="C7" s="118" t="n">
         <f aca="false">Jan!$L$4</f>
         <v>0</v>
       </c>
-      <c r="D7" s="117" t="n">
+      <c r="D7" s="118" t="n">
         <f aca="false">Fev!$L$4</f>
         <v>0</v>
       </c>
-      <c r="E7" s="117" t="n">
+      <c r="E7" s="118" t="n">
         <f aca="false">Mar!$L$4</f>
         <v>0</v>
       </c>
-      <c r="F7" s="117" t="n">
+      <c r="F7" s="118" t="n">
         <f aca="false">Abr!$L$4</f>
         <v>983.93</v>
       </c>
-      <c r="G7" s="117" t="n">
+      <c r="G7" s="118" t="n">
         <f aca="false">Mai!$L$4</f>
         <v>0</v>
       </c>
-      <c r="H7" s="117" t="n">
+      <c r="H7" s="118" t="n">
         <f aca="false">Jun!$L$4</f>
         <v>0</v>
       </c>
-      <c r="I7" s="117" t="n">
+      <c r="I7" s="118" t="n">
         <f aca="false">Jul!$L$4</f>
         <v>0</v>
       </c>
-      <c r="J7" s="117" t="n">
+      <c r="J7" s="118" t="n">
         <f aca="false">Ago!$L$4</f>
         <v>522.75</v>
       </c>
-      <c r="K7" s="117" t="n">
+      <c r="K7" s="118" t="n">
         <f aca="false">Set!$L$4</f>
-        <v>0</v>
-      </c>
-      <c r="L7" s="117" t="n">
+        <v>522.75</v>
+      </c>
+      <c r="L7" s="118" t="n">
         <f aca="false">Out!$L$4</f>
-        <v>0</v>
-      </c>
-      <c r="M7" s="117" t="n">
+        <v>522.75</v>
+      </c>
+      <c r="M7" s="118" t="n">
         <f aca="false">Nov!$L$4</f>
-        <v>0</v>
-      </c>
-      <c r="N7" s="118" t="n">
+        <v>522.75</v>
+      </c>
+      <c r="N7" s="119" t="n">
         <f aca="false">Dez!$L$4</f>
-        <v>0</v>
-      </c>
-      <c r="O7" s="119" t="n">
+        <v>522.75</v>
+      </c>
+      <c r="O7" s="120" t="n">
         <f aca="false">SUM(C7:N7)</f>
-        <v>1506.68</v>
+        <v>3597.68</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="109" t="s">
-        <v>224</v>
-      </c>
-      <c r="C8" s="120" t="n">
+      <c r="B8" s="110" t="s">
+        <v>229</v>
+      </c>
+      <c r="C8" s="121" t="n">
         <f aca="false">C4+C5</f>
         <v>905.02</v>
       </c>
-      <c r="D8" s="120" t="n">
+      <c r="D8" s="121" t="n">
         <f aca="false">D4+D5</f>
         <v>923.78</v>
       </c>
-      <c r="E8" s="120" t="n">
+      <c r="E8" s="121" t="n">
         <f aca="false">E4+E5</f>
         <v>1638.23</v>
       </c>
-      <c r="F8" s="120" t="n">
+      <c r="F8" s="121" t="n">
         <f aca="false">F4+F5</f>
         <v>1239.8</v>
       </c>
-      <c r="G8" s="120" t="n">
+      <c r="G8" s="121" t="n">
         <f aca="false">G4+G5</f>
         <v>4532.04</v>
       </c>
-      <c r="H8" s="120" t="n">
+      <c r="H8" s="121" t="n">
         <f aca="false">H4+H5</f>
         <v>2021.7</v>
       </c>
-      <c r="I8" s="120" t="n">
+      <c r="I8" s="121" t="n">
         <f aca="false">I4+I5</f>
         <v>3094.11</v>
       </c>
-      <c r="J8" s="120" t="n">
+      <c r="J8" s="121" t="n">
         <f aca="false">J4+J5</f>
-        <v>1836.69</v>
-      </c>
-      <c r="K8" s="120" t="n">
+        <v>2017.8</v>
+      </c>
+      <c r="K8" s="121" t="n">
         <f aca="false">K4+K5</f>
-        <v>0</v>
-      </c>
-      <c r="L8" s="120" t="n">
+        <v>1528.21</v>
+      </c>
+      <c r="L8" s="121" t="n">
         <f aca="false">L4+L5</f>
         <v>0</v>
       </c>
-      <c r="M8" s="120" t="n">
+      <c r="M8" s="121" t="n">
         <f aca="false">M4+M5</f>
         <v>0</v>
       </c>
-      <c r="N8" s="121" t="n">
+      <c r="N8" s="122" t="n">
         <f aca="false">N4+N5</f>
         <v>0</v>
       </c>
-      <c r="O8" s="121" t="n">
+      <c r="O8" s="122" t="n">
         <f aca="false">SUM(C8:N8)</f>
-        <v>16191.37</v>
+        <v>17900.69</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="109" t="s">
+      <c r="B9" s="110" t="s">
         <v>107</v>
       </c>
-      <c r="C9" s="122" t="n">
+      <c r="C9" s="123" t="n">
         <f aca="false">C3-C8</f>
         <v>1341.55</v>
       </c>
-      <c r="D9" s="122" t="n">
+      <c r="D9" s="123" t="n">
         <f aca="false">D3-D8</f>
         <v>1357.77</v>
       </c>
-      <c r="E9" s="122" t="n">
+      <c r="E9" s="123" t="n">
         <f aca="false">E3-E8</f>
         <v>442.54</v>
       </c>
-      <c r="F9" s="122" t="n">
+      <c r="F9" s="123" t="n">
         <f aca="false">F3-F8</f>
         <v>1439.24</v>
       </c>
-      <c r="G9" s="122" t="n">
+      <c r="G9" s="123" t="n">
         <f aca="false">G3-G8</f>
         <v>-8.29999999999927</v>
       </c>
-      <c r="H9" s="122" t="n">
+      <c r="H9" s="123" t="n">
         <f aca="false">H3-H8</f>
         <v>288.000000000001</v>
       </c>
-      <c r="I9" s="122" t="n">
+      <c r="I9" s="123" t="n">
         <f aca="false">I3-I8</f>
         <v>197.14</v>
       </c>
-      <c r="J9" s="122" t="n">
+      <c r="J9" s="123" t="n">
         <f aca="false">J3-J8</f>
-        <v>900.45</v>
-      </c>
-      <c r="K9" s="122" t="n">
+        <v>719.34</v>
+      </c>
+      <c r="K9" s="123" t="n">
         <f aca="false">K3-K8</f>
-        <v>900.45</v>
-      </c>
-      <c r="L9" s="122" t="n">
+        <v>841.13</v>
+      </c>
+      <c r="L9" s="123" t="n">
         <f aca="false">L3-L8</f>
-        <v>900.45</v>
-      </c>
-      <c r="M9" s="122" t="n">
+        <v>841.13</v>
+      </c>
+      <c r="M9" s="123" t="n">
         <f aca="false">M3-M8</f>
-        <v>900.45</v>
-      </c>
-      <c r="N9" s="123" t="n">
+        <v>841.13</v>
+      </c>
+      <c r="N9" s="124" t="n">
         <f aca="false">N3-N8</f>
-        <v>900.45</v>
-      </c>
-      <c r="O9" s="123" t="n">
+        <v>841.13</v>
+      </c>
+      <c r="O9" s="124" t="n">
         <f aca="false">N9</f>
-        <v>900.45</v>
+        <v>841.13</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="124" t="s">
+      <c r="B10" s="125" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="125" t="n">
+      <c r="C10" s="126" t="n">
         <f aca="false">Jan!D4</f>
         <v>103.33</v>
       </c>
-      <c r="D10" s="125" t="n">
+      <c r="D10" s="126" t="n">
         <f aca="false">Fev!D4</f>
         <v>200</v>
       </c>
-      <c r="E10" s="125" t="n">
+      <c r="E10" s="126" t="n">
         <f aca="false">Mar!D4</f>
         <v>0</v>
       </c>
-      <c r="F10" s="125" t="n">
+      <c r="F10" s="126" t="n">
         <f aca="false">Abr!D4</f>
         <v>136.5</v>
       </c>
-      <c r="G10" s="125" t="n">
+      <c r="G10" s="126" t="n">
         <f aca="false">Mai!D4</f>
         <v>20</v>
       </c>
-      <c r="H10" s="125" t="n">
+      <c r="H10" s="126" t="n">
         <f aca="false">Jun!D4</f>
         <v>0</v>
       </c>
-      <c r="I10" s="125" t="n">
+      <c r="I10" s="126" t="n">
         <f aca="false">Jul!D4</f>
         <v>366.25</v>
       </c>
-      <c r="J10" s="125" t="n">
+      <c r="J10" s="126" t="n">
         <f aca="false">Ago!D4</f>
         <v>0</v>
       </c>
-      <c r="K10" s="125" t="n">
+      <c r="K10" s="126" t="n">
         <f aca="false">Set!D4</f>
         <v>0</v>
       </c>
-      <c r="L10" s="125" t="n">
+      <c r="L10" s="126" t="n">
         <f aca="false">Out!D4</f>
         <v>0</v>
       </c>
-      <c r="M10" s="125" t="n">
+      <c r="M10" s="126" t="n">
         <f aca="false">Nov!D4</f>
         <v>0</v>
       </c>
-      <c r="N10" s="126" t="n">
+      <c r="N10" s="127" t="n">
         <f aca="false">Dez!D4</f>
         <v>0</v>
       </c>
-      <c r="O10" s="126" t="n">
+      <c r="O10" s="127" t="n">
         <f aca="false">SUM(C10:N10)</f>
         <v>826.08</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="13" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="L13" s="100" t="n">
+      <c r="L13" s="101" t="n">
         <f aca="false">12*25.82</f>
         <v>309.84</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="101" t="s">
-        <v>208</v>
-      </c>
-      <c r="C15" s="102" t="s">
-        <v>209</v>
-      </c>
-      <c r="D15" s="103" t="s">
+      <c r="B15" s="102" t="s">
+        <v>213</v>
+      </c>
+      <c r="C15" s="103" t="s">
+        <v>214</v>
+      </c>
+      <c r="D15" s="104" t="s">
         <v>106</v>
       </c>
-      <c r="E15" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="F15" s="103" t="s">
-        <v>211</v>
-      </c>
-      <c r="G15" s="103" t="s">
-        <v>212</v>
-      </c>
-      <c r="H15" s="103" t="s">
-        <v>213</v>
-      </c>
-      <c r="I15" s="103" t="s">
-        <v>214</v>
-      </c>
-      <c r="J15" s="103" t="s">
+      <c r="E15" s="104" t="s">
         <v>215</v>
       </c>
-      <c r="K15" s="103" t="s">
+      <c r="F15" s="104" t="s">
         <v>216</v>
       </c>
-      <c r="L15" s="103" t="s">
+      <c r="G15" s="104" t="s">
         <v>217</v>
       </c>
-      <c r="M15" s="103" t="s">
+      <c r="H15" s="104" t="s">
         <v>218</v>
       </c>
-      <c r="N15" s="104" t="s">
+      <c r="I15" s="104" t="s">
         <v>219</v>
       </c>
-      <c r="O15" s="104" t="s">
-        <v>225</v>
+      <c r="J15" s="104" t="s">
+        <v>220</v>
+      </c>
+      <c r="K15" s="104" t="s">
+        <v>221</v>
+      </c>
+      <c r="L15" s="104" t="s">
+        <v>222</v>
+      </c>
+      <c r="M15" s="104" t="s">
+        <v>223</v>
+      </c>
+      <c r="N15" s="105" t="s">
+        <v>224</v>
+      </c>
+      <c r="O15" s="105" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="127" t="s">
+      <c r="B16" s="128" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="128" t="n">
+      <c r="C16" s="129" t="n">
         <f aca="false">Jan!$B$36</f>
         <v>0</v>
       </c>
-      <c r="D16" s="129" t="n">
+      <c r="D16" s="130" t="n">
         <f aca="false">Fev!$B$36</f>
         <v>0</v>
       </c>
-      <c r="E16" s="128" t="n">
+      <c r="E16" s="129" t="n">
         <f aca="false">Mar!$B$36</f>
         <v>12</v>
       </c>
-      <c r="F16" s="129" t="n">
+      <c r="F16" s="130" t="n">
         <f aca="false">Abr!$B$36</f>
         <v>79.46</v>
       </c>
-      <c r="G16" s="128" t="n">
+      <c r="G16" s="129" t="n">
         <f aca="false">Mai!$B$36</f>
         <v>0</v>
       </c>
-      <c r="H16" s="129" t="n">
+      <c r="H16" s="130" t="n">
         <f aca="false">Jun!$B$36</f>
         <v>0</v>
       </c>
-      <c r="I16" s="128" t="n">
+      <c r="I16" s="129" t="n">
         <f aca="false">Jul!$B$36</f>
         <v>85.05</v>
       </c>
-      <c r="J16" s="129" t="n">
+      <c r="J16" s="130" t="n">
         <f aca="false">Ago!$B$36</f>
-        <v>4.3</v>
-      </c>
-      <c r="K16" s="128" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="K16" s="129" t="n">
         <f aca="false">Set!$B$36</f>
-        <v>0</v>
-      </c>
-      <c r="L16" s="129" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="L16" s="130" t="n">
         <f aca="false">Out!$B$36</f>
         <v>0</v>
       </c>
-      <c r="M16" s="128" t="n">
+      <c r="M16" s="129" t="n">
         <f aca="false">Nov!$B$36</f>
         <v>0</v>
       </c>
-      <c r="N16" s="130" t="n">
+      <c r="N16" s="131" t="n">
         <f aca="false">Dez!$B$36</f>
         <v>0</v>
       </c>
-      <c r="O16" s="131" t="n">
+      <c r="O16" s="132" t="n">
         <f aca="false">SUM(C16:N16)</f>
-        <v>180.81</v>
+        <v>196.18</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="132" t="s">
+      <c r="B17" s="133" t="s">
         <v>50</v>
       </c>
-      <c r="C17" s="133" t="n">
+      <c r="C17" s="134" t="n">
         <f aca="false">Jan!$B$42</f>
         <v>23.69</v>
       </c>
-      <c r="D17" s="134" t="n">
+      <c r="D17" s="135" t="n">
         <f aca="false">Fev!$B$42</f>
         <v>39</v>
       </c>
-      <c r="E17" s="133" t="n">
+      <c r="E17" s="134" t="n">
         <f aca="false">Mar!$B$42</f>
         <v>47.88</v>
       </c>
-      <c r="F17" s="134" t="n">
+      <c r="F17" s="135" t="n">
         <f aca="false">Abr!$B$42</f>
         <v>190.31</v>
       </c>
-      <c r="G17" s="133" t="n">
+      <c r="G17" s="134" t="n">
         <f aca="false">Mai!$B$42</f>
         <v>69.7</v>
       </c>
-      <c r="H17" s="134" t="n">
+      <c r="H17" s="135" t="n">
         <f aca="false">Jun!$B$42</f>
         <v>42</v>
       </c>
-      <c r="I17" s="133" t="n">
+      <c r="I17" s="134" t="n">
         <f aca="false">Jul!$B$42</f>
         <v>245.5</v>
       </c>
-      <c r="J17" s="134" t="n">
+      <c r="J17" s="135" t="n">
         <f aca="false">Ago!$B$42</f>
-        <v>28.48</v>
-      </c>
-      <c r="K17" s="133" t="n">
+        <v>53.98</v>
+      </c>
+      <c r="K17" s="134" t="n">
         <f aca="false">Set!$B$42</f>
-        <v>0</v>
-      </c>
-      <c r="L17" s="134" t="n">
+        <v>746.6</v>
+      </c>
+      <c r="L17" s="135" t="n">
         <f aca="false">Out!$B$42</f>
         <v>0</v>
       </c>
-      <c r="M17" s="133" t="n">
+      <c r="M17" s="134" t="n">
         <f aca="false">Nov!$B$42</f>
         <v>0</v>
       </c>
-      <c r="N17" s="135" t="n">
+      <c r="N17" s="136" t="n">
         <f aca="false">Dez!$B$42</f>
         <v>0</v>
       </c>
-      <c r="O17" s="136" t="n">
+      <c r="O17" s="137" t="n">
         <f aca="false">SUM(C17:N17)</f>
-        <v>686.56</v>
+        <v>1458.66</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="132" t="s">
+      <c r="B18" s="133" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="133" t="n">
+      <c r="C18" s="134" t="n">
         <f aca="false">Jan!$B$51</f>
         <v>93.95</v>
       </c>
-      <c r="D18" s="134" t="n">
+      <c r="D18" s="135" t="n">
         <f aca="false">Fev!B51</f>
         <v>226.24</v>
       </c>
-      <c r="E18" s="133" t="n">
+      <c r="E18" s="134" t="n">
         <f aca="false">Mar!$B$51</f>
         <v>19.3</v>
       </c>
-      <c r="F18" s="134" t="n">
+      <c r="F18" s="135" t="n">
         <f aca="false">Abr!$B$51</f>
         <v>153.2</v>
       </c>
-      <c r="G18" s="133" t="n">
+      <c r="G18" s="134" t="n">
         <f aca="false">Mai!$B$51</f>
         <v>76.9</v>
       </c>
-      <c r="H18" s="134" t="n">
+      <c r="H18" s="135" t="n">
         <f aca="false">Jun!$B$51</f>
         <v>0</v>
       </c>
-      <c r="I18" s="133" t="n">
+      <c r="I18" s="134" t="n">
         <f aca="false">Jul!$B$51</f>
         <v>398.68</v>
       </c>
-      <c r="J18" s="134" t="n">
+      <c r="J18" s="135" t="n">
         <f aca="false">Ago!$B$51</f>
-        <v>331.82</v>
-      </c>
-      <c r="K18" s="133" t="n">
+        <v>371.82</v>
+      </c>
+      <c r="K18" s="134" t="n">
         <f aca="false">Set!$B$51</f>
-        <v>0</v>
-      </c>
-      <c r="L18" s="134" t="n">
+        <v>225.03</v>
+      </c>
+      <c r="L18" s="135" t="n">
         <f aca="false">Out!$B$51</f>
         <v>0</v>
       </c>
-      <c r="M18" s="133" t="n">
+      <c r="M18" s="134" t="n">
         <f aca="false">Nov!$B$51</f>
         <v>0</v>
       </c>
-      <c r="N18" s="135" t="n">
+      <c r="N18" s="136" t="n">
         <f aca="false">Dez!$B$51</f>
         <v>0</v>
       </c>
-      <c r="O18" s="136" t="n">
+      <c r="O18" s="137" t="n">
         <f aca="false">SUM(C18:N18)</f>
-        <v>1300.09</v>
+        <v>1565.12</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="132" t="s">
+      <c r="B19" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="C19" s="133" t="n">
+      <c r="C19" s="134" t="n">
         <f aca="false">Jan!$B$59</f>
         <v>72</v>
       </c>
-      <c r="D19" s="134" t="n">
+      <c r="D19" s="135" t="n">
         <f aca="false">Fev!$B$59</f>
         <v>296.34</v>
       </c>
-      <c r="E19" s="133" t="n">
+      <c r="E19" s="134" t="n">
         <f aca="false">Mar!$B$59</f>
         <v>210</v>
       </c>
-      <c r="F19" s="134" t="n">
+      <c r="F19" s="135" t="n">
         <f aca="false">Abr!$B$59</f>
         <v>48.5</v>
       </c>
-      <c r="G19" s="133" t="n">
+      <c r="G19" s="134" t="n">
         <f aca="false">Mai!$B$59</f>
         <v>48</v>
       </c>
-      <c r="H19" s="134" t="n">
+      <c r="H19" s="135" t="n">
         <f aca="false">Jun!$B$59</f>
         <v>0</v>
       </c>
-      <c r="I19" s="133" t="n">
+      <c r="I19" s="134" t="n">
         <f aca="false">Jul!$B$59</f>
         <v>823</v>
       </c>
-      <c r="J19" s="134" t="n">
+      <c r="J19" s="135" t="n">
         <f aca="false">Ago!$B$59</f>
         <v>0</v>
       </c>
-      <c r="K19" s="133" t="n">
+      <c r="K19" s="134" t="n">
         <f aca="false">Set!$B$59</f>
-        <v>0</v>
-      </c>
-      <c r="L19" s="134" t="n">
+        <v>45</v>
+      </c>
+      <c r="L19" s="135" t="n">
         <f aca="false">Out!$B$59</f>
         <v>0</v>
       </c>
-      <c r="M19" s="133" t="n">
+      <c r="M19" s="134" t="n">
         <f aca="false">Nov!$B$59</f>
         <v>0</v>
       </c>
-      <c r="N19" s="135" t="n">
+      <c r="N19" s="136" t="n">
         <f aca="false">Dez!$B$59</f>
         <v>0</v>
       </c>
-      <c r="O19" s="136" t="n">
+      <c r="O19" s="137" t="n">
         <f aca="false">SUM(C19:N19)</f>
-        <v>1497.84</v>
+        <v>1542.84</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="132" t="s">
+      <c r="B20" s="133" t="s">
         <v>88</v>
       </c>
-      <c r="C20" s="133" t="n">
+      <c r="C20" s="134" t="n">
         <f aca="false">Jan!$B$67</f>
         <v>0</v>
       </c>
-      <c r="D20" s="134" t="n">
+      <c r="D20" s="135" t="n">
         <f aca="false">Fev!$B$67</f>
         <v>0</v>
       </c>
-      <c r="E20" s="133" t="n">
+      <c r="E20" s="134" t="n">
         <f aca="false">Mar!$B$67</f>
         <v>34.45</v>
       </c>
-      <c r="F20" s="134" t="n">
+      <c r="F20" s="135" t="n">
         <f aca="false">Abr!$B$67</f>
         <v>0</v>
       </c>
-      <c r="G20" s="133" t="n">
+      <c r="G20" s="134" t="n">
         <f aca="false">Mai!$B$67</f>
         <v>0</v>
       </c>
-      <c r="H20" s="134" t="n">
+      <c r="H20" s="135" t="n">
         <f aca="false">Jun!$B$67</f>
         <v>0</v>
       </c>
-      <c r="I20" s="133" t="n">
+      <c r="I20" s="134" t="n">
         <f aca="false">Jul!$B$67</f>
         <v>0</v>
       </c>
-      <c r="J20" s="134" t="n">
+      <c r="J20" s="135" t="n">
         <f aca="false">Ago!$B$67</f>
         <v>0</v>
       </c>
-      <c r="K20" s="133" t="n">
+      <c r="K20" s="134" t="n">
         <f aca="false">Set!$B$67</f>
         <v>0</v>
       </c>
-      <c r="L20" s="134" t="n">
+      <c r="L20" s="135" t="n">
         <f aca="false">Out!$B$67</f>
         <v>0</v>
       </c>
-      <c r="M20" s="133" t="n">
+      <c r="M20" s="134" t="n">
         <f aca="false">Nov!$B$67</f>
         <v>0</v>
       </c>
-      <c r="N20" s="135" t="n">
+      <c r="N20" s="136" t="n">
         <f aca="false">Dez!$B$67</f>
         <v>0</v>
       </c>
-      <c r="O20" s="136" t="n">
+      <c r="O20" s="137" t="n">
         <f aca="false">SUM(C20:N20)</f>
         <v>34.45</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="132" t="s">
+      <c r="B21" s="133" t="s">
         <v>77</v>
       </c>
-      <c r="C21" s="133" t="n">
+      <c r="C21" s="134" t="n">
         <f aca="false">Jan!$B$75</f>
         <v>0</v>
       </c>
-      <c r="D21" s="134" t="n">
+      <c r="D21" s="135" t="n">
         <f aca="false">Fev!$B$75</f>
         <v>0</v>
       </c>
-      <c r="E21" s="133" t="n">
+      <c r="E21" s="134" t="n">
         <f aca="false">Mar!$B$75</f>
         <v>0</v>
       </c>
-      <c r="F21" s="134" t="n">
+      <c r="F21" s="135" t="n">
         <f aca="false">Abr!$B$75</f>
         <v>0</v>
       </c>
-      <c r="G21" s="133" t="n">
+      <c r="G21" s="134" t="n">
         <f aca="false">Mai!$B$75</f>
         <v>0</v>
       </c>
-      <c r="H21" s="134" t="n">
+      <c r="H21" s="135" t="n">
         <f aca="false">Jun!$B$75</f>
         <v>0</v>
       </c>
-      <c r="I21" s="133" t="n">
+      <c r="I21" s="134" t="n">
         <f aca="false">Jul!$B$75</f>
         <v>0</v>
       </c>
-      <c r="J21" s="134" t="n">
+      <c r="J21" s="135" t="n">
         <f aca="false">Ago!$B$75</f>
         <v>0</v>
       </c>
-      <c r="K21" s="133" t="n">
+      <c r="K21" s="134" t="n">
         <f aca="false">Set!$B$75</f>
         <v>0</v>
       </c>
-      <c r="L21" s="134" t="n">
+      <c r="L21" s="135" t="n">
         <f aca="false">Out!$B$75</f>
         <v>0</v>
       </c>
-      <c r="M21" s="133" t="n">
+      <c r="M21" s="134" t="n">
         <f aca="false">Nov!$B$75</f>
         <v>0</v>
       </c>
-      <c r="N21" s="135" t="n">
+      <c r="N21" s="136" t="n">
         <f aca="false">Dez!$B$75</f>
         <v>0</v>
       </c>
-      <c r="O21" s="136" t="n">
+      <c r="O21" s="137" t="n">
         <f aca="false">SUM(C21:N21)</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="137" t="s">
+      <c r="B22" s="138" t="s">
         <v>79</v>
       </c>
-      <c r="C22" s="133" t="n">
+      <c r="C22" s="134" t="n">
         <f aca="false">Jan!$D$90</f>
         <v>0</v>
       </c>
-      <c r="D22" s="133" t="n">
+      <c r="D22" s="134" t="n">
         <f aca="false">Fev!$D$90</f>
         <v>0</v>
       </c>
-      <c r="E22" s="133" t="n">
+      <c r="E22" s="134" t="n">
         <f aca="false">Mar!$D$90</f>
         <v>0</v>
       </c>
-      <c r="F22" s="133" t="n">
+      <c r="F22" s="134" t="n">
         <f aca="false">Abr!$D$90</f>
         <v>201.64</v>
       </c>
-      <c r="G22" s="133" t="n">
+      <c r="G22" s="134" t="n">
         <f aca="false">Mai!$D$90</f>
         <v>5548.69</v>
       </c>
-      <c r="H22" s="133" t="n">
+      <c r="H22" s="134" t="n">
         <f aca="false">Jun!$D$90</f>
         <v>350</v>
       </c>
-      <c r="I22" s="133" t="n">
+      <c r="I22" s="134" t="n">
         <f aca="false">Jul!$D$90</f>
         <v>0</v>
       </c>
-      <c r="J22" s="133" t="n">
+      <c r="J22" s="134" t="n">
         <f aca="false">Ago!$D$90</f>
         <v>0</v>
       </c>
-      <c r="K22" s="133" t="n">
+      <c r="K22" s="134" t="n">
         <f aca="false">Set!$D$90</f>
         <v>0</v>
       </c>
-      <c r="L22" s="133" t="n">
+      <c r="L22" s="134" t="n">
         <f aca="false">Out!$D$90</f>
         <v>0</v>
       </c>
-      <c r="M22" s="133" t="n">
+      <c r="M22" s="134" t="n">
         <f aca="false">Nov!$D$90</f>
         <v>0</v>
       </c>
-      <c r="N22" s="133" t="n">
+      <c r="N22" s="134" t="n">
         <f aca="false">Dez!$D$90</f>
         <v>0</v>
       </c>
-      <c r="O22" s="138"/>
+      <c r="O22" s="139"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="139" t="s">
+      <c r="B23" s="140" t="s">
         <v>99</v>
       </c>
-      <c r="C23" s="140" t="n">
+      <c r="C23" s="141" t="n">
         <f aca="false">Jan!$B$83</f>
         <v>0</v>
       </c>
-      <c r="D23" s="141" t="n">
+      <c r="D23" s="142" t="n">
         <f aca="false">Fev!$B$83</f>
         <v>0</v>
       </c>
-      <c r="E23" s="140" t="n">
+      <c r="E23" s="141" t="n">
         <f aca="false">Mar!$B$83</f>
         <v>880</v>
       </c>
-      <c r="F23" s="141" t="n">
+      <c r="F23" s="142" t="n">
         <f aca="false">Abr!$B$83</f>
         <v>50</v>
       </c>
-      <c r="G23" s="140" t="n">
+      <c r="G23" s="141" t="n">
         <f aca="false">Mai!$B$83</f>
         <v>0</v>
       </c>
-      <c r="H23" s="141" t="n">
+      <c r="H23" s="142" t="n">
         <f aca="false">Jun!$B$83</f>
         <v>0</v>
       </c>
-      <c r="I23" s="140" t="n">
+      <c r="I23" s="141" t="n">
         <f aca="false">Jul!$B$83</f>
         <v>0</v>
       </c>
-      <c r="J23" s="141" t="n">
+      <c r="J23" s="142" t="n">
         <f aca="false">Ago!$B$83</f>
         <v>0</v>
       </c>
-      <c r="K23" s="140" t="n">
+      <c r="K23" s="141" t="n">
         <f aca="false">Set!$B$83</f>
         <v>0</v>
       </c>
-      <c r="L23" s="141" t="n">
+      <c r="L23" s="142" t="n">
         <f aca="false">Out!$B$83</f>
         <v>0</v>
       </c>
-      <c r="M23" s="140" t="n">
+      <c r="M23" s="141" t="n">
         <f aca="false">Nov!$B$83</f>
         <v>0</v>
       </c>
-      <c r="N23" s="142" t="n">
+      <c r="N23" s="143" t="n">
         <f aca="false">Dez!$B$83</f>
         <v>0</v>
       </c>
-      <c r="O23" s="143" t="n">
+      <c r="O23" s="144" t="n">
         <f aca="false">SUM(C23:N23)</f>
         <v>930</v>
       </c>
@@ -9061,14 +9098,14 @@
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="73" t="n">
         <f aca="false">SUM(D27:D31)</f>
-        <v>180.81</v>
+        <v>196.18</v>
       </c>
       <c r="C28" s="74" t="s">
         <v>67</v>
       </c>
       <c r="D28" s="75" t="n">
         <f aca="false">SUBTOTAL(9,Fev!D36,Fev!D36,Mar!D36,Abr!D36,Mai!D36,Jun!D36,Jul!D36,Ago!D36,Set!D36,Out!D36,Nov!D36,Dez!D36)</f>
-        <v>135.6</v>
+        <v>150.97</v>
       </c>
       <c r="F28" s="72" t="s">
         <v>66</v>
@@ -9077,13 +9114,13 @@
         <f aca="false">SUBTOTAL(9,Jan!I35,Fev!I35,Mar!I35,Abr!I35,Mai!I35,Jun!I35,Jul!I35,Ago!I35,Set!I35,Out!I35,Nov!I35,Dez!I35)</f>
         <v>90</v>
       </c>
-      <c r="I28" s="144" t="s">
-        <v>226</v>
-      </c>
-      <c r="J28" s="144"/>
-      <c r="K28" s="144"/>
-      <c r="L28" s="144"/>
-      <c r="M28" s="145" t="n">
+      <c r="I28" s="145" t="s">
+        <v>231</v>
+      </c>
+      <c r="J28" s="145"/>
+      <c r="K28" s="145"/>
+      <c r="L28" s="145"/>
+      <c r="M28" s="146" t="n">
         <f aca="false">SUM(L30:L44)-SUM(K30:K44)</f>
         <v>3332.14</v>
       </c>
@@ -9101,22 +9138,22 @@
       </c>
       <c r="G29" s="75" t="n">
         <f aca="false">SUBTOTAL(9,Jan!I36,Fev!I36,Mar!I36,Abr!I36,Mai!I36,Jun!I36,Jul!I36,Ago!I36,Set!I36,Out!I36,Nov!I36,Dez!I36)</f>
-        <v>397.6</v>
-      </c>
-      <c r="I29" s="146" t="s">
-        <v>227</v>
-      </c>
-      <c r="J29" s="147" t="s">
-        <v>228</v>
-      </c>
-      <c r="K29" s="147" t="s">
-        <v>229</v>
-      </c>
-      <c r="L29" s="147" t="s">
-        <v>230</v>
-      </c>
-      <c r="M29" s="148" t="s">
-        <v>231</v>
+        <v>427.6</v>
+      </c>
+      <c r="I29" s="147" t="s">
+        <v>232</v>
+      </c>
+      <c r="J29" s="148" t="s">
+        <v>233</v>
+      </c>
+      <c r="K29" s="148" t="s">
+        <v>234</v>
+      </c>
+      <c r="L29" s="148" t="s">
+        <v>235</v>
+      </c>
+      <c r="M29" s="149" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9134,20 +9171,20 @@
         <f aca="false">SUBTOTAL(9,Jan!I37,Fev!I37,Mar!I37,Abr!I37,Mai!I37,Jun!I37,Jul!I37,Ago!I37,Set!I37,Out!I37,Nov!I37,Dez!I37)</f>
         <v>0</v>
       </c>
-      <c r="I30" s="149" t="s">
-        <v>232</v>
-      </c>
-      <c r="J30" s="150" t="s">
-        <v>233</v>
-      </c>
-      <c r="K30" s="150" t="n">
+      <c r="I30" s="150" t="s">
+        <v>237</v>
+      </c>
+      <c r="J30" s="151" t="s">
+        <v>238</v>
+      </c>
+      <c r="K30" s="151" t="n">
         <v>201.64</v>
       </c>
-      <c r="L30" s="150" t="n">
+      <c r="L30" s="151" t="n">
         <f aca="false">200.05+10+10+64</f>
         <v>284.05</v>
       </c>
-      <c r="M30" s="151" t="n">
+      <c r="M30" s="152" t="n">
         <f aca="false">L30-K30</f>
         <v>82.41</v>
       </c>
@@ -9165,19 +9202,19 @@
         <f aca="false">SUBTOTAL(9,Jan!I38,Fev!I38,Mar!I38,Abr!I38,Mai!I38,Jun!I38,Jul!I38,Ago!I38,Set!I38,Out!I38,Nov!I38,Dez!I38)</f>
         <v>0</v>
       </c>
-      <c r="I31" s="152" t="s">
-        <v>234</v>
-      </c>
-      <c r="J31" s="150" t="s">
-        <v>235</v>
-      </c>
-      <c r="K31" s="150" t="n">
+      <c r="I31" s="153" t="s">
+        <v>239</v>
+      </c>
+      <c r="J31" s="151" t="s">
+        <v>240</v>
+      </c>
+      <c r="K31" s="151" t="n">
         <v>1289.99</v>
       </c>
-      <c r="L31" s="150" t="n">
+      <c r="L31" s="151" t="n">
         <v>1517.64</v>
       </c>
-      <c r="M31" s="151" t="n">
+      <c r="M31" s="152" t="n">
         <f aca="false">L31-K31</f>
         <v>227.65</v>
       </c>
@@ -9190,21 +9227,21 @@
       </c>
       <c r="G32" s="75" t="n">
         <f aca="false">SUBTOTAL(9,Jan!I39,Fev!I39,Mar!I39,Abr!I39,Mai!I39,Jun!I39,Jul!I39,Ago!I39,Set!I39,Out!I39,Nov!I39,Dez!I39)</f>
-        <v>541.3</v>
-      </c>
-      <c r="I32" s="152" t="s">
-        <v>236</v>
-      </c>
-      <c r="J32" s="150" t="s">
-        <v>237</v>
-      </c>
-      <c r="K32" s="150" t="n">
+        <v>691.26</v>
+      </c>
+      <c r="I32" s="153" t="s">
+        <v>241</v>
+      </c>
+      <c r="J32" s="151" t="s">
+        <v>242</v>
+      </c>
+      <c r="K32" s="151" t="n">
         <v>700</v>
       </c>
-      <c r="L32" s="150" t="n">
+      <c r="L32" s="151" t="n">
         <v>1000</v>
       </c>
-      <c r="M32" s="151" t="n">
+      <c r="M32" s="152" t="n">
         <f aca="false">L32-K32</f>
         <v>300</v>
       </c>
@@ -9218,31 +9255,31 @@
       </c>
       <c r="D33" s="71" t="n">
         <f aca="false">SUBTOTAL(9,Fev!D41,Fev!D41,Mar!D41,Abr!D41,Mai!D41,Jun!D41,Jul!D41,Ago!D41,Set!D41,Out!D41,Nov!D41,Dez!D41)</f>
-        <v>76.36</v>
+        <v>134.86</v>
       </c>
       <c r="F33" s="76" t="s">
         <v>72</v>
       </c>
       <c r="G33" s="75" t="n">
         <f aca="false">SUBTOTAL(9,Jan!I40,Fev!I40,Mar!I40,Abr!I40,Mai!I40,Jun!I40,Jul!I40,Ago!I40,Set!I40,Out!I40,Nov!I40,Dez!I40)</f>
-        <v>1220</v>
-      </c>
-      <c r="H33" s="100" t="s">
-        <v>238</v>
-      </c>
-      <c r="I33" s="152" t="s">
-        <v>239</v>
-      </c>
-      <c r="J33" s="150" t="s">
-        <v>240</v>
-      </c>
-      <c r="K33" s="150" t="n">
+        <v>1530</v>
+      </c>
+      <c r="H33" s="101" t="s">
+        <v>243</v>
+      </c>
+      <c r="I33" s="153" t="s">
+        <v>244</v>
+      </c>
+      <c r="J33" s="151" t="s">
+        <v>245</v>
+      </c>
+      <c r="K33" s="151" t="n">
         <v>128</v>
       </c>
-      <c r="L33" s="150" t="n">
+      <c r="L33" s="151" t="n">
         <v>176</v>
       </c>
-      <c r="M33" s="151" t="n">
+      <c r="M33" s="152" t="n">
         <f aca="false">L33-K33</f>
         <v>48</v>
       </c>
@@ -9250,7 +9287,7 @@
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="73" t="n">
         <f aca="false">SUM(D33:D40)</f>
-        <v>701.87</v>
+        <v>1473.97</v>
       </c>
       <c r="C34" s="74" t="s">
         <v>75</v>
@@ -9266,23 +9303,23 @@
         <f aca="false">SUBTOTAL(9,Jan!I41,Fev!I41,Mar!I41,Abr!I41,Mai!I41,Jun!I41,Jul!I41,Ago!I41,Set!I41,Out!I41,Nov!I41,Dez!I41)</f>
         <v>40</v>
       </c>
-      <c r="H34" s="100" t="n">
+      <c r="H34" s="101" t="n">
         <f aca="false">SUM(K30:K36)</f>
         <v>5165.22</v>
       </c>
-      <c r="I34" s="152" t="s">
-        <v>241</v>
-      </c>
-      <c r="J34" s="150" t="s">
-        <v>240</v>
-      </c>
-      <c r="K34" s="150" t="n">
+      <c r="I34" s="153" t="s">
+        <v>246</v>
+      </c>
+      <c r="J34" s="151" t="s">
+        <v>245</v>
+      </c>
+      <c r="K34" s="151" t="n">
         <v>320.74</v>
       </c>
-      <c r="L34" s="150" t="n">
+      <c r="L34" s="151" t="n">
         <v>385</v>
       </c>
-      <c r="M34" s="151" t="n">
+      <c r="M34" s="152" t="n">
         <f aca="false">L34-K34</f>
         <v>64.26</v>
       </c>
@@ -9302,19 +9339,19 @@
         <f aca="false">SUBTOTAL(9,Jan!I42,Fev!I42,Mar!I42,Abr!I42,Mai!I42,Jun!I42,Jul!I42,Ago!I42,Set!I42,Out!I42,Nov!I42,Dez!I42)</f>
         <v>3914.36</v>
       </c>
-      <c r="I35" s="152" t="s">
-        <v>242</v>
-      </c>
-      <c r="J35" s="150" t="s">
-        <v>243</v>
-      </c>
-      <c r="K35" s="150" t="n">
+      <c r="I35" s="153" t="s">
+        <v>247</v>
+      </c>
+      <c r="J35" s="151" t="s">
+        <v>248</v>
+      </c>
+      <c r="K35" s="151" t="n">
         <v>1715.14</v>
       </c>
-      <c r="L35" s="150" t="n">
+      <c r="L35" s="151" t="n">
         <v>2017.8</v>
       </c>
-      <c r="M35" s="151" t="n">
+      <c r="M35" s="152" t="n">
         <f aca="false">L35-K35</f>
         <v>302.66</v>
       </c>
@@ -9334,19 +9371,19 @@
         <f aca="false">SUBTOTAL(9,Jan!I43,Fev!I43,Mar!I43,Abr!I43,Mai!I43,Jun!I43,Jul!I43,Ago!I43,Set!I43,Out!I43,Nov!I43,Dez!I43)</f>
         <v>0</v>
       </c>
-      <c r="I36" s="152" t="s">
-        <v>244</v>
-      </c>
-      <c r="J36" s="152" t="s">
-        <v>245</v>
-      </c>
-      <c r="K36" s="152" t="n">
+      <c r="I36" s="153" t="s">
+        <v>249</v>
+      </c>
+      <c r="J36" s="153" t="s">
+        <v>250</v>
+      </c>
+      <c r="K36" s="153" t="n">
         <v>809.71</v>
       </c>
-      <c r="L36" s="152" t="n">
+      <c r="L36" s="153" t="n">
         <v>1000</v>
       </c>
-      <c r="M36" s="151" t="n">
+      <c r="M36" s="152" t="n">
         <f aca="false">L36-K36</f>
         <v>190.29</v>
       </c>
@@ -9366,19 +9403,19 @@
         <f aca="false">SUBTOTAL(9,C22:N22)</f>
         <v>6100.33</v>
       </c>
-      <c r="I37" s="153" t="s">
-        <v>246</v>
-      </c>
-      <c r="J37" s="133" t="s">
-        <v>245</v>
-      </c>
-      <c r="K37" s="154" t="n">
+      <c r="I37" s="154" t="s">
+        <v>251</v>
+      </c>
+      <c r="J37" s="134" t="s">
+        <v>250</v>
+      </c>
+      <c r="K37" s="155" t="n">
         <v>2378</v>
       </c>
-      <c r="L37" s="155" t="n">
+      <c r="L37" s="156" t="n">
         <v>3669</v>
       </c>
-      <c r="M37" s="151" t="n">
+      <c r="M37" s="152" t="n">
         <f aca="false">L37-K37</f>
         <v>1291</v>
       </c>
@@ -9389,26 +9426,26 @@
       </c>
       <c r="D38" s="75" t="n">
         <f aca="false">SUBTOTAL(9,Fev!D46,Fev!D46,Mar!D46,Abr!D46,Mai!D46,Jun!D46,Jul!D46,Ago!D46,Set!D46,Out!D46,Nov!D46,Dez!D46)</f>
-        <v>470.51</v>
+        <v>1184.11</v>
       </c>
       <c r="F38" s="81"/>
       <c r="G38" s="78" t="n">
         <f aca="false">SUBTOTAL(9,Jan!I45,Fev!I45,Mar!I45,Abr!I45,Mai!I45,Jun!I45,Jul!I45,Ago!I45,Set!I45,Out!I45,Nov!I45,Dez!I45)</f>
         <v>0</v>
       </c>
-      <c r="I38" s="152" t="s">
-        <v>247</v>
-      </c>
-      <c r="J38" s="150" t="s">
-        <v>245</v>
-      </c>
-      <c r="K38" s="150" t="n">
+      <c r="I38" s="153" t="s">
+        <v>252</v>
+      </c>
+      <c r="J38" s="151" t="s">
+        <v>250</v>
+      </c>
+      <c r="K38" s="151" t="n">
         <v>78.9</v>
       </c>
-      <c r="L38" s="150" t="n">
+      <c r="L38" s="151" t="n">
         <v>93.24</v>
       </c>
-      <c r="M38" s="151" t="n">
+      <c r="M38" s="152" t="n">
         <f aca="false">L38-K38</f>
         <v>14.34</v>
       </c>
@@ -9419,79 +9456,79 @@
         <f aca="false">SUBTOTAL(9,Fev!D47,Fev!D47,Mar!D47,Abr!D47,Mai!D47,Jun!D47,Jul!D47,Ago!D47,Set!D47,Out!D47,Nov!D47,Dez!D47)</f>
         <v>0</v>
       </c>
-      <c r="I39" s="152" t="s">
-        <v>248</v>
-      </c>
-      <c r="J39" s="150" t="s">
-        <v>235</v>
-      </c>
-      <c r="K39" s="150" t="n">
+      <c r="I39" s="153" t="s">
+        <v>253</v>
+      </c>
+      <c r="J39" s="151" t="s">
+        <v>240</v>
+      </c>
+      <c r="K39" s="151" t="n">
         <v>630</v>
       </c>
-      <c r="L39" s="150" t="n">
+      <c r="L39" s="151" t="n">
         <v>741</v>
       </c>
-      <c r="M39" s="151" t="n">
+      <c r="M39" s="152" t="n">
         <f aca="false">L39-K39</f>
         <v>111</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="156"/>
+      <c r="B40" s="157"/>
       <c r="C40" s="64"/>
       <c r="D40" s="78" t="n">
         <f aca="false">SUBTOTAL(9,Fev!D48,Fev!D48,Mar!D48,Abr!D48,Mai!D48,Jun!D48,Jul!D48,Ago!D48,Set!D48,Out!D48,Nov!D48,Dez!D48)</f>
         <v>0</v>
       </c>
-      <c r="I40" s="157" t="s">
-        <v>249</v>
-      </c>
-      <c r="J40" s="150" t="s">
-        <v>250</v>
-      </c>
-      <c r="K40" s="150" t="n">
+      <c r="I40" s="158" t="s">
+        <v>254</v>
+      </c>
+      <c r="J40" s="151" t="s">
+        <v>255</v>
+      </c>
+      <c r="K40" s="151" t="n">
         <v>394</v>
       </c>
-      <c r="L40" s="150" t="n">
+      <c r="L40" s="151" t="n">
         <v>765</v>
       </c>
-      <c r="M40" s="151" t="n">
+      <c r="M40" s="152" t="n">
         <f aca="false">L40-K40</f>
         <v>371</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="156"/>
+      <c r="B41" s="157"/>
       <c r="C41" s="64"/>
       <c r="D41" s="78"/>
-      <c r="I41" s="157" t="s">
-        <v>251</v>
-      </c>
-      <c r="J41" s="150" t="s">
+      <c r="I41" s="158" t="s">
+        <v>256</v>
+      </c>
+      <c r="J41" s="151" t="s">
+        <v>255</v>
+      </c>
+      <c r="K41" s="151" t="n">
+        <v>208.14</v>
+      </c>
+      <c r="L41" s="151" t="n">
+        <v>230</v>
+      </c>
+      <c r="M41" s="152"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I42" s="153" t="s">
+        <v>257</v>
+      </c>
+      <c r="J42" s="151" t="s">
         <v>250</v>
       </c>
-      <c r="K41" s="150" t="n">
-        <v>208.14</v>
-      </c>
-      <c r="L41" s="150" t="n">
-        <v>230</v>
-      </c>
-      <c r="M41" s="151"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I42" s="152" t="s">
-        <v>252</v>
-      </c>
-      <c r="J42" s="150" t="s">
-        <v>245</v>
-      </c>
-      <c r="K42" s="150" t="n">
+      <c r="K42" s="151" t="n">
         <v>59.9</v>
       </c>
-      <c r="L42" s="150" t="n">
+      <c r="L42" s="151" t="n">
         <v>103.9</v>
       </c>
-      <c r="M42" s="151" t="n">
+      <c r="M42" s="152" t="n">
         <f aca="false">L42-K42</f>
         <v>44</v>
       </c>
@@ -9507,22 +9544,22 @@
         <f aca="false">SUBTOTAL(9,Fev!D50,Fev!D50,Mar!D50,Abr!D50,Mai!D50,Jun!D50,Jul!D50,Ago!D50,Set!D50,Out!D50,Nov!D50,Dez!D50)</f>
         <v>354.4</v>
       </c>
-      <c r="H43" s="100" t="s">
-        <v>253</v>
-      </c>
-      <c r="I43" s="152" t="s">
-        <v>254</v>
-      </c>
-      <c r="J43" s="150" t="s">
-        <v>250</v>
-      </c>
-      <c r="K43" s="150" t="n">
+      <c r="H43" s="101" t="s">
+        <v>258</v>
+      </c>
+      <c r="I43" s="153" t="s">
+        <v>259</v>
+      </c>
+      <c r="J43" s="151" t="s">
+        <v>255</v>
+      </c>
+      <c r="K43" s="151" t="n">
         <v>175</v>
       </c>
-      <c r="L43" s="150" t="n">
+      <c r="L43" s="151" t="n">
         <v>373.58</v>
       </c>
-      <c r="M43" s="151" t="n">
+      <c r="M43" s="152" t="n">
         <f aca="false">L43-K43</f>
         <v>198.58</v>
       </c>
@@ -9530,7 +9567,7 @@
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="73" t="n">
         <f aca="false">SUM(D43:D49)</f>
-        <v>1432.38</v>
+        <v>1697.41</v>
       </c>
       <c r="C44" s="74" t="s">
         <v>57</v>
@@ -9539,23 +9576,23 @@
         <f aca="false">SUBTOTAL(9,Fev!D51,Fev!D51,Mar!D51,Abr!D51,Mai!D51,Jun!D51,Jul!D51,Ago!D51,Set!D51,Out!D51,Nov!D51,Dez!D51)</f>
         <v>10</v>
       </c>
-      <c r="H44" s="100" t="n">
+      <c r="H44" s="101" t="n">
         <f aca="false">SUM(K38:K44)</f>
         <v>1652.7</v>
       </c>
-      <c r="I44" s="158" t="s">
+      <c r="I44" s="159" t="s">
+        <v>260</v>
+      </c>
+      <c r="J44" s="160" t="s">
         <v>255</v>
       </c>
-      <c r="J44" s="159" t="s">
-        <v>250</v>
-      </c>
-      <c r="K44" s="159" t="n">
+      <c r="K44" s="160" t="n">
         <v>106.76</v>
       </c>
-      <c r="L44" s="159" t="n">
+      <c r="L44" s="160" t="n">
         <v>171.85</v>
       </c>
-      <c r="M44" s="160" t="n">
+      <c r="M44" s="161" t="n">
         <f aca="false">L44-K44</f>
         <v>65.09</v>
       </c>
@@ -9577,16 +9614,16 @@
         <f aca="false">SUBTOTAL(9,Fev!D53,Fev!D53,Mar!D53,Abr!D53,Mai!D53,Jun!D53,Jul!D53,Ago!D53,Set!D53,Out!D53,Nov!D53,Dez!D53)</f>
         <v>407.82</v>
       </c>
-      <c r="I46" s="161" t="s">
-        <v>220</v>
-      </c>
-      <c r="J46" s="161"/>
-      <c r="K46" s="161"/>
-      <c r="L46" s="162" t="n">
+      <c r="I46" s="162" t="s">
+        <v>225</v>
+      </c>
+      <c r="J46" s="162"/>
+      <c r="K46" s="162"/>
+      <c r="L46" s="163" t="n">
         <f aca="false">SUM(H34,H44)</f>
         <v>6817.92</v>
       </c>
-      <c r="M46" s="162"/>
+      <c r="M46" s="163"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C47" s="74" t="s">
@@ -9603,7 +9640,7 @@
       </c>
       <c r="D48" s="75" t="n">
         <f aca="false">SUBTOTAL(9,Fev!D55,Fev!D55,Mar!D55,Abr!D55,Mai!D55,Jun!D55,Jul!D55,Ago!D55,Set!D55,Out!D55,Nov!D55,Dez!D55)</f>
-        <v>660.16</v>
+        <v>925.19</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9628,7 +9665,7 @@
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="73" t="n">
         <f aca="false">SUM(D51:D57)</f>
-        <v>1722.18</v>
+        <v>1767.18</v>
       </c>
       <c r="C52" s="74" t="s">
         <v>40</v>
@@ -9662,7 +9699,7 @@
       </c>
       <c r="D55" s="75" t="n">
         <f aca="false">SUBTOTAL(9,Fev!D62,Fev!D62,Mar!D62,Abr!D62,Mai!D62,Jun!D62,Jul!D62,Ago!D62,Set!D62,Out!D62,Nov!D62,Dez!D62)</f>
-        <v>1230.34</v>
+        <v>1275.34</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9883,10 +9920,10 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B83" s="69" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="C83" s="70" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="D83" s="71" t="n">
         <f aca="false">SUBTOTAL(9,Fev!D90,Fev!D90,Mar!D90,Abr!D90,Mai!D90,Jun!D90,Jul!D90,Ago!D90,Set!D90,Out!D90,Nov!D90,Dez!D90)</f>
@@ -9993,45 +10030,45 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="C2" s="163" t="s">
+        <v>263</v>
+      </c>
+      <c r="C2" s="164" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="164"/>
+      <c r="E2" s="165"/>
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="165"/>
-      <c r="H2" s="164"/>
-      <c r="J2" s="166"/>
+      <c r="G2" s="166"/>
+      <c r="H2" s="165"/>
+      <c r="J2" s="167"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="167"/>
+      <c r="C3" s="168"/>
       <c r="D3" s="17"/>
-      <c r="E3" s="164"/>
+      <c r="E3" s="165"/>
       <c r="F3" s="11" t="n">
         <f aca="false">SUM(D3:D7)</f>
         <v>0</v>
       </c>
-      <c r="G3" s="165"/>
-      <c r="H3" s="164"/>
-      <c r="M3" s="168" t="s">
-        <v>259</v>
-      </c>
-      <c r="N3" s="168" t="s">
-        <v>260</v>
-      </c>
-      <c r="P3" s="169" t="s">
+      <c r="G3" s="166"/>
+      <c r="H3" s="165"/>
+      <c r="M3" s="169" t="s">
+        <v>264</v>
+      </c>
+      <c r="N3" s="169" t="s">
+        <v>265</v>
+      </c>
+      <c r="P3" s="170" t="s">
         <v>64</v>
       </c>
-      <c r="R3" s="170" t="s">
+      <c r="R3" s="171" t="s">
         <v>66</v>
       </c>
     </row>
@@ -10045,17 +10082,17 @@
         <f aca="false">SUM(F11:F32)</f>
         <v>0</v>
       </c>
-      <c r="M4" s="169" t="str">
+      <c r="M4" s="170" t="str">
         <f aca="false">P3</f>
         <v>Alimentação</v>
       </c>
-      <c r="N4" s="171" t="s">
+      <c r="N4" s="172" t="s">
         <v>65</v>
       </c>
-      <c r="P4" s="169" t="s">
+      <c r="P4" s="170" t="s">
         <v>50</v>
       </c>
-      <c r="R4" s="170" t="s">
+      <c r="R4" s="171" t="s">
         <v>35</v>
       </c>
     </row>
@@ -10069,13 +10106,13 @@
         <f aca="false">D4</f>
         <v>0</v>
       </c>
-      <c r="N5" s="171" t="s">
+      <c r="N5" s="172" t="s">
         <v>67</v>
       </c>
-      <c r="P5" s="169" t="s">
+      <c r="P5" s="170" t="s">
         <v>32</v>
       </c>
-      <c r="R5" s="170" t="s">
+      <c r="R5" s="171" t="s">
         <v>69</v>
       </c>
     </row>
@@ -10087,13 +10124,13 @@
         <f aca="false">SUM(K11:K22)</f>
         <v>0</v>
       </c>
-      <c r="N6" s="171" t="s">
+      <c r="N6" s="172" t="s">
         <v>154</v>
       </c>
-      <c r="P6" s="169" t="s">
-        <v>261</v>
-      </c>
-      <c r="R6" s="170" t="s">
+      <c r="P6" s="170" t="s">
+        <v>266</v>
+      </c>
+      <c r="R6" s="171" t="s">
         <v>71</v>
       </c>
     </row>
@@ -10103,30 +10140,30 @@
       </c>
       <c r="C7" s="33"/>
       <c r="D7" s="34" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="F7" s="36" t="n">
         <f aca="false">F3-F4-F6</f>
         <v>0</v>
       </c>
-      <c r="N7" s="171" t="s">
+      <c r="N7" s="172" t="s">
         <v>70</v>
       </c>
-      <c r="P7" s="169" t="s">
+      <c r="P7" s="170" t="s">
         <v>39</v>
       </c>
-      <c r="R7" s="170" t="s">
+      <c r="R7" s="171" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N8" s="171" t="s">
+      <c r="N8" s="172" t="s">
         <v>62</v>
       </c>
-      <c r="P8" s="169" t="s">
+      <c r="P8" s="170" t="s">
         <v>88</v>
       </c>
-      <c r="R8" s="170" t="s">
+      <c r="R8" s="171" t="s">
         <v>72</v>
       </c>
     </row>
@@ -10145,10 +10182,10 @@
       <c r="J9" s="38"/>
       <c r="K9" s="38"/>
       <c r="N9" s="79"/>
-      <c r="P9" s="169" t="s">
+      <c r="P9" s="170" t="s">
         <v>77</v>
       </c>
-      <c r="R9" s="170" t="s">
+      <c r="R9" s="171" t="s">
         <v>74</v>
       </c>
     </row>
@@ -10180,17 +10217,17 @@
       <c r="K10" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="M10" s="169" t="str">
+      <c r="M10" s="170" t="str">
         <f aca="false">P4</f>
         <v>Lazer</v>
       </c>
-      <c r="N10" s="171" t="s">
+      <c r="N10" s="172" t="s">
         <v>73</v>
       </c>
-      <c r="P10" s="169" t="s">
+      <c r="P10" s="170" t="s">
         <v>99</v>
       </c>
-      <c r="R10" s="170" t="s">
+      <c r="R10" s="171" t="s">
         <v>42</v>
       </c>
     </row>
@@ -10203,14 +10240,14 @@
       <c r="H11" s="50"/>
       <c r="I11" s="51"/>
       <c r="J11" s="51"/>
-      <c r="K11" s="172"/>
-      <c r="N11" s="171" t="s">
+      <c r="K11" s="173"/>
+      <c r="N11" s="172" t="s">
         <v>75</v>
       </c>
-      <c r="P11" s="169" t="s">
+      <c r="P11" s="170" t="s">
         <v>79</v>
       </c>
-      <c r="R11" s="170" t="s">
+      <c r="R11" s="171" t="s">
         <v>77</v>
       </c>
     </row>
@@ -10223,11 +10260,11 @@
       <c r="H12" s="59"/>
       <c r="I12" s="60"/>
       <c r="J12" s="60"/>
-      <c r="K12" s="173"/>
-      <c r="N12" s="171" t="s">
+      <c r="K12" s="174"/>
+      <c r="N12" s="172" t="s">
         <v>76</v>
       </c>
-      <c r="R12" s="170" t="s">
+      <c r="R12" s="171" t="s">
         <v>79</v>
       </c>
     </row>
@@ -10240,11 +10277,11 @@
       <c r="H13" s="59"/>
       <c r="I13" s="60"/>
       <c r="J13" s="60"/>
-      <c r="K13" s="173"/>
-      <c r="N13" s="171" t="s">
+      <c r="K13" s="174"/>
+      <c r="N13" s="172" t="s">
         <v>195</v>
       </c>
-      <c r="R13" s="170" t="s">
+      <c r="R13" s="171" t="s">
         <v>129</v>
       </c>
     </row>
@@ -10257,8 +10294,8 @@
       <c r="H14" s="59"/>
       <c r="I14" s="60"/>
       <c r="J14" s="60"/>
-      <c r="K14" s="173"/>
-      <c r="N14" s="171" t="s">
+      <c r="K14" s="174"/>
+      <c r="N14" s="172" t="s">
         <v>51</v>
       </c>
     </row>
@@ -10271,8 +10308,8 @@
       <c r="H15" s="59"/>
       <c r="I15" s="60"/>
       <c r="J15" s="60"/>
-      <c r="K15" s="173"/>
-      <c r="N15" s="171" t="s">
+      <c r="K15" s="174"/>
+      <c r="N15" s="172" t="s">
         <v>78</v>
       </c>
     </row>
@@ -10285,8 +10322,8 @@
       <c r="H16" s="59"/>
       <c r="I16" s="60"/>
       <c r="J16" s="60"/>
-      <c r="K16" s="173"/>
-      <c r="N16" s="174" t="s">
+      <c r="K16" s="174"/>
+      <c r="N16" s="175" t="s">
         <v>55</v>
       </c>
     </row>
@@ -10299,8 +10336,8 @@
       <c r="H17" s="59"/>
       <c r="I17" s="60"/>
       <c r="J17" s="60"/>
-      <c r="K17" s="173"/>
-      <c r="N17" s="170"/>
+      <c r="K17" s="174"/>
+      <c r="N17" s="171"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="56"/>
@@ -10311,7 +10348,7 @@
       <c r="H18" s="59"/>
       <c r="I18" s="60"/>
       <c r="J18" s="60"/>
-      <c r="K18" s="173"/>
+      <c r="K18" s="174"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="56"/>
@@ -10322,12 +10359,12 @@
       <c r="H19" s="59"/>
       <c r="I19" s="60"/>
       <c r="J19" s="60"/>
-      <c r="K19" s="173"/>
-      <c r="M19" s="169" t="str">
+      <c r="K19" s="174"/>
+      <c r="M19" s="170" t="str">
         <f aca="false">P5</f>
         <v>Despesas</v>
       </c>
-      <c r="N19" s="171" t="s">
+      <c r="N19" s="172" t="s">
         <v>81</v>
       </c>
     </row>
@@ -10340,8 +10377,8 @@
       <c r="H20" s="59"/>
       <c r="I20" s="60"/>
       <c r="J20" s="60"/>
-      <c r="K20" s="173"/>
-      <c r="N20" s="171" t="s">
+      <c r="K20" s="174"/>
+      <c r="N20" s="172" t="s">
         <v>57</v>
       </c>
     </row>
@@ -10354,8 +10391,8 @@
       <c r="H21" s="59"/>
       <c r="I21" s="60"/>
       <c r="J21" s="60"/>
-      <c r="K21" s="173"/>
-      <c r="N21" s="171" t="s">
+      <c r="K21" s="174"/>
+      <c r="N21" s="172" t="s">
         <v>44</v>
       </c>
     </row>
@@ -10368,8 +10405,8 @@
       <c r="H22" s="61"/>
       <c r="I22" s="62"/>
       <c r="J22" s="62"/>
-      <c r="K22" s="175"/>
-      <c r="N22" s="171" t="s">
+      <c r="K22" s="176"/>
+      <c r="N22" s="172" t="s">
         <v>33</v>
       </c>
     </row>
@@ -10379,7 +10416,7 @@
       <c r="D23" s="16"/>
       <c r="E23" s="16"/>
       <c r="F23" s="58"/>
-      <c r="N23" s="171" t="s">
+      <c r="N23" s="172" t="s">
         <v>83</v>
       </c>
     </row>
@@ -10389,7 +10426,7 @@
       <c r="D24" s="16"/>
       <c r="E24" s="16"/>
       <c r="F24" s="58"/>
-      <c r="N24" s="171" t="s">
+      <c r="N24" s="172" t="s">
         <v>59</v>
       </c>
     </row>
@@ -10399,7 +10436,7 @@
       <c r="D25" s="16"/>
       <c r="E25" s="16"/>
       <c r="F25" s="58"/>
-      <c r="N25" s="170"/>
+      <c r="N25" s="171"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="56"/>
@@ -10428,12 +10465,12 @@
       <c r="D29" s="16"/>
       <c r="E29" s="16"/>
       <c r="F29" s="58"/>
-      <c r="M29" s="169" t="str">
+      <c r="M29" s="170" t="str">
         <f aca="false">P7</f>
         <v>Transporte</v>
       </c>
-      <c r="N29" s="171" t="s">
-        <v>263</v>
+      <c r="N29" s="172" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10442,7 +10479,7 @@
       <c r="D30" s="16"/>
       <c r="E30" s="16"/>
       <c r="F30" s="58"/>
-      <c r="N30" s="171" t="s">
+      <c r="N30" s="172" t="s">
         <v>40</v>
       </c>
     </row>
@@ -10452,7 +10489,7 @@
       <c r="D31" s="16"/>
       <c r="E31" s="16"/>
       <c r="F31" s="58"/>
-      <c r="N31" s="171" t="s">
+      <c r="N31" s="172" t="s">
         <v>85</v>
       </c>
     </row>
@@ -10462,42 +10499,42 @@
       <c r="D32" s="33"/>
       <c r="E32" s="33"/>
       <c r="F32" s="68"/>
-      <c r="N32" s="171" t="s">
+      <c r="N32" s="172" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N33" s="171" t="s">
+      <c r="N33" s="172" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N34" s="171" t="s">
+      <c r="N34" s="172" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="169" t="s">
+      <c r="B35" s="170" t="s">
         <v>64</v>
       </c>
-      <c r="C35" s="171" t="s">
+      <c r="C35" s="172" t="s">
         <v>65</v>
       </c>
-      <c r="D35" s="176" t="n">
+      <c r="D35" s="177" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C35,$F$11:$F$32)</f>
         <v>0</v>
       </c>
-      <c r="N35" s="170"/>
+      <c r="N35" s="171"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="177" t="n">
+      <c r="B36" s="178" t="n">
         <f aca="false">SUBTOTAL(9,D35:D39)</f>
         <v>0</v>
       </c>
-      <c r="C36" s="171" t="s">
+      <c r="C36" s="172" t="s">
         <v>67</v>
       </c>
-      <c r="D36" s="176" t="n">
+      <c r="D36" s="177" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C36,$F$11:$F$32)</f>
         <v>0</v>
       </c>
@@ -10515,10 +10552,10 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C37" s="171" t="s">
+      <c r="C37" s="172" t="s">
         <v>68</v>
       </c>
-      <c r="D37" s="176" t="n">
+      <c r="D37" s="177" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C37,$F$11:$F$32)</f>
         <v>0</v>
       </c>
@@ -10526,19 +10563,19 @@
       <c r="I37" s="44"/>
       <c r="J37" s="45"/>
       <c r="K37" s="46"/>
-      <c r="M37" s="169" t="str">
+      <c r="M37" s="170" t="str">
         <f aca="false">P8</f>
         <v>Educação</v>
       </c>
-      <c r="N37" s="178" t="s">
-        <v>264</v>
+      <c r="N37" s="179" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C38" s="171" t="s">
+      <c r="C38" s="172" t="s">
         <v>70</v>
       </c>
-      <c r="D38" s="176" t="n">
+      <c r="D38" s="177" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C38,$F$11:$F$32)</f>
         <v>0</v>
       </c>
@@ -10546,13 +10583,13 @@
       <c r="I38" s="53"/>
       <c r="J38" s="54"/>
       <c r="K38" s="55"/>
-      <c r="N38" s="178" t="s">
+      <c r="N38" s="179" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C39" s="171"/>
-      <c r="D39" s="176" t="n">
+      <c r="C39" s="172"/>
+      <c r="D39" s="177" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C39,$F$11:$F$32)</f>
         <v>0</v>
       </c>
@@ -10560,7 +10597,7 @@
       <c r="I39" s="53"/>
       <c r="J39" s="54"/>
       <c r="K39" s="55"/>
-      <c r="N39" s="178" t="s">
+      <c r="N39" s="179" t="s">
         <v>91</v>
       </c>
     </row>
@@ -10570,18 +10607,18 @@
       <c r="I40" s="53"/>
       <c r="J40" s="54"/>
       <c r="K40" s="55"/>
-      <c r="N40" s="178" t="s">
-        <v>265</v>
+      <c r="N40" s="179" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="169" t="s">
+      <c r="B41" s="170" t="s">
         <v>50</v>
       </c>
-      <c r="C41" s="171" t="s">
+      <c r="C41" s="172" t="s">
         <v>73</v>
       </c>
-      <c r="D41" s="176" t="n">
+      <c r="D41" s="177" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C41,$F$11:$F$32)</f>
         <v>0</v>
       </c>
@@ -10589,19 +10626,19 @@
       <c r="I41" s="53"/>
       <c r="J41" s="54"/>
       <c r="K41" s="55"/>
-      <c r="N41" s="178" t="s">
+      <c r="N41" s="179" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="177" t="n">
+      <c r="B42" s="178" t="n">
         <f aca="false">SUBTOTAL(9,D41:D48)</f>
         <v>0</v>
       </c>
-      <c r="C42" s="171" t="s">
+      <c r="C42" s="172" t="s">
         <v>75</v>
       </c>
-      <c r="D42" s="176" t="n">
+      <c r="D42" s="177" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C42,$F$11:$F$32)</f>
         <v>0</v>
       </c>
@@ -10609,15 +10646,15 @@
       <c r="I42" s="53"/>
       <c r="J42" s="54"/>
       <c r="K42" s="55"/>
-      <c r="N42" s="178" t="s">
+      <c r="N42" s="179" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C43" s="171" t="s">
+      <c r="C43" s="172" t="s">
         <v>76</v>
       </c>
-      <c r="D43" s="176" t="n">
+      <c r="D43" s="177" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C43,$F$11:$F$32)</f>
         <v>0</v>
       </c>
@@ -10625,13 +10662,13 @@
       <c r="I43" s="53"/>
       <c r="J43" s="54"/>
       <c r="K43" s="55"/>
-      <c r="N43" s="179"/>
+      <c r="N43" s="180"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C44" s="171" t="s">
+      <c r="C44" s="172" t="s">
         <v>78</v>
       </c>
-      <c r="D44" s="176" t="n">
+      <c r="D44" s="177" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C44,$F$11:$F$32)</f>
         <v>0</v>
       </c>
@@ -10641,10 +10678,10 @@
       <c r="K44" s="55"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C45" s="171" t="s">
+      <c r="C45" s="172" t="s">
         <v>80</v>
       </c>
-      <c r="D45" s="176" t="n">
+      <c r="D45" s="177" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C45,$F$11:$F$32)</f>
         <v>0</v>
       </c>
@@ -10652,19 +10689,19 @@
       <c r="I45" s="53"/>
       <c r="J45" s="54"/>
       <c r="K45" s="55"/>
-      <c r="M45" s="169" t="str">
+      <c r="M45" s="170" t="str">
         <f aca="false">P9</f>
         <v>Saúde</v>
       </c>
-      <c r="N45" s="171" t="s">
+      <c r="N45" s="172" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C46" s="171" t="s">
+      <c r="C46" s="172" t="s">
         <v>51</v>
       </c>
-      <c r="D46" s="176" t="n">
+      <c r="D46" s="177" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C46,$F$11:$F$32)</f>
         <v>0</v>
       </c>
@@ -10672,13 +10709,13 @@
       <c r="I46" s="53"/>
       <c r="J46" s="54"/>
       <c r="K46" s="55"/>
-      <c r="N46" s="171" t="s">
+      <c r="N46" s="172" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C47" s="170"/>
-      <c r="D47" s="176" t="n">
+      <c r="C47" s="171"/>
+      <c r="D47" s="177" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C47,$F$11:$F$32)</f>
         <v>0</v>
       </c>
@@ -10686,13 +10723,13 @@
       <c r="I47" s="53"/>
       <c r="J47" s="54"/>
       <c r="K47" s="55"/>
-      <c r="N47" s="171" t="s">
-        <v>266</v>
+      <c r="N47" s="172" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C48" s="170"/>
-      <c r="D48" s="176" t="n">
+      <c r="C48" s="171"/>
+      <c r="D48" s="177" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C48,$F$11:$F$32)</f>
         <v>0</v>
       </c>
@@ -10700,7 +10737,7 @@
       <c r="I48" s="53"/>
       <c r="J48" s="54"/>
       <c r="K48" s="55"/>
-      <c r="N48" s="171" t="s">
+      <c r="N48" s="172" t="s">
         <v>97</v>
       </c>
     </row>
@@ -10709,18 +10746,18 @@
       <c r="I49" s="53"/>
       <c r="J49" s="54"/>
       <c r="K49" s="55"/>
-      <c r="N49" s="171" t="s">
-        <v>267</v>
+      <c r="N49" s="172" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="169" t="s">
+      <c r="B50" s="170" t="s">
         <v>32</v>
       </c>
-      <c r="C50" s="171" t="s">
+      <c r="C50" s="172" t="s">
         <v>81</v>
       </c>
-      <c r="D50" s="176" t="n">
+      <c r="D50" s="177" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C50,$F$11:$F$32)</f>
         <v>0</v>
       </c>
@@ -10728,19 +10765,19 @@
       <c r="I50" s="53"/>
       <c r="J50" s="54"/>
       <c r="K50" s="55"/>
-      <c r="N50" s="171" t="s">
+      <c r="N50" s="172" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="177" t="n">
+      <c r="B51" s="178" t="n">
         <f aca="false">SUBTOTAL(9,D50:D56)</f>
         <v>0</v>
       </c>
-      <c r="C51" s="171" t="s">
+      <c r="C51" s="172" t="s">
         <v>57</v>
       </c>
-      <c r="D51" s="176" t="n">
+      <c r="D51" s="177" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C51,$F$11:$F$32)</f>
         <v>0</v>
       </c>
@@ -10748,13 +10785,13 @@
       <c r="I51" s="53"/>
       <c r="J51" s="54"/>
       <c r="K51" s="55"/>
-      <c r="N51" s="170"/>
+      <c r="N51" s="171"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C52" s="171" t="s">
+      <c r="C52" s="172" t="s">
         <v>82</v>
       </c>
-      <c r="D52" s="176" t="n">
+      <c r="D52" s="177" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C52,$F$11:$F$32)</f>
         <v>0</v>
       </c>
@@ -10764,328 +10801,328 @@
       <c r="K52" s="63"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C53" s="171" t="s">
+      <c r="C53" s="172" t="s">
         <v>33</v>
       </c>
-      <c r="D53" s="176" t="n">
+      <c r="D53" s="177" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C53,$F$11:$F$32)</f>
         <v>0</v>
       </c>
-      <c r="M53" s="169" t="str">
+      <c r="M53" s="170" t="str">
         <f aca="false">P10</f>
         <v>Imprevistos</v>
       </c>
-      <c r="N53" s="171" t="s">
+      <c r="N53" s="172" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C54" s="171" t="s">
+      <c r="C54" s="172" t="s">
         <v>83</v>
       </c>
-      <c r="D54" s="176" t="n">
+      <c r="D54" s="177" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C54,$F$11:$F$32)</f>
         <v>0</v>
       </c>
-      <c r="N54" s="171" t="s">
+      <c r="N54" s="172" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C55" s="171" t="s">
+      <c r="C55" s="172" t="s">
         <v>59</v>
       </c>
-      <c r="D55" s="176" t="n">
+      <c r="D55" s="177" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C55,$F$11:$F$32)</f>
         <v>0</v>
       </c>
-      <c r="N55" s="171" t="s">
+      <c r="N55" s="172" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C56" s="170"/>
-      <c r="D56" s="176" t="n">
+      <c r="C56" s="171"/>
+      <c r="D56" s="177" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C56,$F$11:$F$32)</f>
         <v>0</v>
       </c>
-      <c r="N56" s="171" t="s">
+      <c r="N56" s="172" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N57" s="171" t="s">
+      <c r="N57" s="172" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B58" s="169" t="s">
+      <c r="B58" s="170" t="s">
         <v>39</v>
       </c>
-      <c r="C58" s="171" t="s">
+      <c r="C58" s="172" t="s">
         <v>84</v>
       </c>
-      <c r="D58" s="176" t="n">
+      <c r="D58" s="177" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C58,$F$11:$F$32)</f>
         <v>0</v>
       </c>
-      <c r="N58" s="171" t="s">
+      <c r="N58" s="172" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B59" s="177" t="n">
+      <c r="B59" s="178" t="n">
         <f aca="false">SUBTOTAL(9,D58:D64)</f>
         <v>0</v>
       </c>
-      <c r="C59" s="171" t="s">
+      <c r="C59" s="172" t="s">
         <v>40</v>
       </c>
-      <c r="D59" s="176" t="n">
+      <c r="D59" s="177" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C59,$F$11:$F$32)</f>
         <v>0</v>
       </c>
-      <c r="N59" s="170"/>
+      <c r="N59" s="171"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C60" s="171" t="s">
+      <c r="C60" s="172" t="s">
         <v>85</v>
       </c>
-      <c r="D60" s="176" t="n">
+      <c r="D60" s="177" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C60,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C61" s="171" t="s">
+      <c r="C61" s="172" t="s">
         <v>86</v>
       </c>
-      <c r="D61" s="176" t="n">
+      <c r="D61" s="177" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C61,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C62" s="171" t="s">
+      <c r="C62" s="172" t="s">
         <v>47</v>
       </c>
-      <c r="D62" s="176" t="n">
+      <c r="D62" s="177" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C62,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C63" s="171" t="s">
+      <c r="C63" s="172" t="s">
         <v>87</v>
       </c>
-      <c r="D63" s="176" t="n">
+      <c r="D63" s="177" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C63,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C64" s="170"/>
-      <c r="D64" s="176" t="n">
+      <c r="C64" s="171"/>
+      <c r="D64" s="177" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C64,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B66" s="169" t="s">
+      <c r="B66" s="170" t="s">
         <v>88</v>
       </c>
-      <c r="C66" s="178" t="s">
+      <c r="C66" s="179" t="s">
         <v>89</v>
       </c>
-      <c r="D66" s="176" t="n">
+      <c r="D66" s="177" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C66,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B67" s="177" t="n">
+      <c r="B67" s="178" t="n">
         <f aca="false">SUBTOTAL(9,D66:D72)</f>
         <v>0</v>
       </c>
-      <c r="C67" s="178" t="s">
+      <c r="C67" s="179" t="s">
         <v>90</v>
       </c>
-      <c r="D67" s="176" t="n">
+      <c r="D67" s="177" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C67,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C68" s="178" t="s">
+      <c r="C68" s="179" t="s">
         <v>91</v>
       </c>
-      <c r="D68" s="176" t="n">
+      <c r="D68" s="177" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C68,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C69" s="178" t="s">
+      <c r="C69" s="179" t="s">
         <v>92</v>
       </c>
-      <c r="D69" s="176" t="n">
+      <c r="D69" s="177" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C69,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C70" s="178" t="s">
+      <c r="C70" s="179" t="s">
         <v>93</v>
       </c>
-      <c r="D70" s="176" t="n">
+      <c r="D70" s="177" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C70,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C71" s="178" t="s">
+      <c r="C71" s="179" t="s">
         <v>94</v>
       </c>
-      <c r="D71" s="176" t="n">
+      <c r="D71" s="177" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C71,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C72" s="179"/>
-      <c r="D72" s="176" t="n">
+      <c r="C72" s="180"/>
+      <c r="D72" s="177" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C72,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B74" s="169" t="s">
+      <c r="B74" s="170" t="s">
         <v>77</v>
       </c>
-      <c r="C74" s="171" t="s">
+      <c r="C74" s="172" t="s">
         <v>95</v>
       </c>
-      <c r="D74" s="176" t="n">
+      <c r="D74" s="177" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C74,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B75" s="177" t="n">
+      <c r="B75" s="178" t="n">
         <f aca="false">SUBTOTAL(9,D74:D80)</f>
         <v>0</v>
       </c>
-      <c r="C75" s="171" t="s">
+      <c r="C75" s="172" t="s">
         <v>96</v>
       </c>
-      <c r="D75" s="176" t="n">
+      <c r="D75" s="177" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C75,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C76" s="171" t="s">
+      <c r="C76" s="172" t="s">
         <v>97</v>
       </c>
-      <c r="D76" s="176" t="n">
+      <c r="D76" s="177" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C76,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C77" s="171" t="s">
+      <c r="C77" s="172" t="s">
         <v>98</v>
       </c>
-      <c r="D77" s="176" t="n">
+      <c r="D77" s="177" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C77,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C78" s="170"/>
-      <c r="D78" s="176" t="n">
+      <c r="C78" s="171"/>
+      <c r="D78" s="177" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C78,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C79" s="170"/>
-      <c r="D79" s="176" t="n">
+      <c r="C79" s="171"/>
+      <c r="D79" s="177" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C79,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C80" s="170"/>
-      <c r="D80" s="176" t="n">
+      <c r="C80" s="171"/>
+      <c r="D80" s="177" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C80,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B82" s="169" t="s">
+      <c r="B82" s="170" t="s">
         <v>99</v>
       </c>
-      <c r="C82" s="171" t="s">
+      <c r="C82" s="172" t="s">
         <v>100</v>
       </c>
-      <c r="D82" s="176" t="n">
+      <c r="D82" s="177" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C82,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B83" s="177" t="n">
+      <c r="B83" s="178" t="n">
         <f aca="false">SUBTOTAL(9,D82:D88)</f>
         <v>0</v>
       </c>
-      <c r="C83" s="171" t="s">
+      <c r="C83" s="172" t="s">
         <v>101</v>
       </c>
-      <c r="D83" s="176" t="n">
+      <c r="D83" s="177" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C83,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C84" s="171" t="s">
+      <c r="C84" s="172" t="s">
         <v>102</v>
       </c>
-      <c r="D84" s="176" t="n">
+      <c r="D84" s="177" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C84,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C85" s="171" t="s">
+      <c r="C85" s="172" t="s">
         <v>103</v>
       </c>
-      <c r="D85" s="176" t="n">
+      <c r="D85" s="177" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C85,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C86" s="171" t="s">
+      <c r="C86" s="172" t="s">
         <v>104</v>
       </c>
-      <c r="D86" s="176" t="n">
+      <c r="D86" s="177" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C86,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C87" s="171" t="s">
+      <c r="C87" s="172" t="s">
         <v>105</v>
       </c>
-      <c r="D87" s="176" t="n">
+      <c r="D87" s="177" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C87,$F$11:$F$32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C88" s="170"/>
-      <c r="D88" s="176" t="n">
+      <c r="C88" s="171"/>
+      <c r="D88" s="177" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C88,$F$11:$F$32)</f>
         <v>0</v>
       </c>
@@ -11192,7 +11229,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46252</v>
+        <v>46278</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -12385,7 +12422,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46252</v>
+        <v>46278</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -13593,7 +13630,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46252</v>
+        <v>46278</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -14876,7 +14913,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46252</v>
+        <v>46278</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>150</v>
@@ -16162,7 +16199,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46252</v>
+        <v>46278</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>170</v>
@@ -17416,7 +17453,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46252</v>
+        <v>46278</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
@@ -18642,11 +18679,11 @@
       </c>
       <c r="F4" s="19" t="n">
         <f aca="false">SUM(F11:F32)</f>
-        <v>420.33</v>
+        <v>519.69</v>
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46252</v>
+        <v>46278</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>150</v>
@@ -18690,7 +18727,7 @@
       </c>
       <c r="F6" s="28" t="n">
         <f aca="false">SUM(K11:K22)</f>
-        <v>1416.36</v>
+        <v>1498.11</v>
       </c>
       <c r="I6" s="29" t="s">
         <v>203</v>
@@ -18700,7 +18737,7 @@
       </c>
       <c r="L6" s="92" t="n">
         <f aca="false">246-SUM(F15:F32)</f>
-        <v>138.34</v>
+        <v>38.98</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18717,7 +18754,7 @@
       </c>
       <c r="F7" s="36" t="n">
         <f aca="false">F3-F4-F6</f>
-        <v>900.45</v>
+        <v>719.34</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18821,7 +18858,8 @@
       </c>
       <c r="J12" s="60"/>
       <c r="K12" s="55" t="n">
-        <v>72.66</v>
+        <f aca="false">72.66+81.75</f>
+        <v>154.41</v>
       </c>
       <c r="M12" s="52"/>
       <c r="N12" s="53"/>
@@ -18994,10 +19032,16 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="56"/>
-      <c r="C20" s="57"/>
-      <c r="D20" s="57"/>
+      <c r="C20" s="57" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" s="57" t="s">
+        <v>67</v>
+      </c>
       <c r="E20" s="16"/>
-      <c r="F20" s="58"/>
+      <c r="F20" s="58" t="n">
+        <v>10</v>
+      </c>
       <c r="H20" s="59"/>
       <c r="I20" s="51"/>
       <c r="J20" s="60"/>
@@ -19009,10 +19053,16 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="56"/>
-      <c r="C21" s="57"/>
-      <c r="D21" s="57"/>
+      <c r="C21" s="57" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" s="57" t="s">
+        <v>55</v>
+      </c>
       <c r="E21" s="16"/>
-      <c r="F21" s="58"/>
+      <c r="F21" s="58" t="n">
+        <v>7.5</v>
+      </c>
       <c r="H21" s="59"/>
       <c r="I21" s="51"/>
       <c r="J21" s="60"/>
@@ -19024,10 +19074,16 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="56"/>
-      <c r="C22" s="57"/>
-      <c r="D22" s="57"/>
+      <c r="C22" s="57" t="s">
+        <v>50</v>
+      </c>
+      <c r="D22" s="57" t="s">
+        <v>73</v>
+      </c>
       <c r="E22" s="16"/>
-      <c r="F22" s="58"/>
+      <c r="F22" s="58" t="n">
+        <v>25.5</v>
+      </c>
       <c r="H22" s="61"/>
       <c r="I22" s="62"/>
       <c r="J22" s="62"/>
@@ -19039,13 +19095,19 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="56"/>
-      <c r="C23" s="57"/>
-      <c r="D23" s="57"/>
+      <c r="C23" s="57" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" s="57" t="s">
+        <v>59</v>
+      </c>
       <c r="E23" s="16"/>
-      <c r="F23" s="58"/>
+      <c r="F23" s="58" t="n">
+        <v>40</v>
+      </c>
       <c r="K23" s="12" t="n">
         <f aca="false">SUM(K11:K22)</f>
-        <v>1416.36</v>
+        <v>1498.11</v>
       </c>
       <c r="M23" s="52"/>
       <c r="N23" s="53"/>
@@ -19054,10 +19116,16 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="56"/>
-      <c r="C24" s="57"/>
-      <c r="D24" s="57"/>
+      <c r="C24" s="57" t="s">
+        <v>50</v>
+      </c>
+      <c r="D24" s="57" t="s">
+        <v>55</v>
+      </c>
       <c r="E24" s="16"/>
-      <c r="F24" s="58"/>
+      <c r="F24" s="58" t="n">
+        <v>16.36</v>
+      </c>
       <c r="M24" s="52"/>
       <c r="N24" s="53"/>
       <c r="O24" s="54"/>
@@ -19145,14 +19213,14 @@
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="73" t="n">
         <f aca="false">SUM(D35:D39)</f>
-        <v>4.3</v>
+        <v>14.3</v>
       </c>
       <c r="C36" s="74" t="s">
         <v>67</v>
       </c>
       <c r="D36" s="75" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C36,$F$11:$F$32)</f>
-        <v>4.3</v>
+        <v>14.3</v>
       </c>
       <c r="H36" s="76" t="s">
         <v>35</v>
@@ -19205,7 +19273,7 @@
       </c>
       <c r="I39" s="75" t="n">
         <f aca="false">SUMIF($I$11:$I$22,H39,$K$11:$K$22)</f>
-        <v>72.66</v>
+        <v>154.41</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19228,7 +19296,7 @@
       </c>
       <c r="D41" s="71" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C41,$F$11:$F$32)</f>
-        <v>28.48</v>
+        <v>53.98</v>
       </c>
       <c r="H41" s="76" t="s">
         <v>74</v>
@@ -19241,7 +19309,7 @@
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="73" t="n">
         <f aca="false">SUBTOTAL(9,D41:D48)</f>
-        <v>28.48</v>
+        <v>53.98</v>
       </c>
       <c r="C42" s="74" t="s">
         <v>75</v>
@@ -19345,7 +19413,7 @@
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="73" t="n">
         <f aca="false">SUM(D50:D56)</f>
-        <v>331.82</v>
+        <v>371.82</v>
       </c>
       <c r="C51" s="74" t="s">
         <v>57</v>
@@ -19388,7 +19456,7 @@
       </c>
       <c r="D55" s="75" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C55,$F$11:$F$32)</f>
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19738,7 +19806,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="13.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="11.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="34.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="8.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="13" style="1" width="12"/>
   </cols>
   <sheetData>
@@ -19766,13 +19834,15 @@
         <v>4</v>
       </c>
       <c r="C3" s="8"/>
-      <c r="D3" s="9"/>
+      <c r="D3" s="9" t="n">
+        <v>1650</v>
+      </c>
       <c r="E3" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F3" s="11" t="n">
         <f aca="false">SUM(D3,D5,D6,D7,D4)</f>
-        <v>900.45</v>
+        <v>2369.34</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>6</v>
@@ -19780,7 +19850,10 @@
       <c r="K3" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="L3" s="14"/>
+      <c r="L3" s="14" t="n">
+        <f aca="false">340+1500</f>
+        <v>1840</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="15" t="s">
@@ -19796,16 +19869,21 @@
       </c>
       <c r="F4" s="19" t="n">
         <f aca="false">SUM(F11:F32)</f>
-        <v>0</v>
+        <v>1085</v>
       </c>
       <c r="I4" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46252</v>
+        <v>46278</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="L4" s="14"/>
+      <c r="L4" s="14" t="n">
+        <v>522.75</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>205</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="21" t="s">
@@ -19842,7 +19920,7 @@
       </c>
       <c r="F6" s="28" t="n">
         <f aca="false">SUM(K11:K22)</f>
-        <v>0</v>
+        <v>443.21</v>
       </c>
       <c r="I6" s="29" t="n">
         <v>45847</v>
@@ -19850,7 +19928,9 @@
       <c r="K6" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="L6" s="31"/>
+      <c r="L6" s="31" t="n">
+        <v>304.01</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="32" t="s">
@@ -19859,14 +19939,22 @@
       <c r="C7" s="33"/>
       <c r="D7" s="34" t="n">
         <f aca="false">Ago!F7</f>
-        <v>900.45</v>
+        <v>719.34</v>
       </c>
       <c r="E7" s="35" t="s">
         <v>19</v>
       </c>
       <c r="F7" s="36" t="n">
         <f aca="false">F3-F4-F6</f>
-        <v>900.45</v>
+        <v>841.13</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H8" s="1" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19931,14 +20019,27 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="47"/>
-      <c r="C11" s="93"/>
-      <c r="D11" s="93"/>
-      <c r="E11" s="48"/>
-      <c r="F11" s="49"/>
+      <c r="C11" s="48" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="48" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="48" t="s">
+        <v>207</v>
+      </c>
+      <c r="F11" s="49" t="n">
+        <f aca="false">710.6-(560/4)</f>
+        <v>570.6</v>
+      </c>
       <c r="H11" s="50"/>
-      <c r="I11" s="94"/>
+      <c r="I11" s="51" t="s">
+        <v>129</v>
+      </c>
       <c r="J11" s="51"/>
-      <c r="K11" s="46"/>
+      <c r="K11" s="46" t="n">
+        <v>35</v>
+      </c>
       <c r="M11" s="52"/>
       <c r="N11" s="53"/>
       <c r="O11" s="54"/>
@@ -19946,14 +20047,26 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="56"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
+      <c r="C12" s="57" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="57" t="s">
+        <v>73</v>
+      </c>
       <c r="E12" s="16"/>
-      <c r="F12" s="58"/>
+      <c r="F12" s="58" t="n">
+        <v>33</v>
+      </c>
       <c r="H12" s="59"/>
-      <c r="I12" s="94"/>
-      <c r="J12" s="60"/>
-      <c r="K12" s="55"/>
+      <c r="I12" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="J12" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="K12" s="55" t="n">
+        <v>30</v>
+      </c>
       <c r="M12" s="52"/>
       <c r="N12" s="53"/>
       <c r="O12" s="54"/>
@@ -19961,14 +20074,27 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="56"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="58"/>
+      <c r="C13" s="57" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" s="57" t="s">
+        <v>59</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="F13" s="58" t="n">
+        <v>225.03</v>
+      </c>
       <c r="H13" s="59"/>
-      <c r="I13" s="94"/>
+      <c r="I13" s="51" t="s">
+        <v>49</v>
+      </c>
       <c r="J13" s="60"/>
-      <c r="K13" s="55"/>
+      <c r="K13" s="55" t="n">
+        <f aca="false">68.21</f>
+        <v>68.21</v>
+      </c>
       <c r="M13" s="52"/>
       <c r="N13" s="53"/>
       <c r="O13" s="54"/>
@@ -19976,14 +20102,26 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="56"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="58"/>
+      <c r="C14" s="57" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="57" t="s">
+        <v>55</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="F14" s="58" t="n">
+        <v>40</v>
+      </c>
       <c r="H14" s="59"/>
-      <c r="I14" s="94"/>
+      <c r="I14" s="51" t="s">
+        <v>72</v>
+      </c>
       <c r="J14" s="60"/>
-      <c r="K14" s="55"/>
+      <c r="K14" s="55" t="n">
+        <v>310</v>
+      </c>
       <c r="M14" s="52"/>
       <c r="N14" s="53"/>
       <c r="O14" s="54"/>
@@ -19991,12 +20129,18 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="56"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
+      <c r="C15" s="57" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" s="57" t="s">
+        <v>154</v>
+      </c>
       <c r="E15" s="16"/>
-      <c r="F15" s="58"/>
+      <c r="F15" s="58" t="n">
+        <v>23</v>
+      </c>
       <c r="H15" s="59"/>
-      <c r="I15" s="94"/>
+      <c r="I15" s="51"/>
       <c r="J15" s="60"/>
       <c r="K15" s="55"/>
       <c r="M15" s="52"/>
@@ -20006,12 +20150,21 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="56"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="58"/>
+      <c r="C16" s="57" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" s="57" t="s">
+        <v>51</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="F16" s="58" t="n">
+        <f aca="false">35+38+23+30+17</f>
+        <v>143</v>
+      </c>
       <c r="H16" s="59"/>
-      <c r="I16" s="94"/>
+      <c r="I16" s="51"/>
       <c r="J16" s="60"/>
       <c r="K16" s="55"/>
       <c r="M16" s="52"/>
@@ -20021,12 +20174,20 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="56"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="58"/>
+      <c r="C17" s="57" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="57" t="s">
+        <v>47</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="F17" s="58" t="n">
+        <v>45</v>
+      </c>
       <c r="H17" s="59"/>
-      <c r="I17" s="94"/>
+      <c r="I17" s="51"/>
       <c r="J17" s="60"/>
       <c r="K17" s="55"/>
       <c r="M17" s="52"/>
@@ -20036,12 +20197,18 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="56"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
+      <c r="C18" s="57" t="s">
+        <v>64</v>
+      </c>
+      <c r="D18" s="57" t="s">
+        <v>67</v>
+      </c>
       <c r="E18" s="16"/>
-      <c r="F18" s="58"/>
+      <c r="F18" s="58" t="n">
+        <v>5.37</v>
+      </c>
       <c r="H18" s="59"/>
-      <c r="I18" s="94"/>
+      <c r="I18" s="51"/>
       <c r="J18" s="60"/>
       <c r="K18" s="55"/>
       <c r="M18" s="52"/>
@@ -20051,12 +20218,12 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="56"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="57"/>
       <c r="E19" s="16"/>
       <c r="F19" s="58"/>
       <c r="H19" s="59"/>
-      <c r="I19" s="94"/>
+      <c r="I19" s="51"/>
       <c r="J19" s="60"/>
       <c r="K19" s="55"/>
       <c r="M19" s="52"/>
@@ -20066,12 +20233,12 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="56"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
+      <c r="C20" s="57"/>
+      <c r="D20" s="57"/>
       <c r="E20" s="16"/>
       <c r="F20" s="58"/>
       <c r="H20" s="59"/>
-      <c r="I20" s="94"/>
+      <c r="I20" s="51"/>
       <c r="J20" s="60"/>
       <c r="K20" s="55"/>
       <c r="M20" s="52"/>
@@ -20081,12 +20248,12 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="56"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
+      <c r="C21" s="57"/>
+      <c r="D21" s="57"/>
       <c r="E21" s="16"/>
       <c r="F21" s="58"/>
       <c r="H21" s="59"/>
-      <c r="I21" s="94"/>
+      <c r="I21" s="51"/>
       <c r="J21" s="60"/>
       <c r="K21" s="55"/>
       <c r="M21" s="52"/>
@@ -20096,8 +20263,8 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="56"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
+      <c r="C22" s="57"/>
+      <c r="D22" s="57"/>
       <c r="E22" s="16"/>
       <c r="F22" s="58"/>
       <c r="H22" s="61"/>
@@ -20111,13 +20278,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="56"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
+      <c r="C23" s="57"/>
+      <c r="D23" s="57"/>
       <c r="E23" s="16"/>
       <c r="F23" s="58"/>
-      <c r="K23" s="12" t="n">
+      <c r="K23" s="93" t="n">
         <f aca="false">SUM(K11:K22)</f>
-        <v>0</v>
+        <v>443.21</v>
       </c>
       <c r="M23" s="52"/>
       <c r="N23" s="53"/>
@@ -20126,8 +20293,8 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="56"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
+      <c r="C24" s="57"/>
+      <c r="D24" s="57"/>
       <c r="E24" s="16"/>
       <c r="F24" s="58"/>
       <c r="M24" s="52"/>
@@ -20137,8 +20304,8 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="56"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
+      <c r="C25" s="57"/>
+      <c r="D25" s="57"/>
       <c r="E25" s="16"/>
       <c r="F25" s="58"/>
       <c r="M25" s="64"/>
@@ -20148,43 +20315,43 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="56"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
+      <c r="C26" s="57"/>
+      <c r="D26" s="57"/>
       <c r="E26" s="16"/>
       <c r="F26" s="58"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="56"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
+      <c r="C27" s="57"/>
+      <c r="D27" s="57"/>
       <c r="E27" s="16"/>
       <c r="F27" s="58"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="56"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
+      <c r="C28" s="57"/>
+      <c r="D28" s="57"/>
       <c r="E28" s="16"/>
       <c r="F28" s="58"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="56"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="16"/>
+      <c r="C29" s="57"/>
+      <c r="D29" s="57"/>
       <c r="E29" s="16"/>
       <c r="F29" s="58"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="56"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
+      <c r="C30" s="57"/>
+      <c r="D30" s="57"/>
       <c r="E30" s="16"/>
       <c r="F30" s="58"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="56"/>
-      <c r="C31" s="16"/>
-      <c r="D31" s="16"/>
+      <c r="C31" s="57"/>
+      <c r="D31" s="57"/>
       <c r="E31" s="16"/>
       <c r="F31" s="58"/>
     </row>
@@ -20217,21 +20384,21 @@
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="73" t="n">
         <f aca="false">SUM(D35:D39)</f>
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="C36" s="74" t="s">
         <v>67</v>
       </c>
       <c r="D36" s="75" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C36,$F$11:$F$32)</f>
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="H36" s="76" t="s">
         <v>35</v>
       </c>
       <c r="I36" s="75" t="n">
         <f aca="false">SUMIF($I$11:$I$22,H36,$K$11:$K$22)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20277,7 +20444,7 @@
       </c>
       <c r="I39" s="75" t="n">
         <f aca="false">SUMIF($I$11:$I$22,H39,$K$11:$K$22)</f>
-        <v>0</v>
+        <v>68.21</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20288,7 +20455,7 @@
       </c>
       <c r="I40" s="75" t="n">
         <f aca="false">SUMIF($I$11:$I$22,H40,$K$11:$K$22)</f>
-        <v>0</v>
+        <v>310</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20300,7 +20467,7 @@
       </c>
       <c r="D41" s="71" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C41,$F$11:$F$32)</f>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="H41" s="76" t="s">
         <v>74</v>
@@ -20313,7 +20480,7 @@
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="73" t="n">
         <f aca="false">SUBTOTAL(9,D41:D48)</f>
-        <v>0</v>
+        <v>746.6</v>
       </c>
       <c r="C42" s="74" t="s">
         <v>75</v>
@@ -20382,7 +20549,7 @@
       </c>
       <c r="D46" s="75" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C46,$F$11:$F$32)</f>
-        <v>0</v>
+        <v>713.6</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20417,7 +20584,7 @@
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="73" t="n">
         <f aca="false">SUM(D50:D56)</f>
-        <v>0</v>
+        <v>225.03</v>
       </c>
       <c r="C51" s="74" t="s">
         <v>57</v>
@@ -20460,7 +20627,7 @@
       </c>
       <c r="D55" s="75" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C55,$F$11:$F$32)</f>
-        <v>0</v>
+        <v>225.03</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20488,7 +20655,7 @@
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="73" t="n">
         <f aca="false">SUM(D58:D64)</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C59" s="74" t="s">
         <v>40</v>
@@ -20522,7 +20689,7 @@
       </c>
       <c r="D62" s="75" t="n">
         <f aca="false">SUMIF($D$11:$D$32,C62,$F$11:$F$32)</f>
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
